--- a/Depreciation_Monthly_Schedule.xlsx
+++ b/Depreciation_Monthly_Schedule.xlsx
@@ -7,8 +7,17 @@
     <workbookView visibility="visible" minimized="0" showHorizontalScroll="1" showVerticalScroll="1" showSheetTabs="1" tabRatio="600" firstSheet="0" activeTab="0" autoFilterDateGrouping="1"/>
   </bookViews>
   <sheets>
-    <sheet name="Per-Asset Monthly" sheetId="1" state="visible" r:id="rId1"/>
-    <sheet name="Monthly Forward" sheetId="2" state="visible" r:id="rId2"/>
+    <sheet name="Per-Asset" sheetId="1" state="visible" r:id="rId1"/>
+    <sheet name="Summary by Year" sheetId="2" state="visible" r:id="rId2"/>
+    <sheet name="2026" sheetId="3" state="visible" r:id="rId3"/>
+    <sheet name="2027" sheetId="4" state="visible" r:id="rId4"/>
+    <sheet name="2028" sheetId="5" state="visible" r:id="rId5"/>
+    <sheet name="2029" sheetId="6" state="visible" r:id="rId6"/>
+    <sheet name="2030" sheetId="7" state="visible" r:id="rId7"/>
+    <sheet name="2031" sheetId="8" state="visible" r:id="rId8"/>
+    <sheet name="2032" sheetId="9" state="visible" r:id="rId9"/>
+    <sheet name="2033" sheetId="10" state="visible" r:id="rId10"/>
+    <sheet name="2034" sheetId="11" state="visible" r:id="rId11"/>
   </sheets>
   <definedNames/>
   <calcPr calcId="124519" fullCalcOnLoad="1"/>
@@ -18,7 +27,7 @@
 <file path=xl/styles.xml><?xml version="1.0" encoding="utf-8"?>
 <styleSheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
   <numFmts count="0"/>
-  <fonts count="12">
+  <fonts count="19">
     <font>
       <name val="Calibri"/>
       <family val="2"/>
@@ -59,26 +68,57 @@
     </font>
     <font>
       <b val="1"/>
+      <sz val="9"/>
+    </font>
+    <font>
+      <b val="1"/>
       <color rgb="00FFFFFF"/>
       <sz val="9"/>
     </font>
     <font>
-      <name val="Consolas"/>
-      <sz val="9"/>
+      <sz val="9.5"/>
     </font>
     <font>
       <name val="Consolas"/>
-      <b val="1"/>
-      <sz val="9"/>
+      <color rgb="00000000"/>
+      <sz val="9.5"/>
     </font>
     <font>
       <name val="Consolas"/>
       <b val="1"/>
       <color rgb="001F3864"/>
-      <sz val="9"/>
+      <sz val="9.5"/>
+    </font>
+    <font>
+      <b val="1"/>
+      <color rgb="00FFFFFF"/>
+    </font>
+    <font>
+      <name val="Consolas"/>
+      <b val="1"/>
+      <color rgb="00FFFFFF"/>
+    </font>
+    <font>
+      <b val="1"/>
+      <color rgb="00FFFFFF"/>
+      <sz val="13"/>
+    </font>
+    <font>
+      <b val="1"/>
+      <color rgb="00FFFFFF"/>
+      <sz val="9.5"/>
+    </font>
+    <font>
+      <name val="Consolas"/>
+      <b val="1"/>
+      <sz val="10"/>
+    </font>
+    <font>
+      <name val="Consolas"/>
+      <sz val="10"/>
     </font>
   </fonts>
-  <fills count="6">
+  <fills count="7">
     <fill>
       <patternFill/>
     </fill>
@@ -103,6 +143,11 @@
     <fill>
       <patternFill patternType="solid">
         <fgColor rgb="00F2F4F8"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="001E7A46"/>
       </patternFill>
     </fill>
   </fills>
@@ -132,7 +177,7 @@
   <cellStyleXfs count="1">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0"/>
   </cellStyleXfs>
-  <cellXfs count="15">
+  <cellXfs count="27">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" pivotButton="0" quotePrefix="0" xfId="0"/>
     <xf numFmtId="0" fontId="1" fillId="2" borderId="0" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
       <alignment horizontal="center" vertical="center"/>
@@ -155,25 +200,61 @@
     <xf numFmtId="4" fontId="7" fillId="0" borderId="1" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
       <alignment horizontal="right" vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="8" fillId="4" borderId="1" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+    <xf numFmtId="0" fontId="15" fillId="2" borderId="0" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="16" fillId="4" borderId="1" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
       <alignment horizontal="center" vertical="center" wrapText="1"/>
     </xf>
-    <xf numFmtId="0" fontId="9" fillId="5" borderId="1" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+    <xf numFmtId="0" fontId="17" fillId="5" borderId="1" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
       <alignment horizontal="center" vertical="center"/>
     </xf>
-    <xf numFmtId="4" fontId="9" fillId="5" borderId="1" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+    <xf numFmtId="0" fontId="18" fillId="5" borderId="1" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="4" fontId="18" fillId="5" borderId="1" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+      <alignment horizontal="right" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="17" fillId="0" borderId="1" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="18" fillId="0" borderId="1" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="4" fontId="18" fillId="0" borderId="1" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+      <alignment horizontal="right" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="13" fillId="6" borderId="1" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="4" fontId="14" fillId="6" borderId="1" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+      <alignment horizontal="right" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="8" fillId="3" borderId="0" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="9" fillId="4" borderId="1" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="10" fillId="5" borderId="1" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
       <alignment horizontal="right" vertical="center"/>
     </xf>
     <xf numFmtId="4" fontId="11" fillId="5" borderId="1" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
       <alignment horizontal="right" vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="9" fillId="0" borderId="1" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
-      <alignment horizontal="center" vertical="center"/>
+    <xf numFmtId="4" fontId="12" fillId="5" borderId="1" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+      <alignment horizontal="right" vertical="center"/>
     </xf>
-    <xf numFmtId="4" fontId="9" fillId="0" borderId="1" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+    <xf numFmtId="0" fontId="10" fillId="0" borderId="1" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
       <alignment horizontal="right" vertical="center"/>
     </xf>
     <xf numFmtId="4" fontId="11" fillId="0" borderId="1" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+      <alignment horizontal="right" vertical="center"/>
+    </xf>
+    <xf numFmtId="4" fontId="12" fillId="0" borderId="1" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+      <alignment horizontal="right" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="13" fillId="6" borderId="1" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
       <alignment horizontal="right" vertical="center"/>
     </xf>
   </cellXfs>
@@ -546,7 +627,7 @@
   <cols>
     <col width="4" customWidth="1" min="1" max="1"/>
     <col width="34" customWidth="1" min="2" max="2"/>
-    <col width="6" customWidth="1" min="3" max="3"/>
+    <col width="7" customWidth="1" min="3" max="3"/>
     <col width="11" customWidth="1" min="4" max="4"/>
     <col width="13" customWidth="1" min="5" max="5"/>
     <col width="8" customWidth="1" min="6" max="6"/>
@@ -557,17 +638,17 @@
     <col width="11" customWidth="1" min="11" max="11"/>
   </cols>
   <sheetData>
-    <row r="1" ht="26" customHeight="1">
+    <row r="1" ht="24" customHeight="1">
       <c r="A1" s="1" t="inlineStr">
         <is>
-          <t>جدول الإهلاك الشهري — لكل أصل (القسط الثابت)</t>
-        </is>
-      </c>
-    </row>
-    <row r="2" ht="16" customHeight="1">
+          <t>جدول الإهلاك الشهري — لكل أصل</t>
+        </is>
+      </c>
+    </row>
+    <row r="2" ht="15" customHeight="1">
       <c r="A2" s="2" t="inlineStr">
         <is>
-          <t>Monthly Depreciation — per asset · straight-line · balance to 30/09/2026 + monthly charge going forward · Al Marwa Projects · QAR</t>
+          <t>Per-asset · straight-line · balance to 30/09/2026 + monthly charge forward · Al Marwa Projects · QAR</t>
         </is>
       </c>
     </row>
@@ -584,60 +665,51 @@
       </c>
       <c r="C4" s="3" t="inlineStr">
         <is>
-          <t>البند
-Cat.</t>
+          <t>البند</t>
         </is>
       </c>
       <c r="D4" s="3" t="inlineStr">
         <is>
-          <t>الشراء
-Acquired</t>
+          <t>الشراء</t>
         </is>
       </c>
       <c r="E4" s="3" t="inlineStr">
         <is>
-          <t>التكلفة
-Cost</t>
+          <t>التكلفة</t>
         </is>
       </c>
       <c r="F4" s="3" t="inlineStr">
         <is>
-          <t>العمر(ش)
-Life</t>
+          <t>العمر(ش)</t>
         </is>
       </c>
       <c r="G4" s="3" t="inlineStr">
         <is>
-          <t>القسط الشهري
-Monthly</t>
+          <t>القسط الشهري</t>
         </is>
       </c>
       <c r="H4" s="3" t="inlineStr">
         <is>
-          <t>مجمّع حتى 30/9
-Accum@30/9</t>
+          <t>مجمّع حتى 30/9</t>
         </is>
       </c>
       <c r="I4" s="3" t="inlineStr">
         <is>
-          <t>صافي 30/9
-NBV@30/9</t>
+          <t>صافي 30/9</t>
         </is>
       </c>
       <c r="J4" s="3" t="inlineStr">
         <is>
-          <t>متبقّي(ش)
-Remain</t>
+          <t>متبقّي(ش)</t>
         </is>
       </c>
       <c r="K4" s="3" t="inlineStr">
         <is>
-          <t>نهاية الإهلاك
-Full-depr</t>
-        </is>
-      </c>
-    </row>
-    <row r="5" ht="13" customHeight="1">
+          <t>نهاية الإهلاك</t>
+        </is>
+      </c>
+    </row>
+    <row r="5" ht="12" customHeight="1">
       <c r="A5" s="4" t="n">
         <v>1</v>
       </c>
@@ -680,7 +752,7 @@
         </is>
       </c>
     </row>
-    <row r="6" ht="13" customHeight="1">
+    <row r="6" ht="12" customHeight="1">
       <c r="A6" s="4" t="n">
         <v>2</v>
       </c>
@@ -723,7 +795,7 @@
         </is>
       </c>
     </row>
-    <row r="7" ht="13" customHeight="1">
+    <row r="7" ht="12" customHeight="1">
       <c r="A7" s="4" t="n">
         <v>3</v>
       </c>
@@ -766,7 +838,7 @@
         </is>
       </c>
     </row>
-    <row r="8" ht="13" customHeight="1">
+    <row r="8" ht="12" customHeight="1">
       <c r="A8" s="4" t="n">
         <v>4</v>
       </c>
@@ -809,7 +881,7 @@
         </is>
       </c>
     </row>
-    <row r="9" ht="13" customHeight="1">
+    <row r="9" ht="12" customHeight="1">
       <c r="A9" s="4" t="n">
         <v>5</v>
       </c>
@@ -852,7 +924,7 @@
         </is>
       </c>
     </row>
-    <row r="10" ht="13" customHeight="1">
+    <row r="10" ht="12" customHeight="1">
       <c r="A10" s="4" t="n">
         <v>6</v>
       </c>
@@ -895,7 +967,7 @@
         </is>
       </c>
     </row>
-    <row r="11" ht="13" customHeight="1">
+    <row r="11" ht="12" customHeight="1">
       <c r="A11" s="4" t="n">
         <v>7</v>
       </c>
@@ -938,7 +1010,7 @@
         </is>
       </c>
     </row>
-    <row r="12" ht="13" customHeight="1">
+    <row r="12" ht="12" customHeight="1">
       <c r="A12" s="4" t="n">
         <v>8</v>
       </c>
@@ -981,7 +1053,7 @@
         </is>
       </c>
     </row>
-    <row r="13" ht="13" customHeight="1">
+    <row r="13" ht="12" customHeight="1">
       <c r="A13" s="4" t="n">
         <v>9</v>
       </c>
@@ -1024,7 +1096,7 @@
         </is>
       </c>
     </row>
-    <row r="14" ht="13" customHeight="1">
+    <row r="14" ht="12" customHeight="1">
       <c r="A14" s="4" t="n">
         <v>10</v>
       </c>
@@ -1067,7 +1139,7 @@
         </is>
       </c>
     </row>
-    <row r="15" ht="13" customHeight="1">
+    <row r="15" ht="12" customHeight="1">
       <c r="A15" s="4" t="n">
         <v>11</v>
       </c>
@@ -1110,7 +1182,7 @@
         </is>
       </c>
     </row>
-    <row r="16" ht="13" customHeight="1">
+    <row r="16" ht="12" customHeight="1">
       <c r="A16" s="4" t="n">
         <v>12</v>
       </c>
@@ -1153,7 +1225,7 @@
         </is>
       </c>
     </row>
-    <row r="17" ht="13" customHeight="1">
+    <row r="17" ht="12" customHeight="1">
       <c r="A17" s="4" t="n">
         <v>13</v>
       </c>
@@ -1196,7 +1268,7 @@
         </is>
       </c>
     </row>
-    <row r="18" ht="13" customHeight="1">
+    <row r="18" ht="12" customHeight="1">
       <c r="A18" s="4" t="n">
         <v>14</v>
       </c>
@@ -1239,7 +1311,7 @@
         </is>
       </c>
     </row>
-    <row r="19" ht="13" customHeight="1">
+    <row r="19" ht="12" customHeight="1">
       <c r="A19" s="4" t="n">
         <v>15</v>
       </c>
@@ -1282,7 +1354,7 @@
         </is>
       </c>
     </row>
-    <row r="20" ht="13" customHeight="1">
+    <row r="20" ht="12" customHeight="1">
       <c r="A20" s="4" t="n">
         <v>16</v>
       </c>
@@ -1325,7 +1397,7 @@
         </is>
       </c>
     </row>
-    <row r="21" ht="13" customHeight="1">
+    <row r="21" ht="12" customHeight="1">
       <c r="A21" s="4" t="n">
         <v>17</v>
       </c>
@@ -1368,7 +1440,7 @@
         </is>
       </c>
     </row>
-    <row r="22" ht="13" customHeight="1">
+    <row r="22" ht="12" customHeight="1">
       <c r="A22" s="4" t="n">
         <v>18</v>
       </c>
@@ -1411,7 +1483,7 @@
         </is>
       </c>
     </row>
-    <row r="23" ht="13" customHeight="1">
+    <row r="23" ht="12" customHeight="1">
       <c r="A23" s="4" t="n">
         <v>19</v>
       </c>
@@ -1454,7 +1526,7 @@
         </is>
       </c>
     </row>
-    <row r="24" ht="13" customHeight="1">
+    <row r="24" ht="12" customHeight="1">
       <c r="A24" s="4" t="n">
         <v>20</v>
       </c>
@@ -1497,7 +1569,7 @@
         </is>
       </c>
     </row>
-    <row r="25" ht="13" customHeight="1">
+    <row r="25" ht="12" customHeight="1">
       <c r="A25" s="4" t="n">
         <v>21</v>
       </c>
@@ -1540,7 +1612,7 @@
         </is>
       </c>
     </row>
-    <row r="26" ht="13" customHeight="1">
+    <row r="26" ht="12" customHeight="1">
       <c r="A26" s="4" t="n">
         <v>22</v>
       </c>
@@ -1583,7 +1655,7 @@
         </is>
       </c>
     </row>
-    <row r="27" ht="13" customHeight="1">
+    <row r="27" ht="12" customHeight="1">
       <c r="A27" s="4" t="n">
         <v>23</v>
       </c>
@@ -1626,7 +1698,7 @@
         </is>
       </c>
     </row>
-    <row r="28" ht="13" customHeight="1">
+    <row r="28" ht="12" customHeight="1">
       <c r="A28" s="4" t="n">
         <v>24</v>
       </c>
@@ -1669,7 +1741,7 @@
         </is>
       </c>
     </row>
-    <row r="29" ht="13" customHeight="1">
+    <row r="29" ht="12" customHeight="1">
       <c r="A29" s="4" t="n">
         <v>25</v>
       </c>
@@ -1712,7 +1784,7 @@
         </is>
       </c>
     </row>
-    <row r="30" ht="13" customHeight="1">
+    <row r="30" ht="12" customHeight="1">
       <c r="A30" s="4" t="n">
         <v>26</v>
       </c>
@@ -1755,7 +1827,7 @@
         </is>
       </c>
     </row>
-    <row r="31" ht="13" customHeight="1">
+    <row r="31" ht="12" customHeight="1">
       <c r="A31" s="4" t="n">
         <v>27</v>
       </c>
@@ -1798,7 +1870,7 @@
         </is>
       </c>
     </row>
-    <row r="32" ht="13" customHeight="1">
+    <row r="32" ht="12" customHeight="1">
       <c r="A32" s="4" t="n">
         <v>28</v>
       </c>
@@ -1841,7 +1913,7 @@
         </is>
       </c>
     </row>
-    <row r="33" ht="13" customHeight="1">
+    <row r="33" ht="12" customHeight="1">
       <c r="A33" s="4" t="n">
         <v>29</v>
       </c>
@@ -1884,7 +1956,7 @@
         </is>
       </c>
     </row>
-    <row r="34" ht="13" customHeight="1">
+    <row r="34" ht="12" customHeight="1">
       <c r="A34" s="4" t="n">
         <v>30</v>
       </c>
@@ -1927,7 +1999,7 @@
         </is>
       </c>
     </row>
-    <row r="35" ht="13" customHeight="1">
+    <row r="35" ht="12" customHeight="1">
       <c r="A35" s="4" t="n">
         <v>31</v>
       </c>
@@ -1970,7 +2042,7 @@
         </is>
       </c>
     </row>
-    <row r="36" ht="13" customHeight="1">
+    <row r="36" ht="12" customHeight="1">
       <c r="A36" s="4" t="n">
         <v>32</v>
       </c>
@@ -2013,7 +2085,7 @@
         </is>
       </c>
     </row>
-    <row r="37" ht="13" customHeight="1">
+    <row r="37" ht="12" customHeight="1">
       <c r="A37" s="4" t="n">
         <v>33</v>
       </c>
@@ -2056,7 +2128,7 @@
         </is>
       </c>
     </row>
-    <row r="38" ht="13" customHeight="1">
+    <row r="38" ht="12" customHeight="1">
       <c r="A38" s="4" t="n">
         <v>34</v>
       </c>
@@ -2099,7 +2171,7 @@
         </is>
       </c>
     </row>
-    <row r="39" ht="13" customHeight="1">
+    <row r="39" ht="12" customHeight="1">
       <c r="A39" s="4" t="n">
         <v>35</v>
       </c>
@@ -2142,7 +2214,7 @@
         </is>
       </c>
     </row>
-    <row r="40" ht="13" customHeight="1">
+    <row r="40" ht="12" customHeight="1">
       <c r="A40" s="4" t="n">
         <v>36</v>
       </c>
@@ -2185,7 +2257,7 @@
         </is>
       </c>
     </row>
-    <row r="41" ht="13" customHeight="1">
+    <row r="41" ht="12" customHeight="1">
       <c r="A41" s="4" t="n">
         <v>37</v>
       </c>
@@ -2228,7 +2300,7 @@
         </is>
       </c>
     </row>
-    <row r="42" ht="13" customHeight="1">
+    <row r="42" ht="12" customHeight="1">
       <c r="A42" s="4" t="n">
         <v>38</v>
       </c>
@@ -2271,7 +2343,7 @@
         </is>
       </c>
     </row>
-    <row r="43" ht="13" customHeight="1">
+    <row r="43" ht="12" customHeight="1">
       <c r="A43" s="4" t="n">
         <v>39</v>
       </c>
@@ -2314,7 +2386,7 @@
         </is>
       </c>
     </row>
-    <row r="44" ht="13" customHeight="1">
+    <row r="44" ht="12" customHeight="1">
       <c r="A44" s="4" t="n">
         <v>40</v>
       </c>
@@ -2357,7 +2429,7 @@
         </is>
       </c>
     </row>
-    <row r="45" ht="13" customHeight="1">
+    <row r="45" ht="12" customHeight="1">
       <c r="A45" s="4" t="n">
         <v>41</v>
       </c>
@@ -2400,7 +2472,7 @@
         </is>
       </c>
     </row>
-    <row r="46" ht="13" customHeight="1">
+    <row r="46" ht="12" customHeight="1">
       <c r="A46" s="4" t="n">
         <v>42</v>
       </c>
@@ -2443,7 +2515,7 @@
         </is>
       </c>
     </row>
-    <row r="47" ht="13" customHeight="1">
+    <row r="47" ht="12" customHeight="1">
       <c r="A47" s="4" t="n">
         <v>43</v>
       </c>
@@ -2486,7 +2558,7 @@
         </is>
       </c>
     </row>
-    <row r="48" ht="13" customHeight="1">
+    <row r="48" ht="12" customHeight="1">
       <c r="A48" s="4" t="n">
         <v>44</v>
       </c>
@@ -2529,7 +2601,7 @@
         </is>
       </c>
     </row>
-    <row r="49" ht="13" customHeight="1">
+    <row r="49" ht="12" customHeight="1">
       <c r="A49" s="4" t="n">
         <v>45</v>
       </c>
@@ -2572,7 +2644,7 @@
         </is>
       </c>
     </row>
-    <row r="50" ht="13" customHeight="1">
+    <row r="50" ht="12" customHeight="1">
       <c r="A50" s="4" t="n">
         <v>46</v>
       </c>
@@ -2615,7 +2687,7 @@
         </is>
       </c>
     </row>
-    <row r="51" ht="13" customHeight="1">
+    <row r="51" ht="12" customHeight="1">
       <c r="A51" s="4" t="n">
         <v>47</v>
       </c>
@@ -2658,7 +2730,7 @@
         </is>
       </c>
     </row>
-    <row r="52" ht="13" customHeight="1">
+    <row r="52" ht="12" customHeight="1">
       <c r="A52" s="4" t="n">
         <v>48</v>
       </c>
@@ -2701,7 +2773,7 @@
         </is>
       </c>
     </row>
-    <row r="53" ht="13" customHeight="1">
+    <row r="53" ht="12" customHeight="1">
       <c r="A53" s="4" t="n">
         <v>49</v>
       </c>
@@ -2744,7 +2816,7 @@
         </is>
       </c>
     </row>
-    <row r="54" ht="13" customHeight="1">
+    <row r="54" ht="12" customHeight="1">
       <c r="A54" s="4" t="n">
         <v>50</v>
       </c>
@@ -2787,7 +2859,7 @@
         </is>
       </c>
     </row>
-    <row r="55" ht="13" customHeight="1">
+    <row r="55" ht="12" customHeight="1">
       <c r="A55" s="4" t="n">
         <v>51</v>
       </c>
@@ -2830,7 +2902,7 @@
         </is>
       </c>
     </row>
-    <row r="56" ht="13" customHeight="1">
+    <row r="56" ht="12" customHeight="1">
       <c r="A56" s="4" t="n">
         <v>52</v>
       </c>
@@ -2873,7 +2945,7 @@
         </is>
       </c>
     </row>
-    <row r="57" ht="13" customHeight="1">
+    <row r="57" ht="12" customHeight="1">
       <c r="A57" s="4" t="n">
         <v>53</v>
       </c>
@@ -2916,7 +2988,7 @@
         </is>
       </c>
     </row>
-    <row r="58" ht="13" customHeight="1">
+    <row r="58" ht="12" customHeight="1">
       <c r="A58" s="4" t="n">
         <v>54</v>
       </c>
@@ -2959,7 +3031,7 @@
         </is>
       </c>
     </row>
-    <row r="59" ht="13" customHeight="1">
+    <row r="59" ht="12" customHeight="1">
       <c r="A59" s="4" t="n">
         <v>55</v>
       </c>
@@ -3002,7 +3074,7 @@
         </is>
       </c>
     </row>
-    <row r="60" ht="13" customHeight="1">
+    <row r="60" ht="12" customHeight="1">
       <c r="A60" s="4" t="n">
         <v>56</v>
       </c>
@@ -3045,7 +3117,7 @@
         </is>
       </c>
     </row>
-    <row r="61" ht="13" customHeight="1">
+    <row r="61" ht="12" customHeight="1">
       <c r="A61" s="4" t="n">
         <v>57</v>
       </c>
@@ -3088,7 +3160,7 @@
         </is>
       </c>
     </row>
-    <row r="62" ht="13" customHeight="1">
+    <row r="62" ht="12" customHeight="1">
       <c r="A62" s="4" t="n">
         <v>58</v>
       </c>
@@ -3131,7 +3203,7 @@
         </is>
       </c>
     </row>
-    <row r="63" ht="13" customHeight="1">
+    <row r="63" ht="12" customHeight="1">
       <c r="A63" s="4" t="n">
         <v>59</v>
       </c>
@@ -3174,7 +3246,7 @@
         </is>
       </c>
     </row>
-    <row r="64" ht="13" customHeight="1">
+    <row r="64" ht="12" customHeight="1">
       <c r="A64" s="4" t="n">
         <v>60</v>
       </c>
@@ -3217,7 +3289,7 @@
         </is>
       </c>
     </row>
-    <row r="65" ht="13" customHeight="1">
+    <row r="65" ht="12" customHeight="1">
       <c r="A65" s="4" t="n">
         <v>61</v>
       </c>
@@ -3260,7 +3332,7 @@
         </is>
       </c>
     </row>
-    <row r="66" ht="13" customHeight="1">
+    <row r="66" ht="12" customHeight="1">
       <c r="A66" s="4" t="n">
         <v>62</v>
       </c>
@@ -3303,7 +3375,7 @@
         </is>
       </c>
     </row>
-    <row r="67" ht="13" customHeight="1">
+    <row r="67" ht="12" customHeight="1">
       <c r="A67" s="4" t="n">
         <v>63</v>
       </c>
@@ -3346,7 +3418,7 @@
         </is>
       </c>
     </row>
-    <row r="68" ht="13" customHeight="1">
+    <row r="68" ht="12" customHeight="1">
       <c r="A68" s="4" t="n">
         <v>64</v>
       </c>
@@ -3389,7 +3461,7 @@
         </is>
       </c>
     </row>
-    <row r="69" ht="13" customHeight="1">
+    <row r="69" ht="12" customHeight="1">
       <c r="A69" s="4" t="n">
         <v>65</v>
       </c>
@@ -3432,7 +3504,7 @@
         </is>
       </c>
     </row>
-    <row r="70" ht="13" customHeight="1">
+    <row r="70" ht="12" customHeight="1">
       <c r="A70" s="4" t="n">
         <v>66</v>
       </c>
@@ -3475,7 +3547,7 @@
         </is>
       </c>
     </row>
-    <row r="71" ht="13" customHeight="1">
+    <row r="71" ht="12" customHeight="1">
       <c r="A71" s="4" t="n">
         <v>67</v>
       </c>
@@ -3518,7 +3590,7 @@
         </is>
       </c>
     </row>
-    <row r="72" ht="13" customHeight="1">
+    <row r="72" ht="12" customHeight="1">
       <c r="A72" s="4" t="n">
         <v>68</v>
       </c>
@@ -3561,7 +3633,7 @@
         </is>
       </c>
     </row>
-    <row r="73" ht="13" customHeight="1">
+    <row r="73" ht="12" customHeight="1">
       <c r="A73" s="4" t="n">
         <v>69</v>
       </c>
@@ -3604,7 +3676,7 @@
         </is>
       </c>
     </row>
-    <row r="74" ht="13" customHeight="1">
+    <row r="74" ht="12" customHeight="1">
       <c r="A74" s="4" t="n">
         <v>70</v>
       </c>
@@ -3647,7 +3719,7 @@
         </is>
       </c>
     </row>
-    <row r="75" ht="13" customHeight="1">
+    <row r="75" ht="12" customHeight="1">
       <c r="A75" s="4" t="n">
         <v>71</v>
       </c>
@@ -3690,7 +3762,7 @@
         </is>
       </c>
     </row>
-    <row r="76" ht="13" customHeight="1">
+    <row r="76" ht="12" customHeight="1">
       <c r="A76" s="4" t="n">
         <v>72</v>
       </c>
@@ -3733,7 +3805,7 @@
         </is>
       </c>
     </row>
-    <row r="77" ht="13" customHeight="1">
+    <row r="77" ht="12" customHeight="1">
       <c r="A77" s="4" t="n">
         <v>73</v>
       </c>
@@ -3776,7 +3848,7 @@
         </is>
       </c>
     </row>
-    <row r="78" ht="13" customHeight="1">
+    <row r="78" ht="12" customHeight="1">
       <c r="A78" s="4" t="n">
         <v>74</v>
       </c>
@@ -3819,7 +3891,7 @@
         </is>
       </c>
     </row>
-    <row r="79" ht="13" customHeight="1">
+    <row r="79" ht="12" customHeight="1">
       <c r="A79" s="4" t="n">
         <v>75</v>
       </c>
@@ -3862,7 +3934,7 @@
         </is>
       </c>
     </row>
-    <row r="80" ht="13" customHeight="1">
+    <row r="80" ht="12" customHeight="1">
       <c r="A80" s="4" t="n">
         <v>76</v>
       </c>
@@ -3905,7 +3977,7 @@
         </is>
       </c>
     </row>
-    <row r="81" ht="13" customHeight="1">
+    <row r="81" ht="12" customHeight="1">
       <c r="A81" s="4" t="n">
         <v>77</v>
       </c>
@@ -3948,7 +4020,7 @@
         </is>
       </c>
     </row>
-    <row r="82" ht="13" customHeight="1">
+    <row r="82" ht="12" customHeight="1">
       <c r="A82" s="4" t="n">
         <v>78</v>
       </c>
@@ -3991,7 +4063,7 @@
         </is>
       </c>
     </row>
-    <row r="83" ht="13" customHeight="1">
+    <row r="83" ht="12" customHeight="1">
       <c r="A83" s="4" t="n">
         <v>79</v>
       </c>
@@ -4034,7 +4106,7 @@
         </is>
       </c>
     </row>
-    <row r="84" ht="13" customHeight="1">
+    <row r="84" ht="12" customHeight="1">
       <c r="A84" s="4" t="n">
         <v>80</v>
       </c>
@@ -4077,7 +4149,7 @@
         </is>
       </c>
     </row>
-    <row r="85" ht="13" customHeight="1">
+    <row r="85" ht="12" customHeight="1">
       <c r="A85" s="4" t="n">
         <v>81</v>
       </c>
@@ -4120,7 +4192,7 @@
         </is>
       </c>
     </row>
-    <row r="86" ht="13" customHeight="1">
+    <row r="86" ht="12" customHeight="1">
       <c r="A86" s="4" t="n">
         <v>82</v>
       </c>
@@ -4163,7 +4235,7 @@
         </is>
       </c>
     </row>
-    <row r="87" ht="13" customHeight="1">
+    <row r="87" ht="12" customHeight="1">
       <c r="A87" s="4" t="n">
         <v>83</v>
       </c>
@@ -4206,7 +4278,7 @@
         </is>
       </c>
     </row>
-    <row r="88" ht="13" customHeight="1">
+    <row r="88" ht="12" customHeight="1">
       <c r="A88" s="4" t="n">
         <v>84</v>
       </c>
@@ -4249,7 +4321,7 @@
         </is>
       </c>
     </row>
-    <row r="89" ht="13" customHeight="1">
+    <row r="89" ht="12" customHeight="1">
       <c r="A89" s="4" t="n">
         <v>85</v>
       </c>
@@ -4292,7 +4364,7 @@
         </is>
       </c>
     </row>
-    <row r="90" ht="13" customHeight="1">
+    <row r="90" ht="12" customHeight="1">
       <c r="A90" s="4" t="n">
         <v>86</v>
       </c>
@@ -4335,7 +4407,7 @@
         </is>
       </c>
     </row>
-    <row r="91" ht="13" customHeight="1">
+    <row r="91" ht="12" customHeight="1">
       <c r="A91" s="4" t="n">
         <v>87</v>
       </c>
@@ -4378,7 +4450,7 @@
         </is>
       </c>
     </row>
-    <row r="92" ht="13" customHeight="1">
+    <row r="92" ht="12" customHeight="1">
       <c r="A92" s="4" t="n">
         <v>88</v>
       </c>
@@ -4421,7 +4493,7 @@
         </is>
       </c>
     </row>
-    <row r="93" ht="13" customHeight="1">
+    <row r="93" ht="12" customHeight="1">
       <c r="A93" s="4" t="n">
         <v>89</v>
       </c>
@@ -4464,7 +4536,7 @@
         </is>
       </c>
     </row>
-    <row r="94" ht="13" customHeight="1">
+    <row r="94" ht="12" customHeight="1">
       <c r="A94" s="4" t="n">
         <v>90</v>
       </c>
@@ -4507,7 +4579,7 @@
         </is>
       </c>
     </row>
-    <row r="95" ht="13" customHeight="1">
+    <row r="95" ht="12" customHeight="1">
       <c r="A95" s="4" t="n">
         <v>91</v>
       </c>
@@ -4550,7 +4622,7 @@
         </is>
       </c>
     </row>
-    <row r="96" ht="13" customHeight="1">
+    <row r="96" ht="12" customHeight="1">
       <c r="A96" s="4" t="n">
         <v>92</v>
       </c>
@@ -4593,7 +4665,7 @@
         </is>
       </c>
     </row>
-    <row r="97" ht="13" customHeight="1">
+    <row r="97" ht="12" customHeight="1">
       <c r="A97" s="4" t="n">
         <v>93</v>
       </c>
@@ -4636,7 +4708,7 @@
         </is>
       </c>
     </row>
-    <row r="98" ht="13" customHeight="1">
+    <row r="98" ht="12" customHeight="1">
       <c r="A98" s="4" t="n">
         <v>94</v>
       </c>
@@ -4679,7 +4751,7 @@
         </is>
       </c>
     </row>
-    <row r="99" ht="13" customHeight="1">
+    <row r="99" ht="12" customHeight="1">
       <c r="A99" s="4" t="n">
         <v>95</v>
       </c>
@@ -4722,7 +4794,7 @@
         </is>
       </c>
     </row>
-    <row r="100" ht="13" customHeight="1">
+    <row r="100" ht="12" customHeight="1">
       <c r="A100" s="4" t="n">
         <v>96</v>
       </c>
@@ -4765,7 +4837,7 @@
         </is>
       </c>
     </row>
-    <row r="101" ht="13" customHeight="1">
+    <row r="101" ht="12" customHeight="1">
       <c r="A101" s="4" t="n">
         <v>97</v>
       </c>
@@ -4808,7 +4880,7 @@
         </is>
       </c>
     </row>
-    <row r="102" ht="13" customHeight="1">
+    <row r="102" ht="12" customHeight="1">
       <c r="A102" s="4" t="n">
         <v>98</v>
       </c>
@@ -4851,7 +4923,7 @@
         </is>
       </c>
     </row>
-    <row r="103" ht="13" customHeight="1">
+    <row r="103" ht="12" customHeight="1">
       <c r="A103" s="4" t="n">
         <v>99</v>
       </c>
@@ -4894,7 +4966,7 @@
         </is>
       </c>
     </row>
-    <row r="104" ht="13" customHeight="1">
+    <row r="104" ht="12" customHeight="1">
       <c r="A104" s="4" t="n">
         <v>100</v>
       </c>
@@ -4937,7 +5009,7 @@
         </is>
       </c>
     </row>
-    <row r="105" ht="13" customHeight="1">
+    <row r="105" ht="12" customHeight="1">
       <c r="A105" s="4" t="n">
         <v>101</v>
       </c>
@@ -4980,7 +5052,7 @@
         </is>
       </c>
     </row>
-    <row r="106" ht="13" customHeight="1">
+    <row r="106" ht="12" customHeight="1">
       <c r="A106" s="4" t="n">
         <v>102</v>
       </c>
@@ -5023,7 +5095,7 @@
         </is>
       </c>
     </row>
-    <row r="107" ht="13" customHeight="1">
+    <row r="107" ht="12" customHeight="1">
       <c r="A107" s="4" t="n">
         <v>103</v>
       </c>
@@ -5066,7 +5138,7 @@
         </is>
       </c>
     </row>
-    <row r="108" ht="13" customHeight="1">
+    <row r="108" ht="12" customHeight="1">
       <c r="A108" s="4" t="n">
         <v>104</v>
       </c>
@@ -5109,7 +5181,7 @@
         </is>
       </c>
     </row>
-    <row r="109" ht="13" customHeight="1">
+    <row r="109" ht="12" customHeight="1">
       <c r="A109" s="4" t="n">
         <v>105</v>
       </c>
@@ -5152,7 +5224,7 @@
         </is>
       </c>
     </row>
-    <row r="110" ht="13" customHeight="1">
+    <row r="110" ht="12" customHeight="1">
       <c r="A110" s="4" t="n">
         <v>106</v>
       </c>
@@ -5195,7 +5267,7 @@
         </is>
       </c>
     </row>
-    <row r="111" ht="13" customHeight="1">
+    <row r="111" ht="12" customHeight="1">
       <c r="A111" s="4" t="n">
         <v>107</v>
       </c>
@@ -5238,7 +5310,7 @@
         </is>
       </c>
     </row>
-    <row r="112" ht="13" customHeight="1">
+    <row r="112" ht="12" customHeight="1">
       <c r="A112" s="4" t="n">
         <v>108</v>
       </c>
@@ -5281,7 +5353,7 @@
         </is>
       </c>
     </row>
-    <row r="113" ht="13" customHeight="1">
+    <row r="113" ht="12" customHeight="1">
       <c r="A113" s="4" t="n">
         <v>109</v>
       </c>
@@ -5324,7 +5396,7 @@
         </is>
       </c>
     </row>
-    <row r="114" ht="13" customHeight="1">
+    <row r="114" ht="12" customHeight="1">
       <c r="A114" s="4" t="n">
         <v>110</v>
       </c>
@@ -5367,7 +5439,7 @@
         </is>
       </c>
     </row>
-    <row r="115" ht="13" customHeight="1">
+    <row r="115" ht="12" customHeight="1">
       <c r="A115" s="4" t="n">
         <v>111</v>
       </c>
@@ -5410,7 +5482,7 @@
         </is>
       </c>
     </row>
-    <row r="116" ht="13" customHeight="1">
+    <row r="116" ht="12" customHeight="1">
       <c r="A116" s="4" t="n">
         <v>112</v>
       </c>
@@ -5453,7 +5525,7 @@
         </is>
       </c>
     </row>
-    <row r="117" ht="13" customHeight="1">
+    <row r="117" ht="12" customHeight="1">
       <c r="A117" s="4" t="n">
         <v>113</v>
       </c>
@@ -5496,7 +5568,7 @@
         </is>
       </c>
     </row>
-    <row r="118" ht="13" customHeight="1">
+    <row r="118" ht="12" customHeight="1">
       <c r="A118" s="4" t="n">
         <v>114</v>
       </c>
@@ -5539,7 +5611,7 @@
         </is>
       </c>
     </row>
-    <row r="119" ht="13" customHeight="1">
+    <row r="119" ht="12" customHeight="1">
       <c r="A119" s="4" t="n">
         <v>115</v>
       </c>
@@ -5582,7 +5654,7 @@
         </is>
       </c>
     </row>
-    <row r="120" ht="13" customHeight="1">
+    <row r="120" ht="12" customHeight="1">
       <c r="A120" s="4" t="n">
         <v>116</v>
       </c>
@@ -5625,7 +5697,7 @@
         </is>
       </c>
     </row>
-    <row r="121" ht="13" customHeight="1">
+    <row r="121" ht="12" customHeight="1">
       <c r="A121" s="4" t="n">
         <v>117</v>
       </c>
@@ -5668,7 +5740,7 @@
         </is>
       </c>
     </row>
-    <row r="122" ht="13" customHeight="1">
+    <row r="122" ht="12" customHeight="1">
       <c r="A122" s="4" t="n">
         <v>118</v>
       </c>
@@ -5711,7 +5783,7 @@
         </is>
       </c>
     </row>
-    <row r="123" ht="13" customHeight="1">
+    <row r="123" ht="12" customHeight="1">
       <c r="A123" s="4" t="n">
         <v>119</v>
       </c>
@@ -5754,7 +5826,7 @@
         </is>
       </c>
     </row>
-    <row r="124" ht="13" customHeight="1">
+    <row r="124" ht="12" customHeight="1">
       <c r="A124" s="4" t="n">
         <v>120</v>
       </c>
@@ -5797,7 +5869,7 @@
         </is>
       </c>
     </row>
-    <row r="125" ht="13" customHeight="1">
+    <row r="125" ht="12" customHeight="1">
       <c r="A125" s="4" t="n">
         <v>121</v>
       </c>
@@ -5840,7 +5912,7 @@
         </is>
       </c>
     </row>
-    <row r="126" ht="13" customHeight="1">
+    <row r="126" ht="12" customHeight="1">
       <c r="A126" s="4" t="n">
         <v>122</v>
       </c>
@@ -5883,7 +5955,7 @@
         </is>
       </c>
     </row>
-    <row r="127" ht="13" customHeight="1">
+    <row r="127" ht="12" customHeight="1">
       <c r="A127" s="4" t="n">
         <v>123</v>
       </c>
@@ -5926,7 +5998,7 @@
         </is>
       </c>
     </row>
-    <row r="128" ht="13" customHeight="1">
+    <row r="128" ht="12" customHeight="1">
       <c r="A128" s="4" t="n">
         <v>124</v>
       </c>
@@ -5969,7 +6041,7 @@
         </is>
       </c>
     </row>
-    <row r="129" ht="13" customHeight="1">
+    <row r="129" ht="12" customHeight="1">
       <c r="A129" s="4" t="n">
         <v>125</v>
       </c>
@@ -6012,7 +6084,7 @@
         </is>
       </c>
     </row>
-    <row r="130" ht="13" customHeight="1">
+    <row r="130" ht="12" customHeight="1">
       <c r="A130" s="4" t="n">
         <v>126</v>
       </c>
@@ -6055,7 +6127,7 @@
         </is>
       </c>
     </row>
-    <row r="131" ht="13" customHeight="1">
+    <row r="131" ht="12" customHeight="1">
       <c r="A131" s="4" t="n">
         <v>127</v>
       </c>
@@ -6098,7 +6170,7 @@
         </is>
       </c>
     </row>
-    <row r="132" ht="13" customHeight="1">
+    <row r="132" ht="12" customHeight="1">
       <c r="A132" s="4" t="n">
         <v>128</v>
       </c>
@@ -6141,7 +6213,7 @@
         </is>
       </c>
     </row>
-    <row r="133" ht="13" customHeight="1">
+    <row r="133" ht="12" customHeight="1">
       <c r="A133" s="4" t="n">
         <v>129</v>
       </c>
@@ -6184,7 +6256,7 @@
         </is>
       </c>
     </row>
-    <row r="134" ht="13" customHeight="1">
+    <row r="134" ht="12" customHeight="1">
       <c r="A134" s="4" t="n">
         <v>130</v>
       </c>
@@ -6227,7 +6299,7 @@
         </is>
       </c>
     </row>
-    <row r="135" ht="13" customHeight="1">
+    <row r="135" ht="12" customHeight="1">
       <c r="A135" s="4" t="n">
         <v>131</v>
       </c>
@@ -6270,7 +6342,7 @@
         </is>
       </c>
     </row>
-    <row r="136" ht="13" customHeight="1">
+    <row r="136" ht="12" customHeight="1">
       <c r="A136" s="4" t="n">
         <v>132</v>
       </c>
@@ -6313,7 +6385,7 @@
         </is>
       </c>
     </row>
-    <row r="137" ht="13" customHeight="1">
+    <row r="137" ht="12" customHeight="1">
       <c r="A137" s="4" t="n">
         <v>133</v>
       </c>
@@ -6356,7 +6428,7 @@
         </is>
       </c>
     </row>
-    <row r="138" ht="13" customHeight="1">
+    <row r="138" ht="12" customHeight="1">
       <c r="A138" s="4" t="n">
         <v>134</v>
       </c>
@@ -6399,7 +6471,7 @@
         </is>
       </c>
     </row>
-    <row r="139" ht="13" customHeight="1">
+    <row r="139" ht="12" customHeight="1">
       <c r="A139" s="4" t="n">
         <v>135</v>
       </c>
@@ -6442,7 +6514,7 @@
         </is>
       </c>
     </row>
-    <row r="140" ht="13" customHeight="1">
+    <row r="140" ht="12" customHeight="1">
       <c r="A140" s="4" t="n">
         <v>136</v>
       </c>
@@ -6485,7 +6557,7 @@
         </is>
       </c>
     </row>
-    <row r="141" ht="13" customHeight="1">
+    <row r="141" ht="12" customHeight="1">
       <c r="A141" s="4" t="n">
         <v>137</v>
       </c>
@@ -6528,7 +6600,7 @@
         </is>
       </c>
     </row>
-    <row r="142" ht="13" customHeight="1">
+    <row r="142" ht="12" customHeight="1">
       <c r="A142" s="4" t="n">
         <v>138</v>
       </c>
@@ -6571,7 +6643,7 @@
         </is>
       </c>
     </row>
-    <row r="143" ht="13" customHeight="1">
+    <row r="143" ht="12" customHeight="1">
       <c r="A143" s="4" t="n">
         <v>139</v>
       </c>
@@ -6614,7 +6686,7 @@
         </is>
       </c>
     </row>
-    <row r="144" ht="13" customHeight="1">
+    <row r="144" ht="12" customHeight="1">
       <c r="A144" s="4" t="n">
         <v>140</v>
       </c>
@@ -6657,7 +6729,7 @@
         </is>
       </c>
     </row>
-    <row r="145" ht="13" customHeight="1">
+    <row r="145" ht="12" customHeight="1">
       <c r="A145" s="4" t="n">
         <v>141</v>
       </c>
@@ -6700,7 +6772,7 @@
         </is>
       </c>
     </row>
-    <row r="146" ht="13" customHeight="1">
+    <row r="146" ht="12" customHeight="1">
       <c r="A146" s="4" t="n">
         <v>142</v>
       </c>
@@ -6743,7 +6815,7 @@
         </is>
       </c>
     </row>
-    <row r="147" ht="13" customHeight="1">
+    <row r="147" ht="12" customHeight="1">
       <c r="A147" s="4" t="n">
         <v>143</v>
       </c>
@@ -6786,7 +6858,7 @@
         </is>
       </c>
     </row>
-    <row r="148" ht="13" customHeight="1">
+    <row r="148" ht="12" customHeight="1">
       <c r="A148" s="4" t="n">
         <v>144</v>
       </c>
@@ -6829,7 +6901,7 @@
         </is>
       </c>
     </row>
-    <row r="149" ht="13" customHeight="1">
+    <row r="149" ht="12" customHeight="1">
       <c r="A149" s="4" t="n">
         <v>145</v>
       </c>
@@ -6872,7 +6944,7 @@
         </is>
       </c>
     </row>
-    <row r="150" ht="13" customHeight="1">
+    <row r="150" ht="12" customHeight="1">
       <c r="A150" s="4" t="n">
         <v>146</v>
       </c>
@@ -6915,7 +6987,7 @@
         </is>
       </c>
     </row>
-    <row r="151" ht="13" customHeight="1">
+    <row r="151" ht="12" customHeight="1">
       <c r="A151" s="4" t="n">
         <v>147</v>
       </c>
@@ -6958,7 +7030,7 @@
         </is>
       </c>
     </row>
-    <row r="152" ht="13" customHeight="1">
+    <row r="152" ht="12" customHeight="1">
       <c r="A152" s="4" t="n">
         <v>148</v>
       </c>
@@ -7001,7 +7073,7 @@
         </is>
       </c>
     </row>
-    <row r="153" ht="13" customHeight="1">
+    <row r="153" ht="12" customHeight="1">
       <c r="A153" s="4" t="n">
         <v>149</v>
       </c>
@@ -7044,7 +7116,7 @@
         </is>
       </c>
     </row>
-    <row r="154" ht="13" customHeight="1">
+    <row r="154" ht="12" customHeight="1">
       <c r="A154" s="4" t="n">
         <v>150</v>
       </c>
@@ -7087,7 +7159,7 @@
         </is>
       </c>
     </row>
-    <row r="155" ht="13" customHeight="1">
+    <row r="155" ht="12" customHeight="1">
       <c r="A155" s="4" t="n">
         <v>151</v>
       </c>
@@ -7130,7 +7202,7 @@
         </is>
       </c>
     </row>
-    <row r="156" ht="13" customHeight="1">
+    <row r="156" ht="12" customHeight="1">
       <c r="A156" s="4" t="n">
         <v>152</v>
       </c>
@@ -7173,7 +7245,7 @@
         </is>
       </c>
     </row>
-    <row r="157" ht="13" customHeight="1">
+    <row r="157" ht="12" customHeight="1">
       <c r="A157" s="4" t="n">
         <v>153</v>
       </c>
@@ -7216,7 +7288,7 @@
         </is>
       </c>
     </row>
-    <row r="158" ht="13" customHeight="1">
+    <row r="158" ht="12" customHeight="1">
       <c r="A158" s="4" t="n">
         <v>154</v>
       </c>
@@ -7259,7 +7331,7 @@
         </is>
       </c>
     </row>
-    <row r="159" ht="13" customHeight="1">
+    <row r="159" ht="12" customHeight="1">
       <c r="A159" s="4" t="n">
         <v>155</v>
       </c>
@@ -7302,7 +7374,7 @@
         </is>
       </c>
     </row>
-    <row r="160" ht="13" customHeight="1">
+    <row r="160" ht="12" customHeight="1">
       <c r="A160" s="4" t="n">
         <v>156</v>
       </c>
@@ -7345,7 +7417,7 @@
         </is>
       </c>
     </row>
-    <row r="161" ht="13" customHeight="1">
+    <row r="161" ht="12" customHeight="1">
       <c r="A161" s="4" t="n">
         <v>157</v>
       </c>
@@ -7388,7 +7460,7 @@
         </is>
       </c>
     </row>
-    <row r="162" ht="13" customHeight="1">
+    <row r="162" ht="12" customHeight="1">
       <c r="A162" s="4" t="n">
         <v>158</v>
       </c>
@@ -7431,7 +7503,7 @@
         </is>
       </c>
     </row>
-    <row r="163" ht="13" customHeight="1">
+    <row r="163" ht="12" customHeight="1">
       <c r="A163" s="4" t="n">
         <v>159</v>
       </c>
@@ -7474,7 +7546,7 @@
         </is>
       </c>
     </row>
-    <row r="164" ht="13" customHeight="1">
+    <row r="164" ht="12" customHeight="1">
       <c r="A164" s="4" t="n">
         <v>160</v>
       </c>
@@ -7517,7 +7589,7 @@
         </is>
       </c>
     </row>
-    <row r="165" ht="13" customHeight="1">
+    <row r="165" ht="12" customHeight="1">
       <c r="A165" s="4" t="n">
         <v>161</v>
       </c>
@@ -7560,7 +7632,7 @@
         </is>
       </c>
     </row>
-    <row r="166" ht="13" customHeight="1">
+    <row r="166" ht="12" customHeight="1">
       <c r="A166" s="4" t="n">
         <v>162</v>
       </c>
@@ -7603,7 +7675,7 @@
         </is>
       </c>
     </row>
-    <row r="167" ht="13" customHeight="1">
+    <row r="167" ht="12" customHeight="1">
       <c r="A167" s="4" t="n">
         <v>163</v>
       </c>
@@ -7646,7 +7718,7 @@
         </is>
       </c>
     </row>
-    <row r="168" ht="13" customHeight="1">
+    <row r="168" ht="12" customHeight="1">
       <c r="A168" s="4" t="n">
         <v>164</v>
       </c>
@@ -7689,7 +7761,7 @@
         </is>
       </c>
     </row>
-    <row r="169" ht="13" customHeight="1">
+    <row r="169" ht="12" customHeight="1">
       <c r="A169" s="4" t="n">
         <v>165</v>
       </c>
@@ -7732,7 +7804,7 @@
         </is>
       </c>
     </row>
-    <row r="170" ht="13" customHeight="1">
+    <row r="170" ht="12" customHeight="1">
       <c r="A170" s="4" t="n">
         <v>166</v>
       </c>
@@ -7775,7 +7847,7 @@
         </is>
       </c>
     </row>
-    <row r="171" ht="13" customHeight="1">
+    <row r="171" ht="12" customHeight="1">
       <c r="A171" s="4" t="n">
         <v>167</v>
       </c>
@@ -7818,7 +7890,7 @@
         </is>
       </c>
     </row>
-    <row r="172" ht="13" customHeight="1">
+    <row r="172" ht="12" customHeight="1">
       <c r="A172" s="4" t="n">
         <v>168</v>
       </c>
@@ -7861,7 +7933,7 @@
         </is>
       </c>
     </row>
-    <row r="173" ht="13" customHeight="1">
+    <row r="173" ht="12" customHeight="1">
       <c r="A173" s="4" t="n">
         <v>169</v>
       </c>
@@ -7904,7 +7976,7 @@
         </is>
       </c>
     </row>
-    <row r="174" ht="13" customHeight="1">
+    <row r="174" ht="12" customHeight="1">
       <c r="A174" s="4" t="n">
         <v>170</v>
       </c>
@@ -7947,7 +8019,7 @@
         </is>
       </c>
     </row>
-    <row r="175" ht="13" customHeight="1">
+    <row r="175" ht="12" customHeight="1">
       <c r="A175" s="4" t="n">
         <v>171</v>
       </c>
@@ -7990,7 +8062,7 @@
         </is>
       </c>
     </row>
-    <row r="176" ht="13" customHeight="1">
+    <row r="176" ht="12" customHeight="1">
       <c r="A176" s="4" t="n">
         <v>172</v>
       </c>
@@ -8033,7 +8105,7 @@
         </is>
       </c>
     </row>
-    <row r="177" ht="13" customHeight="1">
+    <row r="177" ht="12" customHeight="1">
       <c r="A177" s="4" t="n">
         <v>173</v>
       </c>
@@ -8076,7 +8148,7 @@
         </is>
       </c>
     </row>
-    <row r="178" ht="13" customHeight="1">
+    <row r="178" ht="12" customHeight="1">
       <c r="A178" s="4" t="n">
         <v>174</v>
       </c>
@@ -8119,7 +8191,7 @@
         </is>
       </c>
     </row>
-    <row r="179" ht="13" customHeight="1">
+    <row r="179" ht="12" customHeight="1">
       <c r="A179" s="4" t="n">
         <v>175</v>
       </c>
@@ -8162,7 +8234,7 @@
         </is>
       </c>
     </row>
-    <row r="180" ht="13" customHeight="1">
+    <row r="180" ht="12" customHeight="1">
       <c r="A180" s="4" t="n">
         <v>176</v>
       </c>
@@ -8205,7 +8277,7 @@
         </is>
       </c>
     </row>
-    <row r="181" ht="13" customHeight="1">
+    <row r="181" ht="12" customHeight="1">
       <c r="A181" s="4" t="n">
         <v>177</v>
       </c>
@@ -8248,7 +8320,7 @@
         </is>
       </c>
     </row>
-    <row r="182" ht="13" customHeight="1">
+    <row r="182" ht="12" customHeight="1">
       <c r="A182" s="4" t="n">
         <v>178</v>
       </c>
@@ -8291,7 +8363,7 @@
         </is>
       </c>
     </row>
-    <row r="183" ht="13" customHeight="1">
+    <row r="183" ht="12" customHeight="1">
       <c r="A183" s="4" t="n">
         <v>179</v>
       </c>
@@ -8334,7 +8406,7 @@
         </is>
       </c>
     </row>
-    <row r="184" ht="13" customHeight="1">
+    <row r="184" ht="12" customHeight="1">
       <c r="A184" s="4" t="n">
         <v>180</v>
       </c>
@@ -8377,7 +8449,7 @@
         </is>
       </c>
     </row>
-    <row r="185" ht="13" customHeight="1">
+    <row r="185" ht="12" customHeight="1">
       <c r="A185" s="4" t="n">
         <v>181</v>
       </c>
@@ -8420,7 +8492,7 @@
         </is>
       </c>
     </row>
-    <row r="186" ht="13" customHeight="1">
+    <row r="186" ht="12" customHeight="1">
       <c r="A186" s="4" t="n">
         <v>182</v>
       </c>
@@ -8463,7 +8535,7 @@
         </is>
       </c>
     </row>
-    <row r="187" ht="13" customHeight="1">
+    <row r="187" ht="12" customHeight="1">
       <c r="A187" s="4" t="n">
         <v>183</v>
       </c>
@@ -8506,7 +8578,7 @@
         </is>
       </c>
     </row>
-    <row r="188" ht="13" customHeight="1">
+    <row r="188" ht="12" customHeight="1">
       <c r="A188" s="4" t="n">
         <v>184</v>
       </c>
@@ -8549,7 +8621,7 @@
         </is>
       </c>
     </row>
-    <row r="189" ht="13" customHeight="1">
+    <row r="189" ht="12" customHeight="1">
       <c r="A189" s="4" t="n">
         <v>185</v>
       </c>
@@ -8592,7 +8664,7 @@
         </is>
       </c>
     </row>
-    <row r="190" ht="13" customHeight="1">
+    <row r="190" ht="12" customHeight="1">
       <c r="A190" s="4" t="n">
         <v>186</v>
       </c>
@@ -8635,7 +8707,7 @@
         </is>
       </c>
     </row>
-    <row r="191" ht="13" customHeight="1">
+    <row r="191" ht="12" customHeight="1">
       <c r="A191" s="4" t="n">
         <v>187</v>
       </c>
@@ -8678,7 +8750,7 @@
         </is>
       </c>
     </row>
-    <row r="192" ht="13" customHeight="1">
+    <row r="192" ht="12" customHeight="1">
       <c r="A192" s="4" t="n">
         <v>188</v>
       </c>
@@ -8721,7 +8793,7 @@
         </is>
       </c>
     </row>
-    <row r="193" ht="13" customHeight="1">
+    <row r="193" ht="12" customHeight="1">
       <c r="A193" s="4" t="n">
         <v>189</v>
       </c>
@@ -8764,7 +8836,7 @@
         </is>
       </c>
     </row>
-    <row r="194" ht="13" customHeight="1">
+    <row r="194" ht="12" customHeight="1">
       <c r="A194" s="4" t="n">
         <v>190</v>
       </c>
@@ -8807,7 +8879,7 @@
         </is>
       </c>
     </row>
-    <row r="195" ht="13" customHeight="1">
+    <row r="195" ht="12" customHeight="1">
       <c r="A195" s="4" t="n">
         <v>191</v>
       </c>
@@ -8850,7 +8922,7 @@
         </is>
       </c>
     </row>
-    <row r="196" ht="13" customHeight="1">
+    <row r="196" ht="12" customHeight="1">
       <c r="A196" s="4" t="n">
         <v>192</v>
       </c>
@@ -8893,7 +8965,7 @@
         </is>
       </c>
     </row>
-    <row r="197" ht="13" customHeight="1">
+    <row r="197" ht="12" customHeight="1">
       <c r="A197" s="4" t="n">
         <v>193</v>
       </c>
@@ -8936,7 +9008,7 @@
         </is>
       </c>
     </row>
-    <row r="198" ht="13" customHeight="1">
+    <row r="198" ht="12" customHeight="1">
       <c r="A198" s="4" t="n">
         <v>194</v>
       </c>
@@ -8979,7 +9051,7 @@
         </is>
       </c>
     </row>
-    <row r="199" ht="13" customHeight="1">
+    <row r="199" ht="12" customHeight="1">
       <c r="A199" s="4" t="n">
         <v>195</v>
       </c>
@@ -9022,7 +9094,7 @@
         </is>
       </c>
     </row>
-    <row r="200" ht="13" customHeight="1">
+    <row r="200" ht="12" customHeight="1">
       <c r="A200" s="4" t="n">
         <v>196</v>
       </c>
@@ -9065,7 +9137,7 @@
         </is>
       </c>
     </row>
-    <row r="201" ht="13" customHeight="1">
+    <row r="201" ht="12" customHeight="1">
       <c r="A201" s="4" t="n">
         <v>197</v>
       </c>
@@ -9108,7 +9180,7 @@
         </is>
       </c>
     </row>
-    <row r="202" ht="13" customHeight="1">
+    <row r="202" ht="12" customHeight="1">
       <c r="A202" s="4" t="n">
         <v>198</v>
       </c>
@@ -9151,7 +9223,7 @@
         </is>
       </c>
     </row>
-    <row r="203" ht="13" customHeight="1">
+    <row r="203" ht="12" customHeight="1">
       <c r="A203" s="4" t="n">
         <v>199</v>
       </c>
@@ -9194,7 +9266,7 @@
         </is>
       </c>
     </row>
-    <row r="204" ht="13" customHeight="1">
+    <row r="204" ht="12" customHeight="1">
       <c r="A204" s="4" t="n">
         <v>200</v>
       </c>
@@ -9237,7 +9309,7 @@
         </is>
       </c>
     </row>
-    <row r="205" ht="13" customHeight="1">
+    <row r="205" ht="12" customHeight="1">
       <c r="A205" s="4" t="n">
         <v>201</v>
       </c>
@@ -9280,7 +9352,7 @@
         </is>
       </c>
     </row>
-    <row r="206" ht="13" customHeight="1">
+    <row r="206" ht="12" customHeight="1">
       <c r="A206" s="4" t="n">
         <v>202</v>
       </c>
@@ -9323,7 +9395,7 @@
         </is>
       </c>
     </row>
-    <row r="207" ht="13" customHeight="1">
+    <row r="207" ht="12" customHeight="1">
       <c r="A207" s="4" t="n">
         <v>203</v>
       </c>
@@ -9366,7 +9438,7 @@
         </is>
       </c>
     </row>
-    <row r="208" ht="13" customHeight="1">
+    <row r="208" ht="12" customHeight="1">
       <c r="A208" s="4" t="n">
         <v>204</v>
       </c>
@@ -9409,7 +9481,7 @@
         </is>
       </c>
     </row>
-    <row r="209" ht="13" customHeight="1">
+    <row r="209" ht="12" customHeight="1">
       <c r="A209" s="4" t="n">
         <v>205</v>
       </c>
@@ -9452,7 +9524,7 @@
         </is>
       </c>
     </row>
-    <row r="210" ht="13" customHeight="1">
+    <row r="210" ht="12" customHeight="1">
       <c r="A210" s="4" t="n">
         <v>206</v>
       </c>
@@ -9495,7 +9567,7 @@
         </is>
       </c>
     </row>
-    <row r="211" ht="13" customHeight="1">
+    <row r="211" ht="12" customHeight="1">
       <c r="A211" s="4" t="n">
         <v>207</v>
       </c>
@@ -9538,7 +9610,7 @@
         </is>
       </c>
     </row>
-    <row r="212" ht="13" customHeight="1">
+    <row r="212" ht="12" customHeight="1">
       <c r="A212" s="4" t="n">
         <v>208</v>
       </c>
@@ -9581,7 +9653,7 @@
         </is>
       </c>
     </row>
-    <row r="213" ht="13" customHeight="1">
+    <row r="213" ht="12" customHeight="1">
       <c r="A213" s="4" t="n">
         <v>209</v>
       </c>
@@ -9624,7 +9696,7 @@
         </is>
       </c>
     </row>
-    <row r="214" ht="13" customHeight="1">
+    <row r="214" ht="12" customHeight="1">
       <c r="A214" s="4" t="n">
         <v>210</v>
       </c>
@@ -9667,7 +9739,7 @@
         </is>
       </c>
     </row>
-    <row r="215" ht="13" customHeight="1">
+    <row r="215" ht="12" customHeight="1">
       <c r="A215" s="4" t="n">
         <v>211</v>
       </c>
@@ -9710,7 +9782,7 @@
         </is>
       </c>
     </row>
-    <row r="216" ht="13" customHeight="1">
+    <row r="216" ht="12" customHeight="1">
       <c r="A216" s="4" t="n">
         <v>212</v>
       </c>
@@ -9753,7 +9825,7 @@
         </is>
       </c>
     </row>
-    <row r="217" ht="13" customHeight="1">
+    <row r="217" ht="12" customHeight="1">
       <c r="A217" s="4" t="n">
         <v>213</v>
       </c>
@@ -9796,7 +9868,7 @@
         </is>
       </c>
     </row>
-    <row r="218" ht="13" customHeight="1">
+    <row r="218" ht="12" customHeight="1">
       <c r="A218" s="4" t="n">
         <v>214</v>
       </c>
@@ -9839,7 +9911,7 @@
         </is>
       </c>
     </row>
-    <row r="219" ht="13" customHeight="1">
+    <row r="219" ht="12" customHeight="1">
       <c r="A219" s="4" t="n">
         <v>215</v>
       </c>
@@ -9882,7 +9954,7 @@
         </is>
       </c>
     </row>
-    <row r="220" ht="13" customHeight="1">
+    <row r="220" ht="12" customHeight="1">
       <c r="A220" s="4" t="n">
         <v>216</v>
       </c>
@@ -9925,7 +9997,7 @@
         </is>
       </c>
     </row>
-    <row r="221" ht="13" customHeight="1">
+    <row r="221" ht="12" customHeight="1">
       <c r="A221" s="4" t="n">
         <v>217</v>
       </c>
@@ -9968,7 +10040,7 @@
         </is>
       </c>
     </row>
-    <row r="222" ht="13" customHeight="1">
+    <row r="222" ht="12" customHeight="1">
       <c r="A222" s="4" t="n">
         <v>218</v>
       </c>
@@ -10011,7 +10083,7 @@
         </is>
       </c>
     </row>
-    <row r="223" ht="13" customHeight="1">
+    <row r="223" ht="12" customHeight="1">
       <c r="A223" s="4" t="n">
         <v>219</v>
       </c>
@@ -10054,7 +10126,7 @@
         </is>
       </c>
     </row>
-    <row r="224" ht="13" customHeight="1">
+    <row r="224" ht="12" customHeight="1">
       <c r="A224" s="4" t="n">
         <v>220</v>
       </c>
@@ -10097,7 +10169,7 @@
         </is>
       </c>
     </row>
-    <row r="225" ht="13" customHeight="1">
+    <row r="225" ht="12" customHeight="1">
       <c r="A225" s="4" t="n">
         <v>221</v>
       </c>
@@ -10140,7 +10212,7 @@
         </is>
       </c>
     </row>
-    <row r="226" ht="13" customHeight="1">
+    <row r="226" ht="12" customHeight="1">
       <c r="A226" s="4" t="n">
         <v>222</v>
       </c>
@@ -10183,7 +10255,7 @@
         </is>
       </c>
     </row>
-    <row r="227" ht="13" customHeight="1">
+    <row r="227" ht="12" customHeight="1">
       <c r="A227" s="4" t="n">
         <v>223</v>
       </c>
@@ -10226,7 +10298,7 @@
         </is>
       </c>
     </row>
-    <row r="228" ht="13" customHeight="1">
+    <row r="228" ht="12" customHeight="1">
       <c r="A228" s="4" t="n">
         <v>224</v>
       </c>
@@ -10269,7 +10341,7 @@
         </is>
       </c>
     </row>
-    <row r="229" ht="13" customHeight="1">
+    <row r="229" ht="12" customHeight="1">
       <c r="A229" s="4" t="n">
         <v>225</v>
       </c>
@@ -10312,7 +10384,7 @@
         </is>
       </c>
     </row>
-    <row r="230" ht="13" customHeight="1">
+    <row r="230" ht="12" customHeight="1">
       <c r="A230" s="4" t="n">
         <v>226</v>
       </c>
@@ -10355,7 +10427,7 @@
         </is>
       </c>
     </row>
-    <row r="231" ht="13" customHeight="1">
+    <row r="231" ht="12" customHeight="1">
       <c r="A231" s="4" t="n">
         <v>227</v>
       </c>
@@ -10398,7 +10470,7 @@
         </is>
       </c>
     </row>
-    <row r="232" ht="13" customHeight="1">
+    <row r="232" ht="12" customHeight="1">
       <c r="A232" s="4" t="n">
         <v>228</v>
       </c>
@@ -10441,7 +10513,7 @@
         </is>
       </c>
     </row>
-    <row r="233" ht="13" customHeight="1">
+    <row r="233" ht="12" customHeight="1">
       <c r="A233" s="4" t="n">
         <v>229</v>
       </c>
@@ -10484,7 +10556,7 @@
         </is>
       </c>
     </row>
-    <row r="234" ht="13" customHeight="1">
+    <row r="234" ht="12" customHeight="1">
       <c r="A234" s="4" t="n">
         <v>230</v>
       </c>
@@ -10527,7 +10599,7 @@
         </is>
       </c>
     </row>
-    <row r="235" ht="13" customHeight="1">
+    <row r="235" ht="12" customHeight="1">
       <c r="A235" s="4" t="n">
         <v>231</v>
       </c>
@@ -10570,7 +10642,7 @@
         </is>
       </c>
     </row>
-    <row r="236" ht="13" customHeight="1">
+    <row r="236" ht="12" customHeight="1">
       <c r="A236" s="4" t="n">
         <v>232</v>
       </c>
@@ -10613,7 +10685,7 @@
         </is>
       </c>
     </row>
-    <row r="237" ht="13" customHeight="1">
+    <row r="237" ht="12" customHeight="1">
       <c r="A237" s="4" t="n">
         <v>233</v>
       </c>
@@ -10656,7 +10728,7 @@
         </is>
       </c>
     </row>
-    <row r="238" ht="13" customHeight="1">
+    <row r="238" ht="12" customHeight="1">
       <c r="A238" s="4" t="n">
         <v>234</v>
       </c>
@@ -10699,7 +10771,7 @@
         </is>
       </c>
     </row>
-    <row r="239" ht="13" customHeight="1">
+    <row r="239" ht="12" customHeight="1">
       <c r="A239" s="4" t="n">
         <v>235</v>
       </c>
@@ -10742,7 +10814,7 @@
         </is>
       </c>
     </row>
-    <row r="240" ht="13" customHeight="1">
+    <row r="240" ht="12" customHeight="1">
       <c r="A240" s="4" t="n">
         <v>236</v>
       </c>
@@ -10785,7 +10857,7 @@
         </is>
       </c>
     </row>
-    <row r="241" ht="13" customHeight="1">
+    <row r="241" ht="12" customHeight="1">
       <c r="A241" s="4" t="n">
         <v>237</v>
       </c>
@@ -10828,7 +10900,7 @@
         </is>
       </c>
     </row>
-    <row r="242" ht="13" customHeight="1">
+    <row r="242" ht="12" customHeight="1">
       <c r="A242" s="4" t="n">
         <v>238</v>
       </c>
@@ -10871,7 +10943,7 @@
         </is>
       </c>
     </row>
-    <row r="243" ht="13" customHeight="1">
+    <row r="243" ht="12" customHeight="1">
       <c r="A243" s="4" t="n">
         <v>239</v>
       </c>
@@ -10914,7 +10986,7 @@
         </is>
       </c>
     </row>
-    <row r="244" ht="13" customHeight="1">
+    <row r="244" ht="12" customHeight="1">
       <c r="A244" s="4" t="n">
         <v>240</v>
       </c>
@@ -10957,7 +11029,7 @@
         </is>
       </c>
     </row>
-    <row r="245" ht="13" customHeight="1">
+    <row r="245" ht="12" customHeight="1">
       <c r="A245" s="4" t="n">
         <v>241</v>
       </c>
@@ -11000,7 +11072,7 @@
         </is>
       </c>
     </row>
-    <row r="246" ht="13" customHeight="1">
+    <row r="246" ht="12" customHeight="1">
       <c r="A246" s="4" t="n">
         <v>242</v>
       </c>
@@ -11043,7 +11115,7 @@
         </is>
       </c>
     </row>
-    <row r="247" ht="13" customHeight="1">
+    <row r="247" ht="12" customHeight="1">
       <c r="A247" s="4" t="n">
         <v>243</v>
       </c>
@@ -11086,7 +11158,7 @@
         </is>
       </c>
     </row>
-    <row r="248" ht="13" customHeight="1">
+    <row r="248" ht="12" customHeight="1">
       <c r="A248" s="4" t="n">
         <v>244</v>
       </c>
@@ -11129,7 +11201,7 @@
         </is>
       </c>
     </row>
-    <row r="249" ht="13" customHeight="1">
+    <row r="249" ht="12" customHeight="1">
       <c r="A249" s="4" t="n">
         <v>245</v>
       </c>
@@ -11172,7 +11244,7 @@
         </is>
       </c>
     </row>
-    <row r="250" ht="13" customHeight="1">
+    <row r="250" ht="12" customHeight="1">
       <c r="A250" s="4" t="n">
         <v>246</v>
       </c>
@@ -11215,7 +11287,7 @@
         </is>
       </c>
     </row>
-    <row r="251" ht="13" customHeight="1">
+    <row r="251" ht="12" customHeight="1">
       <c r="A251" s="4" t="n">
         <v>247</v>
       </c>
@@ -11258,7 +11330,7 @@
         </is>
       </c>
     </row>
-    <row r="252" ht="13" customHeight="1">
+    <row r="252" ht="12" customHeight="1">
       <c r="A252" s="4" t="n">
         <v>248</v>
       </c>
@@ -11301,7 +11373,7 @@
         </is>
       </c>
     </row>
-    <row r="253" ht="13" customHeight="1">
+    <row r="253" ht="12" customHeight="1">
       <c r="A253" s="4" t="n">
         <v>249</v>
       </c>
@@ -11344,7 +11416,7 @@
         </is>
       </c>
     </row>
-    <row r="254" ht="13" customHeight="1">
+    <row r="254" ht="12" customHeight="1">
       <c r="A254" s="4" t="n">
         <v>250</v>
       </c>
@@ -11387,7 +11459,7 @@
         </is>
       </c>
     </row>
-    <row r="255" ht="13" customHeight="1">
+    <row r="255" ht="12" customHeight="1">
       <c r="A255" s="4" t="n">
         <v>251</v>
       </c>
@@ -11430,7 +11502,7 @@
         </is>
       </c>
     </row>
-    <row r="256" ht="13" customHeight="1">
+    <row r="256" ht="12" customHeight="1">
       <c r="A256" s="4" t="n">
         <v>252</v>
       </c>
@@ -11473,7 +11545,7 @@
         </is>
       </c>
     </row>
-    <row r="257" ht="13" customHeight="1">
+    <row r="257" ht="12" customHeight="1">
       <c r="A257" s="4" t="n">
         <v>253</v>
       </c>
@@ -11516,7 +11588,7 @@
         </is>
       </c>
     </row>
-    <row r="258" ht="13" customHeight="1">
+    <row r="258" ht="12" customHeight="1">
       <c r="A258" s="4" t="n">
         <v>254</v>
       </c>
@@ -11559,7 +11631,7 @@
         </is>
       </c>
     </row>
-    <row r="259" ht="13" customHeight="1">
+    <row r="259" ht="12" customHeight="1">
       <c r="A259" s="4" t="n">
         <v>255</v>
       </c>
@@ -11602,7 +11674,7 @@
         </is>
       </c>
     </row>
-    <row r="260" ht="13" customHeight="1">
+    <row r="260" ht="12" customHeight="1">
       <c r="A260" s="4" t="n">
         <v>256</v>
       </c>
@@ -11645,7 +11717,7 @@
         </is>
       </c>
     </row>
-    <row r="261" ht="13" customHeight="1">
+    <row r="261" ht="12" customHeight="1">
       <c r="A261" s="4" t="n">
         <v>257</v>
       </c>
@@ -11688,7 +11760,7 @@
         </is>
       </c>
     </row>
-    <row r="262" ht="13" customHeight="1">
+    <row r="262" ht="12" customHeight="1">
       <c r="A262" s="4" t="n">
         <v>258</v>
       </c>
@@ -11731,7 +11803,7 @@
         </is>
       </c>
     </row>
-    <row r="263" ht="13" customHeight="1">
+    <row r="263" ht="12" customHeight="1">
       <c r="A263" s="4" t="n">
         <v>259</v>
       </c>
@@ -11774,7 +11846,7 @@
         </is>
       </c>
     </row>
-    <row r="264" ht="13" customHeight="1">
+    <row r="264" ht="12" customHeight="1">
       <c r="A264" s="4" t="n">
         <v>260</v>
       </c>
@@ -11817,7 +11889,7 @@
         </is>
       </c>
     </row>
-    <row r="265" ht="13" customHeight="1">
+    <row r="265" ht="12" customHeight="1">
       <c r="A265" s="4" t="n">
         <v>261</v>
       </c>
@@ -11860,7 +11932,7 @@
         </is>
       </c>
     </row>
-    <row r="266" ht="13" customHeight="1">
+    <row r="266" ht="12" customHeight="1">
       <c r="A266" s="4" t="n">
         <v>262</v>
       </c>
@@ -11903,7 +11975,7 @@
         </is>
       </c>
     </row>
-    <row r="267" ht="13" customHeight="1">
+    <row r="267" ht="12" customHeight="1">
       <c r="A267" s="4" t="n">
         <v>263</v>
       </c>
@@ -11946,7 +12018,7 @@
         </is>
       </c>
     </row>
-    <row r="268" ht="13" customHeight="1">
+    <row r="268" ht="12" customHeight="1">
       <c r="A268" s="4" t="n">
         <v>264</v>
       </c>
@@ -11989,7 +12061,7 @@
         </is>
       </c>
     </row>
-    <row r="269" ht="13" customHeight="1">
+    <row r="269" ht="12" customHeight="1">
       <c r="A269" s="4" t="n">
         <v>265</v>
       </c>
@@ -12032,7 +12104,7 @@
         </is>
       </c>
     </row>
-    <row r="270" ht="13" customHeight="1">
+    <row r="270" ht="12" customHeight="1">
       <c r="A270" s="4" t="n">
         <v>266</v>
       </c>
@@ -12075,7 +12147,7 @@
         </is>
       </c>
     </row>
-    <row r="271" ht="13" customHeight="1">
+    <row r="271" ht="12" customHeight="1">
       <c r="A271" s="4" t="n">
         <v>267</v>
       </c>
@@ -12118,7 +12190,7 @@
         </is>
       </c>
     </row>
-    <row r="272" ht="13" customHeight="1">
+    <row r="272" ht="12" customHeight="1">
       <c r="A272" s="4" t="n">
         <v>268</v>
       </c>
@@ -12161,7 +12233,7 @@
         </is>
       </c>
     </row>
-    <row r="273" ht="13" customHeight="1">
+    <row r="273" ht="12" customHeight="1">
       <c r="A273" s="4" t="n">
         <v>269</v>
       </c>
@@ -12204,7 +12276,7 @@
         </is>
       </c>
     </row>
-    <row r="274" ht="13" customHeight="1">
+    <row r="274" ht="12" customHeight="1">
       <c r="A274" s="4" t="n">
         <v>270</v>
       </c>
@@ -12247,7 +12319,7 @@
         </is>
       </c>
     </row>
-    <row r="275" ht="13" customHeight="1">
+    <row r="275" ht="12" customHeight="1">
       <c r="A275" s="4" t="n">
         <v>271</v>
       </c>
@@ -12290,7 +12362,7 @@
         </is>
       </c>
     </row>
-    <row r="276" ht="13" customHeight="1">
+    <row r="276" ht="12" customHeight="1">
       <c r="A276" s="4" t="n">
         <v>272</v>
       </c>
@@ -12333,7 +12405,7 @@
         </is>
       </c>
     </row>
-    <row r="277" ht="13" customHeight="1">
+    <row r="277" ht="12" customHeight="1">
       <c r="A277" s="4" t="n">
         <v>273</v>
       </c>
@@ -12376,7 +12448,7 @@
         </is>
       </c>
     </row>
-    <row r="278" ht="13" customHeight="1">
+    <row r="278" ht="12" customHeight="1">
       <c r="A278" s="4" t="n">
         <v>274</v>
       </c>
@@ -12419,7 +12491,7 @@
         </is>
       </c>
     </row>
-    <row r="279" ht="13" customHeight="1">
+    <row r="279" ht="12" customHeight="1">
       <c r="A279" s="4" t="n">
         <v>275</v>
       </c>
@@ -12462,7 +12534,7 @@
         </is>
       </c>
     </row>
-    <row r="280" ht="13" customHeight="1">
+    <row r="280" ht="12" customHeight="1">
       <c r="A280" s="4" t="n">
         <v>276</v>
       </c>
@@ -12505,7 +12577,7 @@
         </is>
       </c>
     </row>
-    <row r="281" ht="13" customHeight="1">
+    <row r="281" ht="12" customHeight="1">
       <c r="A281" s="4" t="n">
         <v>277</v>
       </c>
@@ -12548,7 +12620,7 @@
         </is>
       </c>
     </row>
-    <row r="282" ht="13" customHeight="1">
+    <row r="282" ht="12" customHeight="1">
       <c r="A282" s="4" t="n">
         <v>278</v>
       </c>
@@ -12591,7 +12663,7 @@
         </is>
       </c>
     </row>
-    <row r="283" ht="13" customHeight="1">
+    <row r="283" ht="12" customHeight="1">
       <c r="A283" s="4" t="n">
         <v>279</v>
       </c>
@@ -12634,7 +12706,7 @@
         </is>
       </c>
     </row>
-    <row r="284" ht="13" customHeight="1">
+    <row r="284" ht="12" customHeight="1">
       <c r="A284" s="4" t="n">
         <v>280</v>
       </c>
@@ -12677,7 +12749,7 @@
         </is>
       </c>
     </row>
-    <row r="285" ht="13" customHeight="1">
+    <row r="285" ht="12" customHeight="1">
       <c r="A285" s="4" t="n">
         <v>281</v>
       </c>
@@ -12720,7 +12792,7 @@
         </is>
       </c>
     </row>
-    <row r="286" ht="13" customHeight="1">
+    <row r="286" ht="12" customHeight="1">
       <c r="A286" s="4" t="n">
         <v>282</v>
       </c>
@@ -12763,7 +12835,7 @@
         </is>
       </c>
     </row>
-    <row r="287" ht="13" customHeight="1">
+    <row r="287" ht="12" customHeight="1">
       <c r="A287" s="4" t="n">
         <v>283</v>
       </c>
@@ -12806,7 +12878,7 @@
         </is>
       </c>
     </row>
-    <row r="288" ht="13" customHeight="1">
+    <row r="288" ht="12" customHeight="1">
       <c r="A288" s="4" t="n">
         <v>284</v>
       </c>
@@ -12849,7 +12921,7 @@
         </is>
       </c>
     </row>
-    <row r="289" ht="13" customHeight="1">
+    <row r="289" ht="12" customHeight="1">
       <c r="A289" s="4" t="n">
         <v>285</v>
       </c>
@@ -12892,7 +12964,7 @@
         </is>
       </c>
     </row>
-    <row r="290" ht="13" customHeight="1">
+    <row r="290" ht="12" customHeight="1">
       <c r="A290" s="4" t="n">
         <v>286</v>
       </c>
@@ -12935,7 +13007,7 @@
         </is>
       </c>
     </row>
-    <row r="291" ht="13" customHeight="1">
+    <row r="291" ht="12" customHeight="1">
       <c r="A291" s="4" t="n">
         <v>287</v>
       </c>
@@ -12978,7 +13050,7 @@
         </is>
       </c>
     </row>
-    <row r="292" ht="13" customHeight="1">
+    <row r="292" ht="12" customHeight="1">
       <c r="A292" s="4" t="n">
         <v>288</v>
       </c>
@@ -13021,7 +13093,7 @@
         </is>
       </c>
     </row>
-    <row r="293" ht="13" customHeight="1">
+    <row r="293" ht="12" customHeight="1">
       <c r="A293" s="4" t="n">
         <v>289</v>
       </c>
@@ -13064,7 +13136,7 @@
         </is>
       </c>
     </row>
-    <row r="294" ht="13" customHeight="1">
+    <row r="294" ht="12" customHeight="1">
       <c r="A294" s="4" t="n">
         <v>290</v>
       </c>
@@ -13107,7 +13179,7 @@
         </is>
       </c>
     </row>
-    <row r="295" ht="13" customHeight="1">
+    <row r="295" ht="12" customHeight="1">
       <c r="A295" s="4" t="n">
         <v>291</v>
       </c>
@@ -13150,7 +13222,7 @@
         </is>
       </c>
     </row>
-    <row r="296" ht="13" customHeight="1">
+    <row r="296" ht="12" customHeight="1">
       <c r="A296" s="4" t="n">
         <v>292</v>
       </c>
@@ -13193,7 +13265,7 @@
         </is>
       </c>
     </row>
-    <row r="297" ht="13" customHeight="1">
+    <row r="297" ht="12" customHeight="1">
       <c r="A297" s="4" t="n">
         <v>293</v>
       </c>
@@ -13236,7 +13308,7 @@
         </is>
       </c>
     </row>
-    <row r="298" ht="13" customHeight="1">
+    <row r="298" ht="12" customHeight="1">
       <c r="A298" s="4" t="n">
         <v>294</v>
       </c>
@@ -13279,7 +13351,7 @@
         </is>
       </c>
     </row>
-    <row r="299" ht="13" customHeight="1">
+    <row r="299" ht="12" customHeight="1">
       <c r="A299" s="4" t="n">
         <v>295</v>
       </c>
@@ -13322,7 +13394,7 @@
         </is>
       </c>
     </row>
-    <row r="300" ht="13" customHeight="1">
+    <row r="300" ht="12" customHeight="1">
       <c r="A300" s="4" t="n">
         <v>296</v>
       </c>
@@ -13365,7 +13437,7 @@
         </is>
       </c>
     </row>
-    <row r="301" ht="13" customHeight="1">
+    <row r="301" ht="12" customHeight="1">
       <c r="A301" s="4" t="n">
         <v>297</v>
       </c>
@@ -13408,7 +13480,7 @@
         </is>
       </c>
     </row>
-    <row r="302" ht="13" customHeight="1">
+    <row r="302" ht="12" customHeight="1">
       <c r="A302" s="4" t="n">
         <v>298</v>
       </c>
@@ -13451,7 +13523,7 @@
         </is>
       </c>
     </row>
-    <row r="303" ht="13" customHeight="1">
+    <row r="303" ht="12" customHeight="1">
       <c r="A303" s="4" t="n">
         <v>299</v>
       </c>
@@ -13494,7 +13566,7 @@
         </is>
       </c>
     </row>
-    <row r="304" ht="13" customHeight="1">
+    <row r="304" ht="12" customHeight="1">
       <c r="A304" s="4" t="n">
         <v>300</v>
       </c>
@@ -13537,7 +13609,7 @@
         </is>
       </c>
     </row>
-    <row r="305" ht="13" customHeight="1">
+    <row r="305" ht="12" customHeight="1">
       <c r="A305" s="4" t="n">
         <v>301</v>
       </c>
@@ -13580,7 +13652,7 @@
         </is>
       </c>
     </row>
-    <row r="306" ht="13" customHeight="1">
+    <row r="306" ht="12" customHeight="1">
       <c r="A306" s="4" t="n">
         <v>302</v>
       </c>
@@ -13623,7 +13695,7 @@
         </is>
       </c>
     </row>
-    <row r="307" ht="13" customHeight="1">
+    <row r="307" ht="12" customHeight="1">
       <c r="A307" s="4" t="n">
         <v>303</v>
       </c>
@@ -13666,7 +13738,7 @@
         </is>
       </c>
     </row>
-    <row r="308" ht="13" customHeight="1">
+    <row r="308" ht="12" customHeight="1">
       <c r="A308" s="4" t="n">
         <v>304</v>
       </c>
@@ -13709,7 +13781,7 @@
         </is>
       </c>
     </row>
-    <row r="309" ht="13" customHeight="1">
+    <row r="309" ht="12" customHeight="1">
       <c r="A309" s="4" t="n">
         <v>305</v>
       </c>
@@ -13752,7 +13824,7 @@
         </is>
       </c>
     </row>
-    <row r="310" ht="13" customHeight="1">
+    <row r="310" ht="12" customHeight="1">
       <c r="A310" s="4" t="n">
         <v>306</v>
       </c>
@@ -13795,7 +13867,7 @@
         </is>
       </c>
     </row>
-    <row r="311" ht="13" customHeight="1">
+    <row r="311" ht="12" customHeight="1">
       <c r="A311" s="4" t="n">
         <v>307</v>
       </c>
@@ -13838,7 +13910,7 @@
         </is>
       </c>
     </row>
-    <row r="312" ht="13" customHeight="1">
+    <row r="312" ht="12" customHeight="1">
       <c r="A312" s="4" t="n">
         <v>308</v>
       </c>
@@ -13881,7 +13953,7 @@
         </is>
       </c>
     </row>
-    <row r="313" ht="13" customHeight="1">
+    <row r="313" ht="12" customHeight="1">
       <c r="A313" s="4" t="n">
         <v>309</v>
       </c>
@@ -13924,7 +13996,7 @@
         </is>
       </c>
     </row>
-    <row r="314" ht="13" customHeight="1">
+    <row r="314" ht="12" customHeight="1">
       <c r="A314" s="4" t="n">
         <v>310</v>
       </c>
@@ -13967,7 +14039,7 @@
         </is>
       </c>
     </row>
-    <row r="315" ht="13" customHeight="1">
+    <row r="315" ht="12" customHeight="1">
       <c r="A315" s="4" t="n">
         <v>311</v>
       </c>
@@ -14010,7 +14082,7 @@
         </is>
       </c>
     </row>
-    <row r="316" ht="13" customHeight="1">
+    <row r="316" ht="12" customHeight="1">
       <c r="A316" s="4" t="n">
         <v>312</v>
       </c>
@@ -14053,7 +14125,7 @@
         </is>
       </c>
     </row>
-    <row r="317" ht="13" customHeight="1">
+    <row r="317" ht="12" customHeight="1">
       <c r="A317" s="4" t="n">
         <v>313</v>
       </c>
@@ -14096,7 +14168,7 @@
         </is>
       </c>
     </row>
-    <row r="318" ht="13" customHeight="1">
+    <row r="318" ht="12" customHeight="1">
       <c r="A318" s="4" t="n">
         <v>314</v>
       </c>
@@ -14139,7 +14211,7 @@
         </is>
       </c>
     </row>
-    <row r="319" ht="13" customHeight="1">
+    <row r="319" ht="12" customHeight="1">
       <c r="A319" s="4" t="n">
         <v>315</v>
       </c>
@@ -14182,7 +14254,7 @@
         </is>
       </c>
     </row>
-    <row r="320" ht="13" customHeight="1">
+    <row r="320" ht="12" customHeight="1">
       <c r="A320" s="4" t="n">
         <v>316</v>
       </c>
@@ -14225,7 +14297,7 @@
         </is>
       </c>
     </row>
-    <row r="321" ht="13" customHeight="1">
+    <row r="321" ht="12" customHeight="1">
       <c r="A321" s="4" t="n">
         <v>317</v>
       </c>
@@ -14272,6 +14344,543 @@
   <mergeCells count="2">
     <mergeCell ref="A2:K2"/>
     <mergeCell ref="A1:K1"/>
+  </mergeCells>
+  <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
+</worksheet>
+</file>
+
+<file path=xl/worksheets/sheet10.xml><?xml version="1.0" encoding="utf-8"?>
+<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
+  <sheetPr>
+    <outlinePr summaryBelow="1" summaryRight="1"/>
+    <pageSetUpPr/>
+  </sheetPr>
+  <dimension ref="A1:G17"/>
+  <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
+  <cols>
+    <col width="18" customWidth="1" min="1" max="1"/>
+    <col width="14" customWidth="1" min="2" max="2"/>
+    <col width="12" customWidth="1" min="3" max="3"/>
+    <col width="15" customWidth="1" min="4" max="4"/>
+    <col width="16" customWidth="1" min="5" max="5"/>
+    <col width="18" customWidth="1" min="6" max="6"/>
+    <col width="15" customWidth="1" min="7" max="7"/>
+  </cols>
+  <sheetData>
+    <row r="1" ht="24" customHeight="1">
+      <c r="A1" s="1" t="inlineStr">
+        <is>
+          <t>إهلاك السنة المالية 2033 — شهر بشهر</t>
+        </is>
+      </c>
+    </row>
+    <row r="2" ht="16" customHeight="1">
+      <c r="A2" s="18" t="inlineStr">
+        <is>
+          <t>القسط الشهري ثابت لكل أصل حتى نهاية عمره؛ يقلّ الإجمالي كلما اكتمل إهلاك أصل.</t>
+        </is>
+      </c>
+    </row>
+    <row r="4">
+      <c r="A4" s="19" t="inlineStr">
+        <is>
+          <t>الشهر
+Month</t>
+        </is>
+      </c>
+      <c r="B4" s="19" t="inlineStr">
+        <is>
+          <t>سيارات
+Vehicles</t>
+        </is>
+      </c>
+      <c r="C4" s="19" t="inlineStr">
+        <is>
+          <t>تقنية
+IT</t>
+        </is>
+      </c>
+      <c r="D4" s="19" t="inlineStr">
+        <is>
+          <t>آلات ومعدات
+Machinery</t>
+        </is>
+      </c>
+      <c r="E4" s="19" t="inlineStr">
+        <is>
+          <t>إجمالي الشهر
+Monthly total</t>
+        </is>
+      </c>
+      <c r="F4" s="19" t="inlineStr">
+        <is>
+          <t>مجمّع تراكمي (كلي)
+Cumulative (all)</t>
+        </is>
+      </c>
+      <c r="G4" s="19" t="inlineStr">
+        <is>
+          <t>صافي متبقّي
+Remaining NBV</t>
+        </is>
+      </c>
+    </row>
+    <row r="5" ht="15" customHeight="1">
+      <c r="A5" s="20" t="inlineStr">
+        <is>
+          <t>يناير 2033</t>
+        </is>
+      </c>
+      <c r="B5" s="21" t="n">
+        <v>0</v>
+      </c>
+      <c r="C5" s="21" t="n">
+        <v>0</v>
+      </c>
+      <c r="D5" s="21" t="n">
+        <v>539.58</v>
+      </c>
+      <c r="E5" s="22" t="n">
+        <v>539.58</v>
+      </c>
+      <c r="F5" s="21" t="n">
+        <v>387857.5</v>
+      </c>
+      <c r="G5" s="21" t="n">
+        <v>5675.25</v>
+      </c>
+    </row>
+    <row r="6" ht="15" customHeight="1">
+      <c r="A6" s="23" t="inlineStr">
+        <is>
+          <t>فبراير 2033</t>
+        </is>
+      </c>
+      <c r="B6" s="24" t="n">
+        <v>0</v>
+      </c>
+      <c r="C6" s="24" t="n">
+        <v>0</v>
+      </c>
+      <c r="D6" s="24" t="n">
+        <v>539.84</v>
+      </c>
+      <c r="E6" s="25" t="n">
+        <v>539.84</v>
+      </c>
+      <c r="F6" s="24" t="n">
+        <v>388397.34</v>
+      </c>
+      <c r="G6" s="24" t="n">
+        <v>5135.41</v>
+      </c>
+    </row>
+    <row r="7" ht="15" customHeight="1">
+      <c r="A7" s="20" t="inlineStr">
+        <is>
+          <t>مارس 2033</t>
+        </is>
+      </c>
+      <c r="B7" s="21" t="n">
+        <v>0</v>
+      </c>
+      <c r="C7" s="21" t="n">
+        <v>0</v>
+      </c>
+      <c r="D7" s="21" t="n">
+        <v>468.75</v>
+      </c>
+      <c r="E7" s="22" t="n">
+        <v>468.75</v>
+      </c>
+      <c r="F7" s="21" t="n">
+        <v>388866.09</v>
+      </c>
+      <c r="G7" s="21" t="n">
+        <v>4666.66</v>
+      </c>
+    </row>
+    <row r="8" ht="15" customHeight="1">
+      <c r="A8" s="23" t="inlineStr">
+        <is>
+          <t>أبريل 2033</t>
+        </is>
+      </c>
+      <c r="B8" s="24" t="n">
+        <v>0</v>
+      </c>
+      <c r="C8" s="24" t="n">
+        <v>0</v>
+      </c>
+      <c r="D8" s="24" t="n">
+        <v>468.75</v>
+      </c>
+      <c r="E8" s="25" t="n">
+        <v>468.75</v>
+      </c>
+      <c r="F8" s="24" t="n">
+        <v>389334.84</v>
+      </c>
+      <c r="G8" s="24" t="n">
+        <v>4197.91</v>
+      </c>
+    </row>
+    <row r="9" ht="15" customHeight="1">
+      <c r="A9" s="20" t="inlineStr">
+        <is>
+          <t>مايو 2033</t>
+        </is>
+      </c>
+      <c r="B9" s="21" t="n">
+        <v>0</v>
+      </c>
+      <c r="C9" s="21" t="n">
+        <v>0</v>
+      </c>
+      <c r="D9" s="21" t="n">
+        <v>468.75</v>
+      </c>
+      <c r="E9" s="22" t="n">
+        <v>468.75</v>
+      </c>
+      <c r="F9" s="21" t="n">
+        <v>389803.59</v>
+      </c>
+      <c r="G9" s="21" t="n">
+        <v>3729.16</v>
+      </c>
+    </row>
+    <row r="10" ht="15" customHeight="1">
+      <c r="A10" s="23" t="inlineStr">
+        <is>
+          <t>يونيو 2033</t>
+        </is>
+      </c>
+      <c r="B10" s="24" t="n">
+        <v>0</v>
+      </c>
+      <c r="C10" s="24" t="n">
+        <v>0</v>
+      </c>
+      <c r="D10" s="24" t="n">
+        <v>468.75</v>
+      </c>
+      <c r="E10" s="25" t="n">
+        <v>468.75</v>
+      </c>
+      <c r="F10" s="24" t="n">
+        <v>390272.34</v>
+      </c>
+      <c r="G10" s="24" t="n">
+        <v>3260.41</v>
+      </c>
+    </row>
+    <row r="11" ht="15" customHeight="1">
+      <c r="A11" s="20" t="inlineStr">
+        <is>
+          <t>يوليو 2033</t>
+        </is>
+      </c>
+      <c r="B11" s="21" t="n">
+        <v>0</v>
+      </c>
+      <c r="C11" s="21" t="n">
+        <v>0</v>
+      </c>
+      <c r="D11" s="21" t="n">
+        <v>468.75</v>
+      </c>
+      <c r="E11" s="22" t="n">
+        <v>468.75</v>
+      </c>
+      <c r="F11" s="21" t="n">
+        <v>390741.09</v>
+      </c>
+      <c r="G11" s="21" t="n">
+        <v>2791.66</v>
+      </c>
+    </row>
+    <row r="12" ht="15" customHeight="1">
+      <c r="A12" s="23" t="inlineStr">
+        <is>
+          <t>أغسطس 2033</t>
+        </is>
+      </c>
+      <c r="B12" s="24" t="n">
+        <v>0</v>
+      </c>
+      <c r="C12" s="24" t="n">
+        <v>0</v>
+      </c>
+      <c r="D12" s="24" t="n">
+        <v>468.75</v>
+      </c>
+      <c r="E12" s="25" t="n">
+        <v>468.75</v>
+      </c>
+      <c r="F12" s="24" t="n">
+        <v>391209.84</v>
+      </c>
+      <c r="G12" s="24" t="n">
+        <v>2322.91</v>
+      </c>
+    </row>
+    <row r="13" ht="15" customHeight="1">
+      <c r="A13" s="20" t="inlineStr">
+        <is>
+          <t>سبتمبر 2033</t>
+        </is>
+      </c>
+      <c r="B13" s="21" t="n">
+        <v>0</v>
+      </c>
+      <c r="C13" s="21" t="n">
+        <v>0</v>
+      </c>
+      <c r="D13" s="21" t="n">
+        <v>468.75</v>
+      </c>
+      <c r="E13" s="22" t="n">
+        <v>468.75</v>
+      </c>
+      <c r="F13" s="21" t="n">
+        <v>391678.59</v>
+      </c>
+      <c r="G13" s="21" t="n">
+        <v>1854.16</v>
+      </c>
+    </row>
+    <row r="14" ht="15" customHeight="1">
+      <c r="A14" s="23" t="inlineStr">
+        <is>
+          <t>أكتوبر 2033</t>
+        </is>
+      </c>
+      <c r="B14" s="24" t="n">
+        <v>0</v>
+      </c>
+      <c r="C14" s="24" t="n">
+        <v>0</v>
+      </c>
+      <c r="D14" s="24" t="n">
+        <v>468.75</v>
+      </c>
+      <c r="E14" s="25" t="n">
+        <v>468.75</v>
+      </c>
+      <c r="F14" s="24" t="n">
+        <v>392147.34</v>
+      </c>
+      <c r="G14" s="24" t="n">
+        <v>1385.41</v>
+      </c>
+    </row>
+    <row r="15" ht="15" customHeight="1">
+      <c r="A15" s="20" t="inlineStr">
+        <is>
+          <t>نوفمبر 2033</t>
+        </is>
+      </c>
+      <c r="B15" s="21" t="n">
+        <v>0</v>
+      </c>
+      <c r="C15" s="21" t="n">
+        <v>0</v>
+      </c>
+      <c r="D15" s="21" t="n">
+        <v>468.46</v>
+      </c>
+      <c r="E15" s="22" t="n">
+        <v>468.46</v>
+      </c>
+      <c r="F15" s="21" t="n">
+        <v>392615.8</v>
+      </c>
+      <c r="G15" s="21" t="n">
+        <v>916.95</v>
+      </c>
+    </row>
+    <row r="16" ht="15" customHeight="1">
+      <c r="A16" s="23" t="inlineStr">
+        <is>
+          <t>ديسمبر 2033</t>
+        </is>
+      </c>
+      <c r="B16" s="24" t="n">
+        <v>0</v>
+      </c>
+      <c r="C16" s="24" t="n">
+        <v>0</v>
+      </c>
+      <c r="D16" s="24" t="n">
+        <v>458.33</v>
+      </c>
+      <c r="E16" s="25" t="n">
+        <v>458.33</v>
+      </c>
+      <c r="F16" s="24" t="n">
+        <v>393074.13</v>
+      </c>
+      <c r="G16" s="24" t="n">
+        <v>458.62</v>
+      </c>
+    </row>
+    <row r="17" ht="18" customHeight="1">
+      <c r="A17" s="26" t="inlineStr">
+        <is>
+          <t>إجمالي سنة 2033</t>
+        </is>
+      </c>
+      <c r="B17" s="17" t="n">
+        <v>0</v>
+      </c>
+      <c r="C17" s="17" t="n">
+        <v>0</v>
+      </c>
+      <c r="D17" s="17" t="n">
+        <v>5756.21</v>
+      </c>
+      <c r="E17" s="17" t="n">
+        <v>5756.21</v>
+      </c>
+      <c r="F17" s="16" t="inlineStr"/>
+      <c r="G17" s="16" t="inlineStr"/>
+    </row>
+  </sheetData>
+  <mergeCells count="2">
+    <mergeCell ref="A2:G2"/>
+    <mergeCell ref="A1:G1"/>
+  </mergeCells>
+  <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
+</worksheet>
+</file>
+
+<file path=xl/worksheets/sheet11.xml><?xml version="1.0" encoding="utf-8"?>
+<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
+  <sheetPr>
+    <outlinePr summaryBelow="1" summaryRight="1"/>
+    <pageSetUpPr/>
+  </sheetPr>
+  <dimension ref="A1:G6"/>
+  <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
+  <cols>
+    <col width="18" customWidth="1" min="1" max="1"/>
+    <col width="14" customWidth="1" min="2" max="2"/>
+    <col width="12" customWidth="1" min="3" max="3"/>
+    <col width="15" customWidth="1" min="4" max="4"/>
+    <col width="16" customWidth="1" min="5" max="5"/>
+    <col width="18" customWidth="1" min="6" max="6"/>
+    <col width="15" customWidth="1" min="7" max="7"/>
+  </cols>
+  <sheetData>
+    <row r="1" ht="24" customHeight="1">
+      <c r="A1" s="1" t="inlineStr">
+        <is>
+          <t>إهلاك السنة المالية 2034 — شهر بشهر</t>
+        </is>
+      </c>
+    </row>
+    <row r="2" ht="16" customHeight="1">
+      <c r="A2" s="18" t="inlineStr">
+        <is>
+          <t>القسط الشهري ثابت لكل أصل حتى نهاية عمره؛ يقلّ الإجمالي كلما اكتمل إهلاك أصل.</t>
+        </is>
+      </c>
+    </row>
+    <row r="4">
+      <c r="A4" s="19" t="inlineStr">
+        <is>
+          <t>الشهر
+Month</t>
+        </is>
+      </c>
+      <c r="B4" s="19" t="inlineStr">
+        <is>
+          <t>سيارات
+Vehicles</t>
+        </is>
+      </c>
+      <c r="C4" s="19" t="inlineStr">
+        <is>
+          <t>تقنية
+IT</t>
+        </is>
+      </c>
+      <c r="D4" s="19" t="inlineStr">
+        <is>
+          <t>آلات ومعدات
+Machinery</t>
+        </is>
+      </c>
+      <c r="E4" s="19" t="inlineStr">
+        <is>
+          <t>إجمالي الشهر
+Monthly total</t>
+        </is>
+      </c>
+      <c r="F4" s="19" t="inlineStr">
+        <is>
+          <t>مجمّع تراكمي (كلي)
+Cumulative (all)</t>
+        </is>
+      </c>
+      <c r="G4" s="19" t="inlineStr">
+        <is>
+          <t>صافي متبقّي
+Remaining NBV</t>
+        </is>
+      </c>
+    </row>
+    <row r="5" ht="15" customHeight="1">
+      <c r="A5" s="20" t="inlineStr">
+        <is>
+          <t>يناير 2034</t>
+        </is>
+      </c>
+      <c r="B5" s="21" t="n">
+        <v>0</v>
+      </c>
+      <c r="C5" s="21" t="n">
+        <v>0</v>
+      </c>
+      <c r="D5" s="21" t="n">
+        <v>458.62</v>
+      </c>
+      <c r="E5" s="22" t="n">
+        <v>458.62</v>
+      </c>
+      <c r="F5" s="21" t="n">
+        <v>393532.75</v>
+      </c>
+      <c r="G5" s="21" t="n">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="6" ht="18" customHeight="1">
+      <c r="A6" s="26" t="inlineStr">
+        <is>
+          <t>إجمالي سنة 2034</t>
+        </is>
+      </c>
+      <c r="B6" s="17" t="n">
+        <v>0</v>
+      </c>
+      <c r="C6" s="17" t="n">
+        <v>0</v>
+      </c>
+      <c r="D6" s="17" t="n">
+        <v>458.62</v>
+      </c>
+      <c r="E6" s="17" t="n">
+        <v>458.62</v>
+      </c>
+      <c r="F6" s="16" t="inlineStr"/>
+      <c r="G6" s="16" t="inlineStr"/>
+    </row>
+  </sheetData>
+  <mergeCells count="2">
+    <mergeCell ref="A2:G2"/>
+    <mergeCell ref="A1:G1"/>
   </mergeCells>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
 </worksheet>
@@ -14283,2275 +14892,2840 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:G92"/>
+  <dimension ref="A1:E13"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="12" customWidth="1" min="1" max="1"/>
-    <col width="13" customWidth="1" min="2" max="2"/>
+    <col width="14" customWidth="1" min="2" max="2"/>
+    <col width="20" customWidth="1" min="3" max="3"/>
+    <col width="18" customWidth="1" min="4" max="4"/>
+    <col width="22" customWidth="1" min="5" max="5"/>
+  </cols>
+  <sheetData>
+    <row r="1" ht="22" customHeight="1">
+      <c r="A1" s="8" t="inlineStr">
+        <is>
+          <t>ملخّص الإهلاك حسب السنة المالية</t>
+        </is>
+      </c>
+    </row>
+    <row r="3">
+      <c r="A3" s="9" t="inlineStr">
+        <is>
+          <t>السنة
+Year</t>
+        </is>
+      </c>
+      <c r="B3" s="9" t="inlineStr">
+        <is>
+          <t>عدد الشهور
+Months</t>
+        </is>
+      </c>
+      <c r="C3" s="9" t="inlineStr">
+        <is>
+          <t>إهلاك السنة
+Year depreciation</t>
+        </is>
+      </c>
+      <c r="D3" s="9" t="inlineStr">
+        <is>
+          <t>مجمّع تراكمي
+Cumulative</t>
+        </is>
+      </c>
+      <c r="E3" s="9" t="inlineStr">
+        <is>
+          <t>صافي متبقّي آخر السنة
+Remaining NBV</t>
+        </is>
+      </c>
+    </row>
+    <row r="4">
+      <c r="A4" s="10" t="n">
+        <v>2026</v>
+      </c>
+      <c r="B4" s="11" t="n">
+        <v>3</v>
+      </c>
+      <c r="C4" s="12" t="n">
+        <v>40305.03</v>
+      </c>
+      <c r="D4" s="12" t="n">
+        <v>40305.03</v>
+      </c>
+      <c r="E4" s="12" t="n">
+        <v>353227.72</v>
+      </c>
+    </row>
+    <row r="5">
+      <c r="A5" s="13" t="n">
+        <v>2027</v>
+      </c>
+      <c r="B5" s="14" t="n">
+        <v>12</v>
+      </c>
+      <c r="C5" s="15" t="n">
+        <v>144357.3</v>
+      </c>
+      <c r="D5" s="15" t="n">
+        <v>184662.33</v>
+      </c>
+      <c r="E5" s="15" t="n">
+        <v>208870.42</v>
+      </c>
+    </row>
+    <row r="6">
+      <c r="A6" s="10" t="n">
+        <v>2028</v>
+      </c>
+      <c r="B6" s="11" t="n">
+        <v>12</v>
+      </c>
+      <c r="C6" s="12" t="n">
+        <v>121394.72</v>
+      </c>
+      <c r="D6" s="12" t="n">
+        <v>306057.05</v>
+      </c>
+      <c r="E6" s="12" t="n">
+        <v>87475.7</v>
+      </c>
+    </row>
+    <row r="7">
+      <c r="A7" s="13" t="n">
+        <v>2029</v>
+      </c>
+      <c r="B7" s="14" t="n">
+        <v>12</v>
+      </c>
+      <c r="C7" s="15" t="n">
+        <v>60520.29</v>
+      </c>
+      <c r="D7" s="15" t="n">
+        <v>366577.34</v>
+      </c>
+      <c r="E7" s="15" t="n">
+        <v>26955.41</v>
+      </c>
+    </row>
+    <row r="8">
+      <c r="A8" s="10" t="n">
+        <v>2030</v>
+      </c>
+      <c r="B8" s="11" t="n">
+        <v>12</v>
+      </c>
+      <c r="C8" s="12" t="n">
+        <v>7425</v>
+      </c>
+      <c r="D8" s="12" t="n">
+        <v>374002.34</v>
+      </c>
+      <c r="E8" s="12" t="n">
+        <v>19530.41</v>
+      </c>
+    </row>
+    <row r="9">
+      <c r="A9" s="13" t="n">
+        <v>2031</v>
+      </c>
+      <c r="B9" s="14" t="n">
+        <v>12</v>
+      </c>
+      <c r="C9" s="15" t="n">
+        <v>6840.62</v>
+      </c>
+      <c r="D9" s="15" t="n">
+        <v>380842.96</v>
+      </c>
+      <c r="E9" s="15" t="n">
+        <v>12689.79</v>
+      </c>
+    </row>
+    <row r="10">
+      <c r="A10" s="10" t="n">
+        <v>2032</v>
+      </c>
+      <c r="B10" s="11" t="n">
+        <v>12</v>
+      </c>
+      <c r="C10" s="12" t="n">
+        <v>6474.96</v>
+      </c>
+      <c r="D10" s="12" t="n">
+        <v>387317.92</v>
+      </c>
+      <c r="E10" s="12" t="n">
+        <v>6214.83</v>
+      </c>
+    </row>
+    <row r="11">
+      <c r="A11" s="13" t="n">
+        <v>2033</v>
+      </c>
+      <c r="B11" s="14" t="n">
+        <v>12</v>
+      </c>
+      <c r="C11" s="15" t="n">
+        <v>5756.21</v>
+      </c>
+      <c r="D11" s="15" t="n">
+        <v>393074.13</v>
+      </c>
+      <c r="E11" s="15" t="n">
+        <v>458.62</v>
+      </c>
+    </row>
+    <row r="12">
+      <c r="A12" s="10" t="n">
+        <v>2034</v>
+      </c>
+      <c r="B12" s="11" t="n">
+        <v>1</v>
+      </c>
+      <c r="C12" s="12" t="n">
+        <v>458.62</v>
+      </c>
+      <c r="D12" s="12" t="n">
+        <v>393532.75</v>
+      </c>
+      <c r="E12" s="12" t="n">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="13">
+      <c r="A13" s="16" t="inlineStr">
+        <is>
+          <t>الإجمالي</t>
+        </is>
+      </c>
+      <c r="B13" s="16" t="n">
+        <v>88</v>
+      </c>
+      <c r="C13" s="17" t="n">
+        <v>393532.75</v>
+      </c>
+      <c r="D13" s="16" t="inlineStr"/>
+      <c r="E13" s="17" t="n">
+        <v>0</v>
+      </c>
+    </row>
+  </sheetData>
+  <mergeCells count="1">
+    <mergeCell ref="A1:E1"/>
+  </mergeCells>
+  <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
+</worksheet>
+</file>
+
+<file path=xl/worksheets/sheet3.xml><?xml version="1.0" encoding="utf-8"?>
+<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
+  <sheetPr>
+    <outlinePr summaryBelow="1" summaryRight="1"/>
+    <pageSetUpPr/>
+  </sheetPr>
+  <dimension ref="A1:G8"/>
+  <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
+  <cols>
+    <col width="18" customWidth="1" min="1" max="1"/>
+    <col width="14" customWidth="1" min="2" max="2"/>
     <col width="12" customWidth="1" min="3" max="3"/>
-    <col width="14" customWidth="1" min="4" max="4"/>
-    <col width="15" customWidth="1" min="5" max="5"/>
-    <col width="15" customWidth="1" min="6" max="6"/>
+    <col width="15" customWidth="1" min="4" max="4"/>
+    <col width="16" customWidth="1" min="5" max="5"/>
+    <col width="18" customWidth="1" min="6" max="6"/>
     <col width="15" customWidth="1" min="7" max="7"/>
   </cols>
   <sheetData>
-    <row r="1" ht="26" customHeight="1">
+    <row r="1" ht="24" customHeight="1">
       <c r="A1" s="1" t="inlineStr">
         <is>
-          <t>الجدول الشهري القادم — إهلاك كل شهر حتى نهاية الأعمار</t>
+          <t>إهلاك السنة المالية 2026 — شهر بشهر</t>
         </is>
       </c>
     </row>
     <row r="2" ht="16" customHeight="1">
-      <c r="A2" s="2" t="inlineStr">
-        <is>
-          <t>Forward Monthly Depreciation Schedule — from Oct 2026 until fully depreciated (88 months)</t>
+      <c r="A2" s="18" t="inlineStr">
+        <is>
+          <t>ملاحظة: الأشهر يناير–سبتمبر 2026 مُثبتة ضمن الرصيد المُجمّع حتى 30/09/2026؛ هذا التاب يعرض الأشهر المتبقّية من السنة.</t>
         </is>
       </c>
     </row>
     <row r="4">
-      <c r="A4" s="8" t="inlineStr">
+      <c r="A4" s="19" t="inlineStr">
         <is>
           <t>الشهر
 Month</t>
         </is>
       </c>
-      <c r="B4" s="8" t="inlineStr">
+      <c r="B4" s="19" t="inlineStr">
         <is>
           <t>سيارات
 Vehicles</t>
         </is>
       </c>
-      <c r="C4" s="8" t="inlineStr">
+      <c r="C4" s="19" t="inlineStr">
         <is>
           <t>تقنية
 IT</t>
         </is>
       </c>
-      <c r="D4" s="8" t="inlineStr">
+      <c r="D4" s="19" t="inlineStr">
         <is>
           <t>آلات ومعدات
 Machinery</t>
         </is>
       </c>
-      <c r="E4" s="8" t="inlineStr">
+      <c r="E4" s="19" t="inlineStr">
         <is>
           <t>إجمالي الشهر
 Monthly total</t>
         </is>
       </c>
-      <c r="F4" s="8" t="inlineStr">
-        <is>
-          <t>مجمّع تراكمي
-Cumulative</t>
-        </is>
-      </c>
-      <c r="G4" s="8" t="inlineStr">
+      <c r="F4" s="19" t="inlineStr">
+        <is>
+          <t>مجمّع تراكمي (كلي)
+Cumulative (all)</t>
+        </is>
+      </c>
+      <c r="G4" s="19" t="inlineStr">
         <is>
           <t>صافي متبقّي
 Remaining NBV</t>
         </is>
       </c>
     </row>
-    <row r="5" ht="13" customHeight="1">
-      <c r="A5" s="9" t="inlineStr">
-        <is>
-          <t>2026-10</t>
-        </is>
-      </c>
-      <c r="B5" s="10" t="n">
+    <row r="5" ht="15" customHeight="1">
+      <c r="A5" s="20" t="inlineStr">
+        <is>
+          <t>أكتوبر 2026</t>
+        </is>
+      </c>
+      <c r="B5" s="21" t="n">
         <v>8076.69</v>
       </c>
-      <c r="C5" s="10" t="n">
+      <c r="C5" s="21" t="n">
         <v>2746.7</v>
       </c>
-      <c r="D5" s="10" t="n">
+      <c r="D5" s="21" t="n">
         <v>2812.56</v>
       </c>
-      <c r="E5" s="11" t="n">
+      <c r="E5" s="22" t="n">
         <v>13635.95</v>
       </c>
-      <c r="F5" s="10" t="n">
+      <c r="F5" s="21" t="n">
         <v>13635.95</v>
       </c>
-      <c r="G5" s="10" t="n">
+      <c r="G5" s="21" t="n">
         <v>379896.8</v>
       </c>
     </row>
-    <row r="6" ht="13" customHeight="1">
-      <c r="A6" s="12" t="inlineStr">
-        <is>
-          <t>2026-11</t>
-        </is>
-      </c>
-      <c r="B6" s="13" t="n">
+    <row r="6" ht="15" customHeight="1">
+      <c r="A6" s="23" t="inlineStr">
+        <is>
+          <t>نوفمبر 2026</t>
+        </is>
+      </c>
+      <c r="B6" s="24" t="n">
         <v>8076.69</v>
       </c>
-      <c r="C6" s="13" t="n">
+      <c r="C6" s="24" t="n">
         <v>2695.32</v>
       </c>
-      <c r="D6" s="13" t="n">
+      <c r="D6" s="24" t="n">
         <v>2637.58</v>
       </c>
-      <c r="E6" s="14" t="n">
+      <c r="E6" s="25" t="n">
         <v>13409.59</v>
       </c>
-      <c r="F6" s="13" t="n">
+      <c r="F6" s="24" t="n">
         <v>27045.54</v>
       </c>
-      <c r="G6" s="13" t="n">
+      <c r="G6" s="24" t="n">
         <v>366487.21</v>
       </c>
     </row>
-    <row r="7" ht="13" customHeight="1">
-      <c r="A7" s="9" t="inlineStr">
-        <is>
-          <t>2026-12</t>
-        </is>
-      </c>
-      <c r="B7" s="10" t="n">
+    <row r="7" ht="15" customHeight="1">
+      <c r="A7" s="20" t="inlineStr">
+        <is>
+          <t>ديسمبر 2026</t>
+        </is>
+      </c>
+      <c r="B7" s="21" t="n">
         <v>8076.71</v>
       </c>
-      <c r="C7" s="10" t="n">
+      <c r="C7" s="21" t="n">
         <v>2675.9</v>
       </c>
-      <c r="D7" s="10" t="n">
+      <c r="D7" s="21" t="n">
         <v>2506.88</v>
       </c>
-      <c r="E7" s="11" t="n">
+      <c r="E7" s="22" t="n">
         <v>13259.49</v>
       </c>
-      <c r="F7" s="10" t="n">
+      <c r="F7" s="21" t="n">
         <v>40305.03</v>
       </c>
-      <c r="G7" s="10" t="n">
+      <c r="G7" s="21" t="n">
         <v>353227.72</v>
       </c>
     </row>
-    <row r="8" ht="13" customHeight="1">
-      <c r="A8" s="12" t="inlineStr">
-        <is>
-          <t>2027-01</t>
-        </is>
-      </c>
-      <c r="B8" s="13" t="n">
+    <row r="8" ht="18" customHeight="1">
+      <c r="A8" s="26" t="inlineStr">
+        <is>
+          <t>إجمالي سنة 2026</t>
+        </is>
+      </c>
+      <c r="B8" s="17" t="n">
+        <v>24230.09</v>
+      </c>
+      <c r="C8" s="17" t="n">
+        <v>8117.92</v>
+      </c>
+      <c r="D8" s="17" t="n">
+        <v>7957.02</v>
+      </c>
+      <c r="E8" s="17" t="n">
+        <v>40305.03</v>
+      </c>
+      <c r="F8" s="16" t="inlineStr"/>
+      <c r="G8" s="16" t="inlineStr"/>
+    </row>
+  </sheetData>
+  <mergeCells count="2">
+    <mergeCell ref="A2:G2"/>
+    <mergeCell ref="A1:G1"/>
+  </mergeCells>
+  <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
+</worksheet>
+</file>
+
+<file path=xl/worksheets/sheet4.xml><?xml version="1.0" encoding="utf-8"?>
+<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
+  <sheetPr>
+    <outlinePr summaryBelow="1" summaryRight="1"/>
+    <pageSetUpPr/>
+  </sheetPr>
+  <dimension ref="A1:G17"/>
+  <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
+  <cols>
+    <col width="18" customWidth="1" min="1" max="1"/>
+    <col width="14" customWidth="1" min="2" max="2"/>
+    <col width="12" customWidth="1" min="3" max="3"/>
+    <col width="15" customWidth="1" min="4" max="4"/>
+    <col width="16" customWidth="1" min="5" max="5"/>
+    <col width="18" customWidth="1" min="6" max="6"/>
+    <col width="15" customWidth="1" min="7" max="7"/>
+  </cols>
+  <sheetData>
+    <row r="1" ht="24" customHeight="1">
+      <c r="A1" s="1" t="inlineStr">
+        <is>
+          <t>إهلاك السنة المالية 2027 — شهر بشهر</t>
+        </is>
+      </c>
+    </row>
+    <row r="2" ht="16" customHeight="1">
+      <c r="A2" s="18" t="inlineStr">
+        <is>
+          <t>القسط الشهري ثابت لكل أصل حتى نهاية عمره؛ يقلّ الإجمالي كلما اكتمل إهلاك أصل.</t>
+        </is>
+      </c>
+    </row>
+    <row r="4">
+      <c r="A4" s="19" t="inlineStr">
+        <is>
+          <t>الشهر
+Month</t>
+        </is>
+      </c>
+      <c r="B4" s="19" t="inlineStr">
+        <is>
+          <t>سيارات
+Vehicles</t>
+        </is>
+      </c>
+      <c r="C4" s="19" t="inlineStr">
+        <is>
+          <t>تقنية
+IT</t>
+        </is>
+      </c>
+      <c r="D4" s="19" t="inlineStr">
+        <is>
+          <t>آلات ومعدات
+Machinery</t>
+        </is>
+      </c>
+      <c r="E4" s="19" t="inlineStr">
+        <is>
+          <t>إجمالي الشهر
+Monthly total</t>
+        </is>
+      </c>
+      <c r="F4" s="19" t="inlineStr">
+        <is>
+          <t>مجمّع تراكمي (كلي)
+Cumulative (all)</t>
+        </is>
+      </c>
+      <c r="G4" s="19" t="inlineStr">
+        <is>
+          <t>صافي متبقّي
+Remaining NBV</t>
+        </is>
+      </c>
+    </row>
+    <row r="5" ht="15" customHeight="1">
+      <c r="A5" s="20" t="inlineStr">
+        <is>
+          <t>يناير 2027</t>
+        </is>
+      </c>
+      <c r="B5" s="21" t="n">
         <v>7870.03</v>
       </c>
-      <c r="C8" s="13" t="n">
+      <c r="C5" s="21" t="n">
         <v>2633.76</v>
       </c>
-      <c r="D8" s="13" t="n">
+      <c r="D5" s="21" t="n">
         <v>2497.06</v>
       </c>
-      <c r="E8" s="14" t="n">
+      <c r="E5" s="22" t="n">
         <v>13000.85</v>
       </c>
-      <c r="F8" s="13" t="n">
+      <c r="F5" s="21" t="n">
         <v>53305.88</v>
       </c>
-      <c r="G8" s="13" t="n">
+      <c r="G5" s="21" t="n">
         <v>340226.87</v>
       </c>
     </row>
-    <row r="9" ht="13" customHeight="1">
-      <c r="A9" s="9" t="inlineStr">
-        <is>
-          <t>2027-02</t>
-        </is>
-      </c>
-      <c r="B9" s="10" t="n">
+    <row r="6" ht="15" customHeight="1">
+      <c r="A6" s="23" t="inlineStr">
+        <is>
+          <t>فبراير 2027</t>
+        </is>
+      </c>
+      <c r="B6" s="24" t="n">
         <v>7870.01</v>
       </c>
-      <c r="C9" s="10" t="n">
+      <c r="C6" s="24" t="n">
         <v>2604.6</v>
       </c>
-      <c r="D9" s="10" t="n">
+      <c r="D6" s="24" t="n">
         <v>2497.06</v>
       </c>
-      <c r="E9" s="11" t="n">
+      <c r="E6" s="25" t="n">
         <v>12971.67</v>
       </c>
-      <c r="F9" s="10" t="n">
+      <c r="F6" s="24" t="n">
         <v>66277.55</v>
       </c>
-      <c r="G9" s="10" t="n">
+      <c r="G6" s="24" t="n">
         <v>327255.2</v>
       </c>
     </row>
-    <row r="10" ht="13" customHeight="1">
-      <c r="A10" s="12" t="inlineStr">
-        <is>
-          <t>2027-03</t>
-        </is>
-      </c>
-      <c r="B10" s="13" t="n">
+    <row r="7" ht="15" customHeight="1">
+      <c r="A7" s="20" t="inlineStr">
+        <is>
+          <t>مارس 2027</t>
+        </is>
+      </c>
+      <c r="B7" s="21" t="n">
         <v>7728.34</v>
       </c>
-      <c r="C10" s="13" t="n">
+      <c r="C7" s="21" t="n">
         <v>2443.43</v>
       </c>
-      <c r="D10" s="13" t="n">
+      <c r="D7" s="21" t="n">
         <v>2497.08</v>
       </c>
-      <c r="E10" s="14" t="n">
+      <c r="E7" s="22" t="n">
         <v>12668.85</v>
       </c>
-      <c r="F10" s="13" t="n">
+      <c r="F7" s="21" t="n">
         <v>78946.39999999999</v>
       </c>
-      <c r="G10" s="13" t="n">
+      <c r="G7" s="21" t="n">
         <v>314586.35</v>
       </c>
     </row>
-    <row r="11" ht="13" customHeight="1">
-      <c r="A11" s="9" t="inlineStr">
-        <is>
-          <t>2027-04</t>
-        </is>
-      </c>
-      <c r="B11" s="10" t="n">
+    <row r="8" ht="15" customHeight="1">
+      <c r="A8" s="23" t="inlineStr">
+        <is>
+          <t>أبريل 2027</t>
+        </is>
+      </c>
+      <c r="B8" s="24" t="n">
         <v>7661.69</v>
       </c>
-      <c r="C11" s="10" t="n">
+      <c r="C8" s="24" t="n">
         <v>2124.68</v>
       </c>
-      <c r="D11" s="10" t="n">
+      <c r="D8" s="24" t="n">
         <v>2488.73</v>
       </c>
-      <c r="E11" s="11" t="n">
+      <c r="E8" s="25" t="n">
         <v>12275.1</v>
       </c>
-      <c r="F11" s="10" t="n">
+      <c r="F8" s="24" t="n">
         <v>91221.5</v>
       </c>
-      <c r="G11" s="10" t="n">
+      <c r="G8" s="24" t="n">
         <v>302311.25</v>
       </c>
     </row>
-    <row r="12" ht="13" customHeight="1">
-      <c r="A12" s="12" t="inlineStr">
-        <is>
-          <t>2027-05</t>
-        </is>
-      </c>
-      <c r="B12" s="13" t="n">
+    <row r="9" ht="15" customHeight="1">
+      <c r="A9" s="20" t="inlineStr">
+        <is>
+          <t>مايو 2027</t>
+        </is>
+      </c>
+      <c r="B9" s="21" t="n">
         <v>7661.69</v>
       </c>
-      <c r="C12" s="13" t="n">
+      <c r="C9" s="21" t="n">
         <v>2007.98</v>
       </c>
-      <c r="D12" s="13" t="n">
+      <c r="D9" s="21" t="n">
         <v>2348.73</v>
       </c>
-      <c r="E12" s="14" t="n">
+      <c r="E9" s="22" t="n">
         <v>12018.4</v>
       </c>
-      <c r="F12" s="13" t="n">
+      <c r="F9" s="21" t="n">
         <v>103239.9</v>
       </c>
-      <c r="G12" s="13" t="n">
+      <c r="G9" s="21" t="n">
         <v>290292.85</v>
       </c>
     </row>
-    <row r="13" ht="13" customHeight="1">
-      <c r="A13" s="9" t="inlineStr">
-        <is>
-          <t>2027-06</t>
-        </is>
-      </c>
-      <c r="B13" s="10" t="n">
+    <row r="10" ht="15" customHeight="1">
+      <c r="A10" s="23" t="inlineStr">
+        <is>
+          <t>يونيو 2027</t>
+        </is>
+      </c>
+      <c r="B10" s="24" t="n">
         <v>7661.69</v>
       </c>
-      <c r="C13" s="10" t="n">
+      <c r="C10" s="24" t="n">
         <v>1898.26</v>
       </c>
-      <c r="D13" s="10" t="n">
+      <c r="D10" s="24" t="n">
         <v>2348.73</v>
       </c>
-      <c r="E13" s="11" t="n">
+      <c r="E10" s="25" t="n">
         <v>11908.68</v>
       </c>
-      <c r="F13" s="10" t="n">
+      <c r="F10" s="24" t="n">
         <v>115148.58</v>
       </c>
-      <c r="G13" s="10" t="n">
+      <c r="G10" s="24" t="n">
         <v>278384.17</v>
       </c>
     </row>
-    <row r="14" ht="13" customHeight="1">
-      <c r="A14" s="12" t="inlineStr">
-        <is>
-          <t>2027-07</t>
-        </is>
-      </c>
-      <c r="B14" s="13" t="n">
+    <row r="11" ht="15" customHeight="1">
+      <c r="A11" s="20" t="inlineStr">
+        <is>
+          <t>يوليو 2027</t>
+        </is>
+      </c>
+      <c r="B11" s="21" t="n">
         <v>7661.69</v>
       </c>
-      <c r="C14" s="13" t="n">
+      <c r="C11" s="21" t="n">
         <v>1833.27</v>
       </c>
-      <c r="D14" s="13" t="n">
+      <c r="D11" s="21" t="n">
         <v>2348.73</v>
       </c>
-      <c r="E14" s="14" t="n">
+      <c r="E11" s="22" t="n">
         <v>11843.69</v>
       </c>
-      <c r="F14" s="13" t="n">
+      <c r="F11" s="21" t="n">
         <v>126992.27</v>
       </c>
-      <c r="G14" s="13" t="n">
+      <c r="G11" s="21" t="n">
         <v>266540.48</v>
       </c>
     </row>
-    <row r="15" ht="13" customHeight="1">
-      <c r="A15" s="9" t="inlineStr">
-        <is>
-          <t>2027-08</t>
-        </is>
-      </c>
-      <c r="B15" s="10" t="n">
+    <row r="12" ht="15" customHeight="1">
+      <c r="A12" s="23" t="inlineStr">
+        <is>
+          <t>أغسطس 2027</t>
+        </is>
+      </c>
+      <c r="B12" s="24" t="n">
         <v>7661.69</v>
       </c>
-      <c r="C15" s="10" t="n">
+      <c r="C12" s="24" t="n">
         <v>1833.32</v>
       </c>
-      <c r="D15" s="10" t="n">
+      <c r="D12" s="24" t="n">
         <v>2348.73</v>
       </c>
-      <c r="E15" s="11" t="n">
+      <c r="E12" s="25" t="n">
         <v>11843.74</v>
       </c>
-      <c r="F15" s="10" t="n">
+      <c r="F12" s="24" t="n">
         <v>138836.01</v>
       </c>
-      <c r="G15" s="10" t="n">
+      <c r="G12" s="24" t="n">
         <v>254696.74</v>
       </c>
     </row>
-    <row r="16" ht="13" customHeight="1">
-      <c r="A16" s="12" t="inlineStr">
-        <is>
-          <t>2027-09</t>
-        </is>
-      </c>
-      <c r="B16" s="13" t="n">
+    <row r="13" ht="15" customHeight="1">
+      <c r="A13" s="20" t="inlineStr">
+        <is>
+          <t>سبتمبر 2027</t>
+        </is>
+      </c>
+      <c r="B13" s="21" t="n">
         <v>7661.69</v>
       </c>
-      <c r="C16" s="13" t="n">
+      <c r="C13" s="21" t="n">
         <v>1562.16</v>
       </c>
-      <c r="D16" s="13" t="n">
+      <c r="D13" s="21" t="n">
         <v>2336.73</v>
       </c>
-      <c r="E16" s="14" t="n">
+      <c r="E13" s="22" t="n">
         <v>11560.58</v>
       </c>
-      <c r="F16" s="13" t="n">
+      <c r="F13" s="21" t="n">
         <v>150396.59</v>
       </c>
-      <c r="G16" s="13" t="n">
+      <c r="G13" s="21" t="n">
         <v>243136.16</v>
       </c>
     </row>
-    <row r="17" ht="13" customHeight="1">
-      <c r="A17" s="9" t="inlineStr">
-        <is>
-          <t>2027-10</t>
-        </is>
-      </c>
-      <c r="B17" s="10" t="n">
+    <row r="14" ht="15" customHeight="1">
+      <c r="A14" s="23" t="inlineStr">
+        <is>
+          <t>أكتوبر 2027</t>
+        </is>
+      </c>
+      <c r="B14" s="24" t="n">
         <v>7661.69</v>
       </c>
-      <c r="C17" s="10" t="n">
+      <c r="C14" s="24" t="n">
         <v>1467.88</v>
       </c>
-      <c r="D17" s="10" t="n">
+      <c r="D14" s="24" t="n">
         <v>2336.73</v>
       </c>
-      <c r="E17" s="11" t="n">
+      <c r="E14" s="25" t="n">
         <v>11466.3</v>
       </c>
-      <c r="F17" s="10" t="n">
+      <c r="F14" s="24" t="n">
         <v>161862.89</v>
       </c>
-      <c r="G17" s="10" t="n">
+      <c r="G14" s="24" t="n">
         <v>231669.86</v>
       </c>
     </row>
-    <row r="18" ht="13" customHeight="1">
-      <c r="A18" s="12" t="inlineStr">
-        <is>
-          <t>2027-11</t>
-        </is>
-      </c>
-      <c r="B18" s="13" t="n">
+    <row r="15" ht="15" customHeight="1">
+      <c r="A15" s="20" t="inlineStr">
+        <is>
+          <t>نوفمبر 2027</t>
+        </is>
+      </c>
+      <c r="B15" s="21" t="n">
         <v>7661.69</v>
       </c>
-      <c r="C18" s="13" t="n">
+      <c r="C15" s="21" t="n">
         <v>1401.25</v>
       </c>
-      <c r="D18" s="13" t="n">
+      <c r="D15" s="21" t="n">
         <v>2336.73</v>
       </c>
-      <c r="E18" s="14" t="n">
+      <c r="E15" s="22" t="n">
         <v>11399.67</v>
       </c>
-      <c r="F18" s="13" t="n">
+      <c r="F15" s="21" t="n">
         <v>173262.56</v>
       </c>
-      <c r="G18" s="13" t="n">
+      <c r="G15" s="21" t="n">
         <v>220270.19</v>
       </c>
     </row>
-    <row r="19" ht="13" customHeight="1">
-      <c r="A19" s="9" t="inlineStr">
-        <is>
-          <t>2027-12</t>
-        </is>
-      </c>
-      <c r="B19" s="10" t="n">
+    <row r="16" ht="15" customHeight="1">
+      <c r="A16" s="23" t="inlineStr">
+        <is>
+          <t>ديسمبر 2027</t>
+        </is>
+      </c>
+      <c r="B16" s="24" t="n">
         <v>7661.74</v>
       </c>
-      <c r="C19" s="10" t="n">
+      <c r="C16" s="24" t="n">
         <v>1401.25</v>
       </c>
-      <c r="D19" s="10" t="n">
+      <c r="D16" s="24" t="n">
         <v>2336.78</v>
       </c>
-      <c r="E19" s="11" t="n">
+      <c r="E16" s="25" t="n">
         <v>11399.77</v>
       </c>
-      <c r="F19" s="10" t="n">
+      <c r="F16" s="24" t="n">
         <v>184662.33</v>
       </c>
-      <c r="G19" s="10" t="n">
+      <c r="G16" s="24" t="n">
         <v>208870.42</v>
       </c>
     </row>
-    <row r="20" ht="13" customHeight="1">
-      <c r="A20" s="12" t="inlineStr">
-        <is>
-          <t>2028-01</t>
-        </is>
-      </c>
-      <c r="B20" s="13" t="n">
+    <row r="17" ht="18" customHeight="1">
+      <c r="A17" s="26" t="inlineStr">
+        <is>
+          <t>إجمالي سنة 2027</t>
+        </is>
+      </c>
+      <c r="B17" s="17" t="n">
+        <v>92423.64</v>
+      </c>
+      <c r="C17" s="17" t="n">
+        <v>23211.84</v>
+      </c>
+      <c r="D17" s="17" t="n">
+        <v>28721.82</v>
+      </c>
+      <c r="E17" s="17" t="n">
+        <v>144357.3</v>
+      </c>
+      <c r="F17" s="16" t="inlineStr"/>
+      <c r="G17" s="16" t="inlineStr"/>
+    </row>
+  </sheetData>
+  <mergeCells count="2">
+    <mergeCell ref="A2:G2"/>
+    <mergeCell ref="A1:G1"/>
+  </mergeCells>
+  <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
+</worksheet>
+</file>
+
+<file path=xl/worksheets/sheet5.xml><?xml version="1.0" encoding="utf-8"?>
+<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
+  <sheetPr>
+    <outlinePr summaryBelow="1" summaryRight="1"/>
+    <pageSetUpPr/>
+  </sheetPr>
+  <dimension ref="A1:G17"/>
+  <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
+  <cols>
+    <col width="18" customWidth="1" min="1" max="1"/>
+    <col width="14" customWidth="1" min="2" max="2"/>
+    <col width="12" customWidth="1" min="3" max="3"/>
+    <col width="15" customWidth="1" min="4" max="4"/>
+    <col width="16" customWidth="1" min="5" max="5"/>
+    <col width="18" customWidth="1" min="6" max="6"/>
+    <col width="15" customWidth="1" min="7" max="7"/>
+  </cols>
+  <sheetData>
+    <row r="1" ht="24" customHeight="1">
+      <c r="A1" s="1" t="inlineStr">
+        <is>
+          <t>إهلاك السنة المالية 2028 — شهر بشهر</t>
+        </is>
+      </c>
+    </row>
+    <row r="2" ht="16" customHeight="1">
+      <c r="A2" s="18" t="inlineStr">
+        <is>
+          <t>القسط الشهري ثابت لكل أصل حتى نهاية عمره؛ يقلّ الإجمالي كلما اكتمل إهلاك أصل.</t>
+        </is>
+      </c>
+    </row>
+    <row r="4">
+      <c r="A4" s="19" t="inlineStr">
+        <is>
+          <t>الشهر
+Month</t>
+        </is>
+      </c>
+      <c r="B4" s="19" t="inlineStr">
+        <is>
+          <t>سيارات
+Vehicles</t>
+        </is>
+      </c>
+      <c r="C4" s="19" t="inlineStr">
+        <is>
+          <t>تقنية
+IT</t>
+        </is>
+      </c>
+      <c r="D4" s="19" t="inlineStr">
+        <is>
+          <t>آلات ومعدات
+Machinery</t>
+        </is>
+      </c>
+      <c r="E4" s="19" t="inlineStr">
+        <is>
+          <t>إجمالي الشهر
+Monthly total</t>
+        </is>
+      </c>
+      <c r="F4" s="19" t="inlineStr">
+        <is>
+          <t>مجمّع تراكمي (كلي)
+Cumulative (all)</t>
+        </is>
+      </c>
+      <c r="G4" s="19" t="inlineStr">
+        <is>
+          <t>صافي متبقّي
+Remaining NBV</t>
+        </is>
+      </c>
+    </row>
+    <row r="5" ht="15" customHeight="1">
+      <c r="A5" s="20" t="inlineStr">
+        <is>
+          <t>يناير 2028</t>
+        </is>
+      </c>
+      <c r="B5" s="21" t="n">
         <v>6958.36</v>
       </c>
-      <c r="C20" s="13" t="n">
+      <c r="C5" s="21" t="n">
         <v>1401.25</v>
       </c>
-      <c r="D20" s="13" t="n">
+      <c r="D5" s="21" t="n">
         <v>2318.35</v>
       </c>
-      <c r="E20" s="14" t="n">
+      <c r="E5" s="22" t="n">
         <v>10677.96</v>
       </c>
-      <c r="F20" s="13" t="n">
+      <c r="F5" s="21" t="n">
         <v>195340.29</v>
       </c>
-      <c r="G20" s="13" t="n">
+      <c r="G5" s="21" t="n">
         <v>198192.46</v>
       </c>
     </row>
-    <row r="21" ht="13" customHeight="1">
-      <c r="A21" s="9" t="inlineStr">
-        <is>
-          <t>2028-02</t>
-        </is>
-      </c>
-      <c r="B21" s="10" t="n">
+    <row r="6" ht="15" customHeight="1">
+      <c r="A6" s="23" t="inlineStr">
+        <is>
+          <t>فبراير 2028</t>
+        </is>
+      </c>
+      <c r="B6" s="24" t="n">
         <v>6958.36</v>
       </c>
-      <c r="C21" s="10" t="n">
+      <c r="C6" s="24" t="n">
         <v>1401.25</v>
       </c>
-      <c r="D21" s="10" t="n">
+      <c r="D6" s="24" t="n">
         <v>2234.23</v>
       </c>
-      <c r="E21" s="11" t="n">
+      <c r="E6" s="25" t="n">
         <v>10593.84</v>
       </c>
-      <c r="F21" s="10" t="n">
+      <c r="F6" s="24" t="n">
         <v>205934.13</v>
       </c>
-      <c r="G21" s="10" t="n">
+      <c r="G6" s="24" t="n">
         <v>187598.62</v>
       </c>
     </row>
-    <row r="22" ht="13" customHeight="1">
-      <c r="A22" s="12" t="inlineStr">
-        <is>
-          <t>2028-03</t>
-        </is>
-      </c>
-      <c r="B22" s="13" t="n">
+    <row r="7" ht="15" customHeight="1">
+      <c r="A7" s="20" t="inlineStr">
+        <is>
+          <t>مارس 2028</t>
+        </is>
+      </c>
+      <c r="B7" s="21" t="n">
         <v>6958.36</v>
       </c>
-      <c r="C22" s="13" t="n">
+      <c r="C7" s="21" t="n">
         <v>1401.25</v>
       </c>
-      <c r="D22" s="13" t="n">
+      <c r="D7" s="21" t="n">
         <v>2171.73</v>
       </c>
-      <c r="E22" s="14" t="n">
+      <c r="E7" s="22" t="n">
         <v>10531.34</v>
       </c>
-      <c r="F22" s="13" t="n">
+      <c r="F7" s="21" t="n">
         <v>216465.47</v>
       </c>
-      <c r="G22" s="13" t="n">
+      <c r="G7" s="21" t="n">
         <v>177067.28</v>
       </c>
     </row>
-    <row r="23" ht="13" customHeight="1">
-      <c r="A23" s="9" t="inlineStr">
-        <is>
-          <t>2028-04</t>
-        </is>
-      </c>
-      <c r="B23" s="10" t="n">
+    <row r="8" ht="15" customHeight="1">
+      <c r="A8" s="23" t="inlineStr">
+        <is>
+          <t>أبريل 2028</t>
+        </is>
+      </c>
+      <c r="B8" s="24" t="n">
         <v>6958.36</v>
       </c>
-      <c r="C23" s="10" t="n">
+      <c r="C8" s="24" t="n">
         <v>1401.25</v>
       </c>
-      <c r="D23" s="10" t="n">
+      <c r="D8" s="24" t="n">
         <v>2171.73</v>
       </c>
-      <c r="E23" s="11" t="n">
+      <c r="E8" s="25" t="n">
         <v>10531.34</v>
       </c>
-      <c r="F23" s="10" t="n">
+      <c r="F8" s="24" t="n">
         <v>226996.81</v>
       </c>
-      <c r="G23" s="10" t="n">
+      <c r="G8" s="24" t="n">
         <v>166535.94</v>
       </c>
     </row>
-    <row r="24" ht="13" customHeight="1">
-      <c r="A24" s="12" t="inlineStr">
-        <is>
-          <t>2028-05</t>
-        </is>
-      </c>
-      <c r="B24" s="13" t="n">
+    <row r="9" ht="15" customHeight="1">
+      <c r="A9" s="20" t="inlineStr">
+        <is>
+          <t>مايو 2028</t>
+        </is>
+      </c>
+      <c r="B9" s="21" t="n">
         <v>6958.29</v>
       </c>
-      <c r="C24" s="13" t="n">
+      <c r="C9" s="21" t="n">
         <v>1401.25</v>
       </c>
-      <c r="D24" s="13" t="n">
+      <c r="D9" s="21" t="n">
         <v>2171.73</v>
       </c>
-      <c r="E24" s="14" t="n">
+      <c r="E9" s="22" t="n">
         <v>10531.27</v>
       </c>
-      <c r="F24" s="13" t="n">
+      <c r="F9" s="21" t="n">
         <v>237528.08</v>
       </c>
-      <c r="G24" s="13" t="n">
+      <c r="G9" s="21" t="n">
         <v>156004.67</v>
       </c>
     </row>
-    <row r="25" ht="13" customHeight="1">
-      <c r="A25" s="9" t="inlineStr">
-        <is>
-          <t>2028-06</t>
-        </is>
-      </c>
-      <c r="B25" s="10" t="n">
+    <row r="10" ht="15" customHeight="1">
+      <c r="A10" s="23" t="inlineStr">
+        <is>
+          <t>يونيو 2028</t>
+        </is>
+      </c>
+      <c r="B10" s="24" t="n">
         <v>6851.69</v>
       </c>
-      <c r="C25" s="10" t="n">
+      <c r="C10" s="24" t="n">
         <v>1401.25</v>
       </c>
-      <c r="D25" s="10" t="n">
+      <c r="D10" s="24" t="n">
         <v>2171.73</v>
       </c>
-      <c r="E25" s="11" t="n">
+      <c r="E10" s="25" t="n">
         <v>10424.67</v>
       </c>
-      <c r="F25" s="10" t="n">
+      <c r="F10" s="24" t="n">
         <v>247952.75</v>
       </c>
-      <c r="G25" s="10" t="n">
+      <c r="G10" s="24" t="n">
         <v>145580</v>
       </c>
     </row>
-    <row r="26" ht="13" customHeight="1">
-      <c r="A26" s="12" t="inlineStr">
-        <is>
-          <t>2028-07</t>
-        </is>
-      </c>
-      <c r="B26" s="13" t="n">
+    <row r="11" ht="15" customHeight="1">
+      <c r="A11" s="20" t="inlineStr">
+        <is>
+          <t>يوليو 2028</t>
+        </is>
+      </c>
+      <c r="B11" s="21" t="n">
         <v>6851.69</v>
       </c>
-      <c r="C26" s="13" t="n">
+      <c r="C11" s="21" t="n">
         <v>1401.25</v>
       </c>
-      <c r="D26" s="13" t="n">
+      <c r="D11" s="21" t="n">
         <v>2171.73</v>
       </c>
-      <c r="E26" s="14" t="n">
+      <c r="E11" s="22" t="n">
         <v>10424.67</v>
       </c>
-      <c r="F26" s="13" t="n">
+      <c r="F11" s="21" t="n">
         <v>258377.42</v>
       </c>
-      <c r="G26" s="13" t="n">
+      <c r="G11" s="21" t="n">
         <v>135155.33</v>
       </c>
     </row>
-    <row r="27" ht="13" customHeight="1">
-      <c r="A27" s="9" t="inlineStr">
-        <is>
-          <t>2028-08</t>
-        </is>
-      </c>
-      <c r="B27" s="10" t="n">
+    <row r="12" ht="15" customHeight="1">
+      <c r="A12" s="23" t="inlineStr">
+        <is>
+          <t>أغسطس 2028</t>
+        </is>
+      </c>
+      <c r="B12" s="24" t="n">
         <v>6851.69</v>
       </c>
-      <c r="C27" s="10" t="n">
+      <c r="C12" s="24" t="n">
         <v>1401.17</v>
       </c>
-      <c r="D27" s="10" t="n">
+      <c r="D12" s="24" t="n">
         <v>1925.28</v>
       </c>
-      <c r="E27" s="11" t="n">
+      <c r="E12" s="25" t="n">
         <v>10178.14</v>
       </c>
-      <c r="F27" s="10" t="n">
+      <c r="F12" s="24" t="n">
         <v>268555.56</v>
       </c>
-      <c r="G27" s="10" t="n">
+      <c r="G12" s="24" t="n">
         <v>124977.19</v>
       </c>
     </row>
-    <row r="28" ht="13" customHeight="1">
-      <c r="A28" s="12" t="inlineStr">
-        <is>
-          <t>2028-09</t>
-        </is>
-      </c>
-      <c r="B28" s="13" t="n">
+    <row r="13" ht="15" customHeight="1">
+      <c r="A13" s="20" t="inlineStr">
+        <is>
+          <t>سبتمبر 2028</t>
+        </is>
+      </c>
+      <c r="B13" s="21" t="n">
         <v>6651.69</v>
       </c>
-      <c r="C28" s="13" t="n">
+      <c r="C13" s="21" t="n">
         <v>1265.58</v>
       </c>
-      <c r="D28" s="13" t="n">
+      <c r="D13" s="21" t="n">
         <v>1827.36</v>
       </c>
-      <c r="E28" s="14" t="n">
+      <c r="E13" s="22" t="n">
         <v>9744.629999999999</v>
       </c>
-      <c r="F28" s="13" t="n">
+      <c r="F13" s="21" t="n">
         <v>278300.19</v>
       </c>
-      <c r="G28" s="13" t="n">
+      <c r="G13" s="21" t="n">
         <v>115232.56</v>
       </c>
     </row>
-    <row r="29" ht="13" customHeight="1">
-      <c r="A29" s="9" t="inlineStr">
-        <is>
-          <t>2028-10</t>
-        </is>
-      </c>
-      <c r="B29" s="10" t="n">
+    <row r="14" ht="15" customHeight="1">
+      <c r="A14" s="23" t="inlineStr">
+        <is>
+          <t>أكتوبر 2028</t>
+        </is>
+      </c>
+      <c r="B14" s="24" t="n">
         <v>6651.69</v>
       </c>
-      <c r="C29" s="10" t="n">
+      <c r="C14" s="24" t="n">
         <v>1265.58</v>
       </c>
-      <c r="D29" s="10" t="n">
+      <c r="D14" s="24" t="n">
         <v>1786.35</v>
       </c>
-      <c r="E29" s="11" t="n">
+      <c r="E14" s="25" t="n">
         <v>9703.620000000001</v>
       </c>
-      <c r="F29" s="10" t="n">
+      <c r="F14" s="24" t="n">
         <v>288003.81</v>
       </c>
-      <c r="G29" s="10" t="n">
+      <c r="G14" s="24" t="n">
         <v>105528.94</v>
       </c>
     </row>
-    <row r="30" ht="13" customHeight="1">
-      <c r="A30" s="12" t="inlineStr">
-        <is>
-          <t>2028-11</t>
-        </is>
-      </c>
-      <c r="B30" s="13" t="n">
+    <row r="15" ht="15" customHeight="1">
+      <c r="A15" s="20" t="inlineStr">
+        <is>
+          <t>نوفمبر 2028</t>
+        </is>
+      </c>
+      <c r="B15" s="21" t="n">
         <v>6651.69</v>
       </c>
-      <c r="C30" s="13" t="n">
+      <c r="C15" s="21" t="n">
         <v>1265.58</v>
       </c>
-      <c r="D30" s="13" t="n">
+      <c r="D15" s="21" t="n">
         <v>1766.85</v>
       </c>
-      <c r="E30" s="14" t="n">
+      <c r="E15" s="22" t="n">
         <v>9684.120000000001</v>
       </c>
-      <c r="F30" s="13" t="n">
+      <c r="F15" s="21" t="n">
         <v>297687.93</v>
       </c>
-      <c r="G30" s="13" t="n">
+      <c r="G15" s="21" t="n">
         <v>95844.82000000001</v>
       </c>
     </row>
-    <row r="31" ht="13" customHeight="1">
-      <c r="A31" s="9" t="inlineStr">
-        <is>
-          <t>2028-12</t>
-        </is>
-      </c>
-      <c r="B31" s="10" t="n">
+    <row r="16" ht="15" customHeight="1">
+      <c r="A16" s="23" t="inlineStr">
+        <is>
+          <t>ديسمبر 2028</t>
+        </is>
+      </c>
+      <c r="B16" s="24" t="n">
         <v>5336.69</v>
       </c>
-      <c r="C31" s="10" t="n">
+      <c r="C16" s="24" t="n">
         <v>1265.58</v>
       </c>
-      <c r="D31" s="10" t="n">
+      <c r="D16" s="24" t="n">
         <v>1766.85</v>
       </c>
-      <c r="E31" s="11" t="n">
+      <c r="E16" s="25" t="n">
         <v>8369.120000000001</v>
       </c>
-      <c r="F31" s="10" t="n">
+      <c r="F16" s="24" t="n">
         <v>306057.05</v>
       </c>
-      <c r="G31" s="10" t="n">
+      <c r="G16" s="24" t="n">
         <v>87475.7</v>
       </c>
     </row>
-    <row r="32" ht="13" customHeight="1">
-      <c r="A32" s="12" t="inlineStr">
-        <is>
-          <t>2029-01</t>
-        </is>
-      </c>
-      <c r="B32" s="13" t="n">
+    <row r="17" ht="18" customHeight="1">
+      <c r="A17" s="26" t="inlineStr">
+        <is>
+          <t>إجمالي سنة 2028</t>
+        </is>
+      </c>
+      <c r="B17" s="17" t="n">
+        <v>80638.56</v>
+      </c>
+      <c r="C17" s="17" t="n">
+        <v>16272.24</v>
+      </c>
+      <c r="D17" s="17" t="n">
+        <v>24483.92</v>
+      </c>
+      <c r="E17" s="17" t="n">
+        <v>121394.72</v>
+      </c>
+      <c r="F17" s="16" t="inlineStr"/>
+      <c r="G17" s="16" t="inlineStr"/>
+    </row>
+  </sheetData>
+  <mergeCells count="2">
+    <mergeCell ref="A2:G2"/>
+    <mergeCell ref="A1:G1"/>
+  </mergeCells>
+  <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
+</worksheet>
+</file>
+
+<file path=xl/worksheets/sheet6.xml><?xml version="1.0" encoding="utf-8"?>
+<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
+  <sheetPr>
+    <outlinePr summaryBelow="1" summaryRight="1"/>
+    <pageSetUpPr/>
+  </sheetPr>
+  <dimension ref="A1:G17"/>
+  <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
+  <cols>
+    <col width="18" customWidth="1" min="1" max="1"/>
+    <col width="14" customWidth="1" min="2" max="2"/>
+    <col width="12" customWidth="1" min="3" max="3"/>
+    <col width="15" customWidth="1" min="4" max="4"/>
+    <col width="16" customWidth="1" min="5" max="5"/>
+    <col width="18" customWidth="1" min="6" max="6"/>
+    <col width="15" customWidth="1" min="7" max="7"/>
+  </cols>
+  <sheetData>
+    <row r="1" ht="24" customHeight="1">
+      <c r="A1" s="1" t="inlineStr">
+        <is>
+          <t>إهلاك السنة المالية 2029 — شهر بشهر</t>
+        </is>
+      </c>
+    </row>
+    <row r="2" ht="16" customHeight="1">
+      <c r="A2" s="18" t="inlineStr">
+        <is>
+          <t>القسط الشهري ثابت لكل أصل حتى نهاية عمره؛ يقلّ الإجمالي كلما اكتمل إهلاك أصل.</t>
+        </is>
+      </c>
+    </row>
+    <row r="4">
+      <c r="A4" s="19" t="inlineStr">
+        <is>
+          <t>الشهر
+Month</t>
+        </is>
+      </c>
+      <c r="B4" s="19" t="inlineStr">
+        <is>
+          <t>سيارات
+Vehicles</t>
+        </is>
+      </c>
+      <c r="C4" s="19" t="inlineStr">
+        <is>
+          <t>تقنية
+IT</t>
+        </is>
+      </c>
+      <c r="D4" s="19" t="inlineStr">
+        <is>
+          <t>آلات ومعدات
+Machinery</t>
+        </is>
+      </c>
+      <c r="E4" s="19" t="inlineStr">
+        <is>
+          <t>إجمالي الشهر
+Monthly total</t>
+        </is>
+      </c>
+      <c r="F4" s="19" t="inlineStr">
+        <is>
+          <t>مجمّع تراكمي (كلي)
+Cumulative (all)</t>
+        </is>
+      </c>
+      <c r="G4" s="19" t="inlineStr">
+        <is>
+          <t>صافي متبقّي
+Remaining NBV</t>
+        </is>
+      </c>
+    </row>
+    <row r="5" ht="15" customHeight="1">
+      <c r="A5" s="20" t="inlineStr">
+        <is>
+          <t>يناير 2029</t>
+        </is>
+      </c>
+      <c r="B5" s="21" t="n">
         <v>5336.69</v>
       </c>
-      <c r="C32" s="13" t="n">
+      <c r="C5" s="21" t="n">
         <v>1265.58</v>
       </c>
-      <c r="D32" s="13" t="n">
+      <c r="D5" s="21" t="n">
         <v>1766.85</v>
       </c>
-      <c r="E32" s="14" t="n">
+      <c r="E5" s="22" t="n">
         <v>8369.120000000001</v>
       </c>
-      <c r="F32" s="13" t="n">
+      <c r="F5" s="21" t="n">
         <v>314426.17</v>
       </c>
-      <c r="G32" s="13" t="n">
+      <c r="G5" s="21" t="n">
         <v>79106.58</v>
       </c>
     </row>
-    <row r="33" ht="13" customHeight="1">
-      <c r="A33" s="9" t="inlineStr">
-        <is>
-          <t>2029-02</t>
-        </is>
-      </c>
-      <c r="B33" s="10" t="n">
+    <row r="6" ht="15" customHeight="1">
+      <c r="A6" s="23" t="inlineStr">
+        <is>
+          <t>فبراير 2029</t>
+        </is>
+      </c>
+      <c r="B6" s="24" t="n">
         <v>5336.69</v>
       </c>
-      <c r="C33" s="10" t="n">
+      <c r="C6" s="24" t="n">
         <v>890.58</v>
       </c>
-      <c r="D33" s="10" t="n">
+      <c r="D6" s="24" t="n">
         <v>1766.75</v>
       </c>
-      <c r="E33" s="11" t="n">
+      <c r="E6" s="25" t="n">
         <v>7994.02</v>
       </c>
-      <c r="F33" s="10" t="n">
+      <c r="F6" s="24" t="n">
         <v>322420.19</v>
       </c>
-      <c r="G33" s="10" t="n">
+      <c r="G6" s="24" t="n">
         <v>71112.56</v>
       </c>
     </row>
-    <row r="34" ht="13" customHeight="1">
-      <c r="A34" s="12" t="inlineStr">
-        <is>
-          <t>2029-03</t>
-        </is>
-      </c>
-      <c r="B34" s="13" t="n">
+    <row r="7" ht="15" customHeight="1">
+      <c r="A7" s="20" t="inlineStr">
+        <is>
+          <t>مارس 2029</t>
+        </is>
+      </c>
+      <c r="B7" s="21" t="n">
         <v>5336.59</v>
       </c>
-      <c r="C34" s="13" t="n">
+      <c r="C7" s="21" t="n">
         <v>890.58</v>
       </c>
-      <c r="D34" s="13" t="n">
+      <c r="D7" s="21" t="n">
         <v>1670.28</v>
       </c>
-      <c r="E34" s="14" t="n">
+      <c r="E7" s="22" t="n">
         <v>7897.45</v>
       </c>
-      <c r="F34" s="13" t="n">
+      <c r="F7" s="21" t="n">
         <v>330317.64</v>
       </c>
-      <c r="G34" s="13" t="n">
+      <c r="G7" s="21" t="n">
         <v>63215.11</v>
       </c>
     </row>
-    <row r="35" ht="13" customHeight="1">
-      <c r="A35" s="9" t="inlineStr">
-        <is>
-          <t>2029-04</t>
-        </is>
-      </c>
-      <c r="B35" s="10" t="n">
+    <row r="8" ht="15" customHeight="1">
+      <c r="A8" s="23" t="inlineStr">
+        <is>
+          <t>أبريل 2029</t>
+        </is>
+      </c>
+      <c r="B8" s="24" t="n">
         <v>4266.77</v>
       </c>
-      <c r="C35" s="10" t="n">
+      <c r="C8" s="24" t="n">
         <v>890.4400000000001</v>
       </c>
-      <c r="D35" s="10" t="n">
+      <c r="D8" s="24" t="n">
         <v>1586.4</v>
       </c>
-      <c r="E35" s="11" t="n">
+      <c r="E8" s="25" t="n">
         <v>6743.61</v>
       </c>
-      <c r="F35" s="10" t="n">
+      <c r="F8" s="24" t="n">
         <v>337061.25</v>
       </c>
-      <c r="G35" s="10" t="n">
+      <c r="G8" s="24" t="n">
         <v>56471.5</v>
       </c>
     </row>
-    <row r="36" ht="13" customHeight="1">
-      <c r="A36" s="12" t="inlineStr">
-        <is>
-          <t>2029-05</t>
-        </is>
-      </c>
-      <c r="B36" s="13" t="n">
+    <row r="9" ht="15" customHeight="1">
+      <c r="A9" s="20" t="inlineStr">
+        <is>
+          <t>مايو 2029</t>
+        </is>
+      </c>
+      <c r="B9" s="21" t="n">
         <v>3833.34</v>
       </c>
-      <c r="C36" s="13" t="n">
+      <c r="C9" s="21" t="n">
         <v>832.41</v>
       </c>
-      <c r="D36" s="13" t="n">
+      <c r="D9" s="21" t="n">
         <v>1522.11</v>
       </c>
-      <c r="E36" s="14" t="n">
+      <c r="E9" s="22" t="n">
         <v>6187.86</v>
       </c>
-      <c r="F36" s="13" t="n">
+      <c r="F9" s="21" t="n">
         <v>343249.11</v>
       </c>
-      <c r="G36" s="13" t="n">
+      <c r="G9" s="21" t="n">
         <v>50283.64</v>
       </c>
     </row>
-    <row r="37" ht="13" customHeight="1">
-      <c r="A37" s="9" t="inlineStr">
-        <is>
-          <t>2029-06</t>
-        </is>
-      </c>
-      <c r="B37" s="10" t="n">
+    <row r="10" ht="15" customHeight="1">
+      <c r="A10" s="23" t="inlineStr">
+        <is>
+          <t>يونيو 2029</t>
+        </is>
+      </c>
+      <c r="B10" s="24" t="n">
         <v>3833.34</v>
       </c>
-      <c r="C37" s="10" t="n">
+      <c r="C10" s="24" t="n">
         <v>443.33</v>
       </c>
-      <c r="D37" s="10" t="n">
+      <c r="D10" s="24" t="n">
         <v>1500.41</v>
       </c>
-      <c r="E37" s="11" t="n">
+      <c r="E10" s="25" t="n">
         <v>5777.08</v>
       </c>
-      <c r="F37" s="10" t="n">
+      <c r="F10" s="24" t="n">
         <v>349026.19</v>
       </c>
-      <c r="G37" s="10" t="n">
+      <c r="G10" s="24" t="n">
         <v>44506.56</v>
       </c>
     </row>
-    <row r="38" ht="13" customHeight="1">
-      <c r="A38" s="12" t="inlineStr">
-        <is>
-          <t>2029-07</t>
-        </is>
-      </c>
-      <c r="B38" s="13" t="n">
+    <row r="11" ht="15" customHeight="1">
+      <c r="A11" s="20" t="inlineStr">
+        <is>
+          <t>يوليو 2029</t>
+        </is>
+      </c>
+      <c r="B11" s="21" t="n">
         <v>3833.34</v>
       </c>
-      <c r="C38" s="13" t="n">
+      <c r="C11" s="21" t="n">
         <v>418.33</v>
       </c>
-      <c r="D38" s="13" t="n">
+      <c r="D11" s="21" t="n">
         <v>1261.8</v>
       </c>
-      <c r="E38" s="14" t="n">
+      <c r="E11" s="22" t="n">
         <v>5513.47</v>
       </c>
-      <c r="F38" s="13" t="n">
+      <c r="F11" s="21" t="n">
         <v>354539.66</v>
       </c>
-      <c r="G38" s="13" t="n">
+      <c r="G11" s="21" t="n">
         <v>38993.09</v>
       </c>
     </row>
-    <row r="39" ht="13" customHeight="1">
-      <c r="A39" s="9" t="inlineStr">
-        <is>
-          <t>2029-08</t>
-        </is>
-      </c>
-      <c r="B39" s="10" t="n">
+    <row r="12" ht="15" customHeight="1">
+      <c r="A12" s="23" t="inlineStr">
+        <is>
+          <t>أغسطس 2029</t>
+        </is>
+      </c>
+      <c r="B12" s="24" t="n">
         <v>3833.34</v>
       </c>
-      <c r="C39" s="10" t="n">
+      <c r="C12" s="24" t="n">
         <v>418.45</v>
       </c>
-      <c r="D39" s="10" t="n">
+      <c r="D12" s="24" t="n">
         <v>1191.44</v>
       </c>
-      <c r="E39" s="11" t="n">
+      <c r="E12" s="25" t="n">
         <v>5443.23</v>
       </c>
-      <c r="F39" s="10" t="n">
+      <c r="F12" s="24" t="n">
         <v>359982.89</v>
       </c>
-      <c r="G39" s="10" t="n">
+      <c r="G12" s="24" t="n">
         <v>33549.86</v>
       </c>
     </row>
-    <row r="40" ht="13" customHeight="1">
-      <c r="A40" s="12" t="inlineStr">
-        <is>
-          <t>2029-09</t>
-        </is>
-      </c>
-      <c r="B40" s="13" t="n">
+    <row r="13" ht="15" customHeight="1">
+      <c r="A13" s="20" t="inlineStr">
+        <is>
+          <t>سبتمبر 2029</t>
+        </is>
+      </c>
+      <c r="B13" s="21" t="n">
         <v>2033.22</v>
       </c>
-      <c r="C40" s="13" t="n">
-        <v>0</v>
-      </c>
-      <c r="D40" s="13" t="n">
+      <c r="C13" s="21" t="n">
+        <v>0</v>
+      </c>
+      <c r="D13" s="21" t="n">
         <v>1045.22</v>
       </c>
-      <c r="E40" s="14" t="n">
+      <c r="E13" s="22" t="n">
         <v>3078.44</v>
       </c>
-      <c r="F40" s="13" t="n">
+      <c r="F13" s="21" t="n">
         <v>363061.33</v>
       </c>
-      <c r="G40" s="13" t="n">
+      <c r="G13" s="21" t="n">
         <v>30471.42</v>
       </c>
     </row>
-    <row r="41" ht="13" customHeight="1">
-      <c r="A41" s="9" t="inlineStr">
-        <is>
-          <t>2029-10</t>
-        </is>
-      </c>
-      <c r="B41" s="10" t="n">
+    <row r="14" ht="15" customHeight="1">
+      <c r="A14" s="23" t="inlineStr">
+        <is>
+          <t>أكتوبر 2029</t>
+        </is>
+      </c>
+      <c r="B14" s="24" t="n">
         <v>1166.67</v>
       </c>
-      <c r="C41" s="10" t="n">
-        <v>0</v>
-      </c>
-      <c r="D41" s="10" t="n">
+      <c r="C14" s="24" t="n">
+        <v>0</v>
+      </c>
+      <c r="D14" s="24" t="n">
         <v>645.3</v>
       </c>
-      <c r="E41" s="11" t="n">
+      <c r="E14" s="25" t="n">
         <v>1811.97</v>
       </c>
-      <c r="F41" s="10" t="n">
+      <c r="F14" s="24" t="n">
         <v>364873.3</v>
       </c>
-      <c r="G41" s="10" t="n">
+      <c r="G14" s="24" t="n">
         <v>28659.45</v>
       </c>
     </row>
-    <row r="42" ht="13" customHeight="1">
-      <c r="A42" s="12" t="inlineStr">
-        <is>
-          <t>2029-11</t>
-        </is>
-      </c>
-      <c r="B42" s="13" t="n">
+    <row r="15" ht="15" customHeight="1">
+      <c r="A15" s="20" t="inlineStr">
+        <is>
+          <t>نوفمبر 2029</t>
+        </is>
+      </c>
+      <c r="B15" s="21" t="n">
         <v>466.54</v>
       </c>
-      <c r="C42" s="13" t="n">
-        <v>0</v>
-      </c>
-      <c r="D42" s="13" t="n">
+      <c r="C15" s="21" t="n">
+        <v>0</v>
+      </c>
+      <c r="D15" s="21" t="n">
         <v>618.75</v>
       </c>
-      <c r="E42" s="14" t="n">
+      <c r="E15" s="22" t="n">
         <v>1085.29</v>
       </c>
-      <c r="F42" s="13" t="n">
+      <c r="F15" s="21" t="n">
         <v>365958.59</v>
       </c>
-      <c r="G42" s="13" t="n">
+      <c r="G15" s="21" t="n">
         <v>27574.16</v>
       </c>
     </row>
-    <row r="43" ht="13" customHeight="1">
-      <c r="A43" s="9" t="inlineStr">
-        <is>
-          <t>2029-12</t>
-        </is>
-      </c>
-      <c r="B43" s="10" t="n">
-        <v>0</v>
-      </c>
-      <c r="C43" s="10" t="n">
-        <v>0</v>
-      </c>
-      <c r="D43" s="10" t="n">
+    <row r="16" ht="15" customHeight="1">
+      <c r="A16" s="23" t="inlineStr">
+        <is>
+          <t>ديسمبر 2029</t>
+        </is>
+      </c>
+      <c r="B16" s="24" t="n">
+        <v>0</v>
+      </c>
+      <c r="C16" s="24" t="n">
+        <v>0</v>
+      </c>
+      <c r="D16" s="24" t="n">
         <v>618.75</v>
       </c>
-      <c r="E43" s="11" t="n">
+      <c r="E16" s="25" t="n">
         <v>618.75</v>
       </c>
-      <c r="F43" s="10" t="n">
+      <c r="F16" s="24" t="n">
         <v>366577.34</v>
       </c>
-      <c r="G43" s="10" t="n">
+      <c r="G16" s="24" t="n">
         <v>26955.41</v>
       </c>
     </row>
-    <row r="44" ht="13" customHeight="1">
-      <c r="A44" s="12" t="inlineStr">
-        <is>
-          <t>2030-01</t>
-        </is>
-      </c>
-      <c r="B44" s="13" t="n">
-        <v>0</v>
-      </c>
-      <c r="C44" s="13" t="n">
-        <v>0</v>
-      </c>
-      <c r="D44" s="13" t="n">
+    <row r="17" ht="18" customHeight="1">
+      <c r="A17" s="26" t="inlineStr">
+        <is>
+          <t>إجمالي سنة 2029</t>
+        </is>
+      </c>
+      <c r="B17" s="17" t="n">
+        <v>39276.53</v>
+      </c>
+      <c r="C17" s="17" t="n">
+        <v>6049.7</v>
+      </c>
+      <c r="D17" s="17" t="n">
+        <v>15194.06</v>
+      </c>
+      <c r="E17" s="17" t="n">
+        <v>60520.29</v>
+      </c>
+      <c r="F17" s="16" t="inlineStr"/>
+      <c r="G17" s="16" t="inlineStr"/>
+    </row>
+  </sheetData>
+  <mergeCells count="2">
+    <mergeCell ref="A2:G2"/>
+    <mergeCell ref="A1:G1"/>
+  </mergeCells>
+  <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
+</worksheet>
+</file>
+
+<file path=xl/worksheets/sheet7.xml><?xml version="1.0" encoding="utf-8"?>
+<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
+  <sheetPr>
+    <outlinePr summaryBelow="1" summaryRight="1"/>
+    <pageSetUpPr/>
+  </sheetPr>
+  <dimension ref="A1:G17"/>
+  <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
+  <cols>
+    <col width="18" customWidth="1" min="1" max="1"/>
+    <col width="14" customWidth="1" min="2" max="2"/>
+    <col width="12" customWidth="1" min="3" max="3"/>
+    <col width="15" customWidth="1" min="4" max="4"/>
+    <col width="16" customWidth="1" min="5" max="5"/>
+    <col width="18" customWidth="1" min="6" max="6"/>
+    <col width="15" customWidth="1" min="7" max="7"/>
+  </cols>
+  <sheetData>
+    <row r="1" ht="24" customHeight="1">
+      <c r="A1" s="1" t="inlineStr">
+        <is>
+          <t>إهلاك السنة المالية 2030 — شهر بشهر</t>
+        </is>
+      </c>
+    </row>
+    <row r="2" ht="16" customHeight="1">
+      <c r="A2" s="18" t="inlineStr">
+        <is>
+          <t>القسط الشهري ثابت لكل أصل حتى نهاية عمره؛ يقلّ الإجمالي كلما اكتمل إهلاك أصل.</t>
+        </is>
+      </c>
+    </row>
+    <row r="4">
+      <c r="A4" s="19" t="inlineStr">
+        <is>
+          <t>الشهر
+Month</t>
+        </is>
+      </c>
+      <c r="B4" s="19" t="inlineStr">
+        <is>
+          <t>سيارات
+Vehicles</t>
+        </is>
+      </c>
+      <c r="C4" s="19" t="inlineStr">
+        <is>
+          <t>تقنية
+IT</t>
+        </is>
+      </c>
+      <c r="D4" s="19" t="inlineStr">
+        <is>
+          <t>آلات ومعدات
+Machinery</t>
+        </is>
+      </c>
+      <c r="E4" s="19" t="inlineStr">
+        <is>
+          <t>إجمالي الشهر
+Monthly total</t>
+        </is>
+      </c>
+      <c r="F4" s="19" t="inlineStr">
+        <is>
+          <t>مجمّع تراكمي (كلي)
+Cumulative (all)</t>
+        </is>
+      </c>
+      <c r="G4" s="19" t="inlineStr">
+        <is>
+          <t>صافي متبقّي
+Remaining NBV</t>
+        </is>
+      </c>
+    </row>
+    <row r="5" ht="15" customHeight="1">
+      <c r="A5" s="20" t="inlineStr">
+        <is>
+          <t>يناير 2030</t>
+        </is>
+      </c>
+      <c r="B5" s="21" t="n">
+        <v>0</v>
+      </c>
+      <c r="C5" s="21" t="n">
+        <v>0</v>
+      </c>
+      <c r="D5" s="21" t="n">
         <v>618.75</v>
       </c>
-      <c r="E44" s="14" t="n">
+      <c r="E5" s="22" t="n">
         <v>618.75</v>
       </c>
-      <c r="F44" s="13" t="n">
+      <c r="F5" s="21" t="n">
         <v>367196.09</v>
       </c>
-      <c r="G44" s="13" t="n">
+      <c r="G5" s="21" t="n">
         <v>26336.66</v>
       </c>
     </row>
-    <row r="45" ht="13" customHeight="1">
-      <c r="A45" s="9" t="inlineStr">
-        <is>
-          <t>2030-02</t>
-        </is>
-      </c>
-      <c r="B45" s="10" t="n">
-        <v>0</v>
-      </c>
-      <c r="C45" s="10" t="n">
-        <v>0</v>
-      </c>
-      <c r="D45" s="10" t="n">
+    <row r="6" ht="15" customHeight="1">
+      <c r="A6" s="23" t="inlineStr">
+        <is>
+          <t>فبراير 2030</t>
+        </is>
+      </c>
+      <c r="B6" s="24" t="n">
+        <v>0</v>
+      </c>
+      <c r="C6" s="24" t="n">
+        <v>0</v>
+      </c>
+      <c r="D6" s="24" t="n">
         <v>618.75</v>
       </c>
-      <c r="E45" s="11" t="n">
+      <c r="E6" s="25" t="n">
         <v>618.75</v>
       </c>
-      <c r="F45" s="10" t="n">
+      <c r="F6" s="24" t="n">
         <v>367814.84</v>
       </c>
-      <c r="G45" s="10" t="n">
+      <c r="G6" s="24" t="n">
         <v>25717.91</v>
       </c>
     </row>
-    <row r="46" ht="13" customHeight="1">
-      <c r="A46" s="12" t="inlineStr">
-        <is>
-          <t>2030-03</t>
-        </is>
-      </c>
-      <c r="B46" s="13" t="n">
-        <v>0</v>
-      </c>
-      <c r="C46" s="13" t="n">
-        <v>0</v>
-      </c>
-      <c r="D46" s="13" t="n">
+    <row r="7" ht="15" customHeight="1">
+      <c r="A7" s="20" t="inlineStr">
+        <is>
+          <t>مارس 2030</t>
+        </is>
+      </c>
+      <c r="B7" s="21" t="n">
+        <v>0</v>
+      </c>
+      <c r="C7" s="21" t="n">
+        <v>0</v>
+      </c>
+      <c r="D7" s="21" t="n">
         <v>618.75</v>
       </c>
-      <c r="E46" s="14" t="n">
+      <c r="E7" s="22" t="n">
         <v>618.75</v>
       </c>
-      <c r="F46" s="13" t="n">
+      <c r="F7" s="21" t="n">
         <v>368433.59</v>
       </c>
-      <c r="G46" s="13" t="n">
+      <c r="G7" s="21" t="n">
         <v>25099.16</v>
       </c>
     </row>
-    <row r="47" ht="13" customHeight="1">
-      <c r="A47" s="9" t="inlineStr">
-        <is>
-          <t>2030-04</t>
-        </is>
-      </c>
-      <c r="B47" s="10" t="n">
-        <v>0</v>
-      </c>
-      <c r="C47" s="10" t="n">
-        <v>0</v>
-      </c>
-      <c r="D47" s="10" t="n">
+    <row r="8" ht="15" customHeight="1">
+      <c r="A8" s="23" t="inlineStr">
+        <is>
+          <t>أبريل 2030</t>
+        </is>
+      </c>
+      <c r="B8" s="24" t="n">
+        <v>0</v>
+      </c>
+      <c r="C8" s="24" t="n">
+        <v>0</v>
+      </c>
+      <c r="D8" s="24" t="n">
         <v>618.75</v>
       </c>
-      <c r="E47" s="11" t="n">
+      <c r="E8" s="25" t="n">
         <v>618.75</v>
       </c>
-      <c r="F47" s="10" t="n">
+      <c r="F8" s="24" t="n">
         <v>369052.34</v>
       </c>
-      <c r="G47" s="10" t="n">
+      <c r="G8" s="24" t="n">
         <v>24480.41</v>
       </c>
     </row>
-    <row r="48" ht="13" customHeight="1">
-      <c r="A48" s="12" t="inlineStr">
-        <is>
-          <t>2030-05</t>
-        </is>
-      </c>
-      <c r="B48" s="13" t="n">
-        <v>0</v>
-      </c>
-      <c r="C48" s="13" t="n">
-        <v>0</v>
-      </c>
-      <c r="D48" s="13" t="n">
+    <row r="9" ht="15" customHeight="1">
+      <c r="A9" s="20" t="inlineStr">
+        <is>
+          <t>مايو 2030</t>
+        </is>
+      </c>
+      <c r="B9" s="21" t="n">
+        <v>0</v>
+      </c>
+      <c r="C9" s="21" t="n">
+        <v>0</v>
+      </c>
+      <c r="D9" s="21" t="n">
         <v>618.75</v>
       </c>
-      <c r="E48" s="14" t="n">
+      <c r="E9" s="22" t="n">
         <v>618.75</v>
       </c>
-      <c r="F48" s="13" t="n">
+      <c r="F9" s="21" t="n">
         <v>369671.09</v>
       </c>
-      <c r="G48" s="13" t="n">
+      <c r="G9" s="21" t="n">
         <v>23861.66</v>
       </c>
     </row>
-    <row r="49" ht="13" customHeight="1">
-      <c r="A49" s="9" t="inlineStr">
-        <is>
-          <t>2030-06</t>
-        </is>
-      </c>
-      <c r="B49" s="10" t="n">
-        <v>0</v>
-      </c>
-      <c r="C49" s="10" t="n">
-        <v>0</v>
-      </c>
-      <c r="D49" s="10" t="n">
+    <row r="10" ht="15" customHeight="1">
+      <c r="A10" s="23" t="inlineStr">
+        <is>
+          <t>يونيو 2030</t>
+        </is>
+      </c>
+      <c r="B10" s="24" t="n">
+        <v>0</v>
+      </c>
+      <c r="C10" s="24" t="n">
+        <v>0</v>
+      </c>
+      <c r="D10" s="24" t="n">
         <v>618.75</v>
       </c>
-      <c r="E49" s="11" t="n">
+      <c r="E10" s="25" t="n">
         <v>618.75</v>
       </c>
-      <c r="F49" s="10" t="n">
+      <c r="F10" s="24" t="n">
         <v>370289.84</v>
       </c>
-      <c r="G49" s="10" t="n">
+      <c r="G10" s="24" t="n">
         <v>23242.91</v>
       </c>
     </row>
-    <row r="50" ht="13" customHeight="1">
-      <c r="A50" s="12" t="inlineStr">
-        <is>
-          <t>2030-07</t>
-        </is>
-      </c>
-      <c r="B50" s="13" t="n">
-        <v>0</v>
-      </c>
-      <c r="C50" s="13" t="n">
-        <v>0</v>
-      </c>
-      <c r="D50" s="13" t="n">
+    <row r="11" ht="15" customHeight="1">
+      <c r="A11" s="20" t="inlineStr">
+        <is>
+          <t>يوليو 2030</t>
+        </is>
+      </c>
+      <c r="B11" s="21" t="n">
+        <v>0</v>
+      </c>
+      <c r="C11" s="21" t="n">
+        <v>0</v>
+      </c>
+      <c r="D11" s="21" t="n">
         <v>618.75</v>
       </c>
-      <c r="E50" s="14" t="n">
+      <c r="E11" s="22" t="n">
         <v>618.75</v>
       </c>
-      <c r="F50" s="13" t="n">
+      <c r="F11" s="21" t="n">
         <v>370908.59</v>
       </c>
-      <c r="G50" s="13" t="n">
+      <c r="G11" s="21" t="n">
         <v>22624.16</v>
       </c>
     </row>
-    <row r="51" ht="13" customHeight="1">
-      <c r="A51" s="9" t="inlineStr">
-        <is>
-          <t>2030-08</t>
-        </is>
-      </c>
-      <c r="B51" s="10" t="n">
-        <v>0</v>
-      </c>
-      <c r="C51" s="10" t="n">
-        <v>0</v>
-      </c>
-      <c r="D51" s="10" t="n">
+    <row r="12" ht="15" customHeight="1">
+      <c r="A12" s="23" t="inlineStr">
+        <is>
+          <t>أغسطس 2030</t>
+        </is>
+      </c>
+      <c r="B12" s="24" t="n">
+        <v>0</v>
+      </c>
+      <c r="C12" s="24" t="n">
+        <v>0</v>
+      </c>
+      <c r="D12" s="24" t="n">
         <v>618.75</v>
       </c>
-      <c r="E51" s="11" t="n">
+      <c r="E12" s="25" t="n">
         <v>618.75</v>
       </c>
-      <c r="F51" s="10" t="n">
+      <c r="F12" s="24" t="n">
         <v>371527.34</v>
       </c>
-      <c r="G51" s="10" t="n">
+      <c r="G12" s="24" t="n">
         <v>22005.41</v>
       </c>
     </row>
-    <row r="52" ht="13" customHeight="1">
-      <c r="A52" s="12" t="inlineStr">
-        <is>
-          <t>2030-09</t>
-        </is>
-      </c>
-      <c r="B52" s="13" t="n">
-        <v>0</v>
-      </c>
-      <c r="C52" s="13" t="n">
-        <v>0</v>
-      </c>
-      <c r="D52" s="13" t="n">
+    <row r="13" ht="15" customHeight="1">
+      <c r="A13" s="20" t="inlineStr">
+        <is>
+          <t>سبتمبر 2030</t>
+        </is>
+      </c>
+      <c r="B13" s="21" t="n">
+        <v>0</v>
+      </c>
+      <c r="C13" s="21" t="n">
+        <v>0</v>
+      </c>
+      <c r="D13" s="21" t="n">
         <v>618.75</v>
       </c>
-      <c r="E52" s="14" t="n">
+      <c r="E13" s="22" t="n">
         <v>618.75</v>
       </c>
-      <c r="F52" s="13" t="n">
+      <c r="F13" s="21" t="n">
         <v>372146.09</v>
       </c>
-      <c r="G52" s="13" t="n">
+      <c r="G13" s="21" t="n">
         <v>21386.66</v>
       </c>
     </row>
-    <row r="53" ht="13" customHeight="1">
-      <c r="A53" s="9" t="inlineStr">
-        <is>
-          <t>2030-10</t>
-        </is>
-      </c>
-      <c r="B53" s="10" t="n">
-        <v>0</v>
-      </c>
-      <c r="C53" s="10" t="n">
-        <v>0</v>
-      </c>
-      <c r="D53" s="10" t="n">
+    <row r="14" ht="15" customHeight="1">
+      <c r="A14" s="23" t="inlineStr">
+        <is>
+          <t>أكتوبر 2030</t>
+        </is>
+      </c>
+      <c r="B14" s="24" t="n">
+        <v>0</v>
+      </c>
+      <c r="C14" s="24" t="n">
+        <v>0</v>
+      </c>
+      <c r="D14" s="24" t="n">
         <v>618.75</v>
       </c>
-      <c r="E53" s="11" t="n">
+      <c r="E14" s="25" t="n">
         <v>618.75</v>
       </c>
-      <c r="F53" s="10" t="n">
+      <c r="F14" s="24" t="n">
         <v>372764.84</v>
       </c>
-      <c r="G53" s="10" t="n">
+      <c r="G14" s="24" t="n">
         <v>20767.91</v>
       </c>
     </row>
-    <row r="54" ht="13" customHeight="1">
-      <c r="A54" s="12" t="inlineStr">
-        <is>
-          <t>2030-11</t>
-        </is>
-      </c>
-      <c r="B54" s="13" t="n">
-        <v>0</v>
-      </c>
-      <c r="C54" s="13" t="n">
-        <v>0</v>
-      </c>
-      <c r="D54" s="13" t="n">
+    <row r="15" ht="15" customHeight="1">
+      <c r="A15" s="20" t="inlineStr">
+        <is>
+          <t>نوفمبر 2030</t>
+        </is>
+      </c>
+      <c r="B15" s="21" t="n">
+        <v>0</v>
+      </c>
+      <c r="C15" s="21" t="n">
+        <v>0</v>
+      </c>
+      <c r="D15" s="21" t="n">
         <v>618.75</v>
       </c>
-      <c r="E54" s="14" t="n">
+      <c r="E15" s="22" t="n">
         <v>618.75</v>
       </c>
-      <c r="F54" s="13" t="n">
+      <c r="F15" s="21" t="n">
         <v>373383.59</v>
       </c>
-      <c r="G54" s="13" t="n">
+      <c r="G15" s="21" t="n">
         <v>20149.16</v>
       </c>
     </row>
-    <row r="55" ht="13" customHeight="1">
-      <c r="A55" s="9" t="inlineStr">
-        <is>
-          <t>2030-12</t>
-        </is>
-      </c>
-      <c r="B55" s="10" t="n">
-        <v>0</v>
-      </c>
-      <c r="C55" s="10" t="n">
-        <v>0</v>
-      </c>
-      <c r="D55" s="10" t="n">
+    <row r="16" ht="15" customHeight="1">
+      <c r="A16" s="23" t="inlineStr">
+        <is>
+          <t>ديسمبر 2030</t>
+        </is>
+      </c>
+      <c r="B16" s="24" t="n">
+        <v>0</v>
+      </c>
+      <c r="C16" s="24" t="n">
+        <v>0</v>
+      </c>
+      <c r="D16" s="24" t="n">
         <v>618.75</v>
       </c>
-      <c r="E55" s="11" t="n">
+      <c r="E16" s="25" t="n">
         <v>618.75</v>
       </c>
-      <c r="F55" s="10" t="n">
+      <c r="F16" s="24" t="n">
         <v>374002.34</v>
       </c>
-      <c r="G55" s="10" t="n">
+      <c r="G16" s="24" t="n">
         <v>19530.41</v>
       </c>
     </row>
-    <row r="56" ht="13" customHeight="1">
-      <c r="A56" s="12" t="inlineStr">
-        <is>
-          <t>2031-01</t>
-        </is>
-      </c>
-      <c r="B56" s="13" t="n">
-        <v>0</v>
-      </c>
-      <c r="C56" s="13" t="n">
-        <v>0</v>
-      </c>
-      <c r="D56" s="13" t="n">
+    <row r="17" ht="18" customHeight="1">
+      <c r="A17" s="26" t="inlineStr">
+        <is>
+          <t>إجمالي سنة 2030</t>
+        </is>
+      </c>
+      <c r="B17" s="17" t="n">
+        <v>0</v>
+      </c>
+      <c r="C17" s="17" t="n">
+        <v>0</v>
+      </c>
+      <c r="D17" s="17" t="n">
+        <v>7425</v>
+      </c>
+      <c r="E17" s="17" t="n">
+        <v>7425</v>
+      </c>
+      <c r="F17" s="16" t="inlineStr"/>
+      <c r="G17" s="16" t="inlineStr"/>
+    </row>
+  </sheetData>
+  <mergeCells count="2">
+    <mergeCell ref="A2:G2"/>
+    <mergeCell ref="A1:G1"/>
+  </mergeCells>
+  <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
+</worksheet>
+</file>
+
+<file path=xl/worksheets/sheet8.xml><?xml version="1.0" encoding="utf-8"?>
+<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
+  <sheetPr>
+    <outlinePr summaryBelow="1" summaryRight="1"/>
+    <pageSetUpPr/>
+  </sheetPr>
+  <dimension ref="A1:G17"/>
+  <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
+  <cols>
+    <col width="18" customWidth="1" min="1" max="1"/>
+    <col width="14" customWidth="1" min="2" max="2"/>
+    <col width="12" customWidth="1" min="3" max="3"/>
+    <col width="15" customWidth="1" min="4" max="4"/>
+    <col width="16" customWidth="1" min="5" max="5"/>
+    <col width="18" customWidth="1" min="6" max="6"/>
+    <col width="15" customWidth="1" min="7" max="7"/>
+  </cols>
+  <sheetData>
+    <row r="1" ht="24" customHeight="1">
+      <c r="A1" s="1" t="inlineStr">
+        <is>
+          <t>إهلاك السنة المالية 2031 — شهر بشهر</t>
+        </is>
+      </c>
+    </row>
+    <row r="2" ht="16" customHeight="1">
+      <c r="A2" s="18" t="inlineStr">
+        <is>
+          <t>القسط الشهري ثابت لكل أصل حتى نهاية عمره؛ يقلّ الإجمالي كلما اكتمل إهلاك أصل.</t>
+        </is>
+      </c>
+    </row>
+    <row r="4">
+      <c r="A4" s="19" t="inlineStr">
+        <is>
+          <t>الشهر
+Month</t>
+        </is>
+      </c>
+      <c r="B4" s="19" t="inlineStr">
+        <is>
+          <t>سيارات
+Vehicles</t>
+        </is>
+      </c>
+      <c r="C4" s="19" t="inlineStr">
+        <is>
+          <t>تقنية
+IT</t>
+        </is>
+      </c>
+      <c r="D4" s="19" t="inlineStr">
+        <is>
+          <t>آلات ومعدات
+Machinery</t>
+        </is>
+      </c>
+      <c r="E4" s="19" t="inlineStr">
+        <is>
+          <t>إجمالي الشهر
+Monthly total</t>
+        </is>
+      </c>
+      <c r="F4" s="19" t="inlineStr">
+        <is>
+          <t>مجمّع تراكمي (كلي)
+Cumulative (all)</t>
+        </is>
+      </c>
+      <c r="G4" s="19" t="inlineStr">
+        <is>
+          <t>صافي متبقّي
+Remaining NBV</t>
+        </is>
+      </c>
+    </row>
+    <row r="5" ht="15" customHeight="1">
+      <c r="A5" s="20" t="inlineStr">
+        <is>
+          <t>يناير 2031</t>
+        </is>
+      </c>
+      <c r="B5" s="21" t="n">
+        <v>0</v>
+      </c>
+      <c r="C5" s="21" t="n">
+        <v>0</v>
+      </c>
+      <c r="D5" s="21" t="n">
         <v>618.75</v>
       </c>
-      <c r="E56" s="14" t="n">
+      <c r="E5" s="22" t="n">
         <v>618.75</v>
       </c>
-      <c r="F56" s="13" t="n">
+      <c r="F5" s="21" t="n">
         <v>374621.09</v>
       </c>
-      <c r="G56" s="13" t="n">
+      <c r="G5" s="21" t="n">
         <v>18911.66</v>
       </c>
     </row>
-    <row r="57" ht="13" customHeight="1">
-      <c r="A57" s="9" t="inlineStr">
-        <is>
-          <t>2031-02</t>
-        </is>
-      </c>
-      <c r="B57" s="10" t="n">
-        <v>0</v>
-      </c>
-      <c r="C57" s="10" t="n">
-        <v>0</v>
-      </c>
-      <c r="D57" s="10" t="n">
+    <row r="6" ht="15" customHeight="1">
+      <c r="A6" s="23" t="inlineStr">
+        <is>
+          <t>فبراير 2031</t>
+        </is>
+      </c>
+      <c r="B6" s="24" t="n">
+        <v>0</v>
+      </c>
+      <c r="C6" s="24" t="n">
+        <v>0</v>
+      </c>
+      <c r="D6" s="24" t="n">
         <v>618.75</v>
       </c>
-      <c r="E57" s="11" t="n">
+      <c r="E6" s="25" t="n">
         <v>618.75</v>
       </c>
-      <c r="F57" s="10" t="n">
+      <c r="F6" s="24" t="n">
         <v>375239.84</v>
       </c>
-      <c r="G57" s="10" t="n">
+      <c r="G6" s="24" t="n">
         <v>18292.91</v>
       </c>
     </row>
-    <row r="58" ht="13" customHeight="1">
-      <c r="A58" s="12" t="inlineStr">
-        <is>
-          <t>2031-03</t>
-        </is>
-      </c>
-      <c r="B58" s="13" t="n">
-        <v>0</v>
-      </c>
-      <c r="C58" s="13" t="n">
-        <v>0</v>
-      </c>
-      <c r="D58" s="13" t="n">
+    <row r="7" ht="15" customHeight="1">
+      <c r="A7" s="20" t="inlineStr">
+        <is>
+          <t>مارس 2031</t>
+        </is>
+      </c>
+      <c r="B7" s="21" t="n">
+        <v>0</v>
+      </c>
+      <c r="C7" s="21" t="n">
+        <v>0</v>
+      </c>
+      <c r="D7" s="21" t="n">
         <v>618.75</v>
       </c>
-      <c r="E58" s="14" t="n">
+      <c r="E7" s="22" t="n">
         <v>618.75</v>
       </c>
-      <c r="F58" s="13" t="n">
+      <c r="F7" s="21" t="n">
         <v>375858.59</v>
       </c>
-      <c r="G58" s="13" t="n">
+      <c r="G7" s="21" t="n">
         <v>17674.16</v>
       </c>
     </row>
-    <row r="59" ht="13" customHeight="1">
-      <c r="A59" s="9" t="inlineStr">
-        <is>
-          <t>2031-04</t>
-        </is>
-      </c>
-      <c r="B59" s="10" t="n">
-        <v>0</v>
-      </c>
-      <c r="C59" s="10" t="n">
-        <v>0</v>
-      </c>
-      <c r="D59" s="10" t="n">
+    <row r="8" ht="15" customHeight="1">
+      <c r="A8" s="23" t="inlineStr">
+        <is>
+          <t>أبريل 2031</t>
+        </is>
+      </c>
+      <c r="B8" s="24" t="n">
+        <v>0</v>
+      </c>
+      <c r="C8" s="24" t="n">
+        <v>0</v>
+      </c>
+      <c r="D8" s="24" t="n">
         <v>618.75</v>
       </c>
-      <c r="E59" s="11" t="n">
+      <c r="E8" s="25" t="n">
         <v>618.75</v>
       </c>
-      <c r="F59" s="10" t="n">
+      <c r="F8" s="24" t="n">
         <v>376477.34</v>
       </c>
-      <c r="G59" s="10" t="n">
+      <c r="G8" s="24" t="n">
         <v>17055.41</v>
       </c>
     </row>
-    <row r="60" ht="13" customHeight="1">
-      <c r="A60" s="12" t="inlineStr">
-        <is>
-          <t>2031-05</t>
-        </is>
-      </c>
-      <c r="B60" s="13" t="n">
-        <v>0</v>
-      </c>
-      <c r="C60" s="13" t="n">
-        <v>0</v>
-      </c>
-      <c r="D60" s="13" t="n">
+    <row r="9" ht="15" customHeight="1">
+      <c r="A9" s="20" t="inlineStr">
+        <is>
+          <t>مايو 2031</t>
+        </is>
+      </c>
+      <c r="B9" s="21" t="n">
+        <v>0</v>
+      </c>
+      <c r="C9" s="21" t="n">
+        <v>0</v>
+      </c>
+      <c r="D9" s="21" t="n">
         <v>588.5599999999999</v>
       </c>
-      <c r="E60" s="14" t="n">
+      <c r="E9" s="22" t="n">
         <v>588.5599999999999</v>
       </c>
-      <c r="F60" s="13" t="n">
+      <c r="F9" s="21" t="n">
         <v>377065.9</v>
       </c>
-      <c r="G60" s="13" t="n">
+      <c r="G9" s="21" t="n">
         <v>16466.85</v>
       </c>
     </row>
-    <row r="61" ht="13" customHeight="1">
-      <c r="A61" s="9" t="inlineStr">
-        <is>
-          <t>2031-06</t>
-        </is>
-      </c>
-      <c r="B61" s="10" t="n">
-        <v>0</v>
-      </c>
-      <c r="C61" s="10" t="n">
-        <v>0</v>
-      </c>
-      <c r="D61" s="10" t="n">
+    <row r="10" ht="15" customHeight="1">
+      <c r="A10" s="23" t="inlineStr">
+        <is>
+          <t>يونيو 2031</t>
+        </is>
+      </c>
+      <c r="B10" s="24" t="n">
+        <v>0</v>
+      </c>
+      <c r="C10" s="24" t="n">
+        <v>0</v>
+      </c>
+      <c r="D10" s="24" t="n">
         <v>539.58</v>
       </c>
-      <c r="E61" s="11" t="n">
+      <c r="E10" s="25" t="n">
         <v>539.58</v>
       </c>
-      <c r="F61" s="10" t="n">
+      <c r="F10" s="24" t="n">
         <v>377605.48</v>
       </c>
-      <c r="G61" s="10" t="n">
+      <c r="G10" s="24" t="n">
         <v>15927.27</v>
       </c>
     </row>
-    <row r="62" ht="13" customHeight="1">
-      <c r="A62" s="12" t="inlineStr">
-        <is>
-          <t>2031-07</t>
-        </is>
-      </c>
-      <c r="B62" s="13" t="n">
-        <v>0</v>
-      </c>
-      <c r="C62" s="13" t="n">
-        <v>0</v>
-      </c>
-      <c r="D62" s="13" t="n">
+    <row r="11" ht="15" customHeight="1">
+      <c r="A11" s="20" t="inlineStr">
+        <is>
+          <t>يوليو 2031</t>
+        </is>
+      </c>
+      <c r="B11" s="21" t="n">
+        <v>0</v>
+      </c>
+      <c r="C11" s="21" t="n">
+        <v>0</v>
+      </c>
+      <c r="D11" s="21" t="n">
         <v>539.58</v>
       </c>
-      <c r="E62" s="14" t="n">
+      <c r="E11" s="22" t="n">
         <v>539.58</v>
       </c>
-      <c r="F62" s="13" t="n">
+      <c r="F11" s="21" t="n">
         <v>378145.06</v>
       </c>
-      <c r="G62" s="13" t="n">
+      <c r="G11" s="21" t="n">
         <v>15387.69</v>
       </c>
     </row>
-    <row r="63" ht="13" customHeight="1">
-      <c r="A63" s="9" t="inlineStr">
-        <is>
-          <t>2031-08</t>
-        </is>
-      </c>
-      <c r="B63" s="10" t="n">
-        <v>0</v>
-      </c>
-      <c r="C63" s="10" t="n">
-        <v>0</v>
-      </c>
-      <c r="D63" s="10" t="n">
+    <row r="12" ht="15" customHeight="1">
+      <c r="A12" s="23" t="inlineStr">
+        <is>
+          <t>أغسطس 2031</t>
+        </is>
+      </c>
+      <c r="B12" s="24" t="n">
+        <v>0</v>
+      </c>
+      <c r="C12" s="24" t="n">
+        <v>0</v>
+      </c>
+      <c r="D12" s="24" t="n">
         <v>539.58</v>
       </c>
-      <c r="E63" s="11" t="n">
+      <c r="E12" s="25" t="n">
         <v>539.58</v>
       </c>
-      <c r="F63" s="10" t="n">
+      <c r="F12" s="24" t="n">
         <v>378684.64</v>
       </c>
-      <c r="G63" s="10" t="n">
+      <c r="G12" s="24" t="n">
         <v>14848.11</v>
       </c>
     </row>
-    <row r="64" ht="13" customHeight="1">
-      <c r="A64" s="12" t="inlineStr">
-        <is>
-          <t>2031-09</t>
-        </is>
-      </c>
-      <c r="B64" s="13" t="n">
-        <v>0</v>
-      </c>
-      <c r="C64" s="13" t="n">
-        <v>0</v>
-      </c>
-      <c r="D64" s="13" t="n">
+    <row r="13" ht="15" customHeight="1">
+      <c r="A13" s="20" t="inlineStr">
+        <is>
+          <t>سبتمبر 2031</t>
+        </is>
+      </c>
+      <c r="B13" s="21" t="n">
+        <v>0</v>
+      </c>
+      <c r="C13" s="21" t="n">
+        <v>0</v>
+      </c>
+      <c r="D13" s="21" t="n">
         <v>539.58</v>
       </c>
-      <c r="E64" s="14" t="n">
+      <c r="E13" s="22" t="n">
         <v>539.58</v>
       </c>
-      <c r="F64" s="13" t="n">
+      <c r="F13" s="21" t="n">
         <v>379224.22</v>
       </c>
-      <c r="G64" s="13" t="n">
+      <c r="G13" s="21" t="n">
         <v>14308.53</v>
       </c>
     </row>
-    <row r="65" ht="13" customHeight="1">
-      <c r="A65" s="9" t="inlineStr">
-        <is>
-          <t>2031-10</t>
-        </is>
-      </c>
-      <c r="B65" s="10" t="n">
-        <v>0</v>
-      </c>
-      <c r="C65" s="10" t="n">
-        <v>0</v>
-      </c>
-      <c r="D65" s="10" t="n">
+    <row r="14" ht="15" customHeight="1">
+      <c r="A14" s="23" t="inlineStr">
+        <is>
+          <t>أكتوبر 2031</t>
+        </is>
+      </c>
+      <c r="B14" s="24" t="n">
+        <v>0</v>
+      </c>
+      <c r="C14" s="24" t="n">
+        <v>0</v>
+      </c>
+      <c r="D14" s="24" t="n">
         <v>539.58</v>
       </c>
-      <c r="E65" s="11" t="n">
+      <c r="E14" s="25" t="n">
         <v>539.58</v>
       </c>
-      <c r="F65" s="10" t="n">
+      <c r="F14" s="24" t="n">
         <v>379763.8</v>
       </c>
-      <c r="G65" s="10" t="n">
+      <c r="G14" s="24" t="n">
         <v>13768.95</v>
       </c>
     </row>
-    <row r="66" ht="13" customHeight="1">
-      <c r="A66" s="12" t="inlineStr">
-        <is>
-          <t>2031-11</t>
-        </is>
-      </c>
-      <c r="B66" s="13" t="n">
-        <v>0</v>
-      </c>
-      <c r="C66" s="13" t="n">
-        <v>0</v>
-      </c>
-      <c r="D66" s="13" t="n">
+    <row r="15" ht="15" customHeight="1">
+      <c r="A15" s="20" t="inlineStr">
+        <is>
+          <t>نوفمبر 2031</t>
+        </is>
+      </c>
+      <c r="B15" s="21" t="n">
+        <v>0</v>
+      </c>
+      <c r="C15" s="21" t="n">
+        <v>0</v>
+      </c>
+      <c r="D15" s="21" t="n">
         <v>539.58</v>
       </c>
-      <c r="E66" s="14" t="n">
+      <c r="E15" s="22" t="n">
         <v>539.58</v>
       </c>
-      <c r="F66" s="13" t="n">
+      <c r="F15" s="21" t="n">
         <v>380303.38</v>
       </c>
-      <c r="G66" s="13" t="n">
+      <c r="G15" s="21" t="n">
         <v>13229.37</v>
       </c>
     </row>
-    <row r="67" ht="13" customHeight="1">
-      <c r="A67" s="9" t="inlineStr">
-        <is>
-          <t>2031-12</t>
-        </is>
-      </c>
-      <c r="B67" s="10" t="n">
-        <v>0</v>
-      </c>
-      <c r="C67" s="10" t="n">
-        <v>0</v>
-      </c>
-      <c r="D67" s="10" t="n">
+    <row r="16" ht="15" customHeight="1">
+      <c r="A16" s="23" t="inlineStr">
+        <is>
+          <t>ديسمبر 2031</t>
+        </is>
+      </c>
+      <c r="B16" s="24" t="n">
+        <v>0</v>
+      </c>
+      <c r="C16" s="24" t="n">
+        <v>0</v>
+      </c>
+      <c r="D16" s="24" t="n">
         <v>539.58</v>
       </c>
-      <c r="E67" s="11" t="n">
+      <c r="E16" s="25" t="n">
         <v>539.58</v>
       </c>
-      <c r="F67" s="10" t="n">
+      <c r="F16" s="24" t="n">
         <v>380842.96</v>
       </c>
-      <c r="G67" s="10" t="n">
+      <c r="G16" s="24" t="n">
         <v>12689.79</v>
       </c>
     </row>
-    <row r="68" ht="13" customHeight="1">
-      <c r="A68" s="12" t="inlineStr">
-        <is>
-          <t>2032-01</t>
-        </is>
-      </c>
-      <c r="B68" s="13" t="n">
-        <v>0</v>
-      </c>
-      <c r="C68" s="13" t="n">
-        <v>0</v>
-      </c>
-      <c r="D68" s="13" t="n">
+    <row r="17" ht="18" customHeight="1">
+      <c r="A17" s="26" t="inlineStr">
+        <is>
+          <t>إجمالي سنة 2031</t>
+        </is>
+      </c>
+      <c r="B17" s="17" t="n">
+        <v>0</v>
+      </c>
+      <c r="C17" s="17" t="n">
+        <v>0</v>
+      </c>
+      <c r="D17" s="17" t="n">
+        <v>6840.62</v>
+      </c>
+      <c r="E17" s="17" t="n">
+        <v>6840.62</v>
+      </c>
+      <c r="F17" s="16" t="inlineStr"/>
+      <c r="G17" s="16" t="inlineStr"/>
+    </row>
+  </sheetData>
+  <mergeCells count="2">
+    <mergeCell ref="A2:G2"/>
+    <mergeCell ref="A1:G1"/>
+  </mergeCells>
+  <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
+</worksheet>
+</file>
+
+<file path=xl/worksheets/sheet9.xml><?xml version="1.0" encoding="utf-8"?>
+<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
+  <sheetPr>
+    <outlinePr summaryBelow="1" summaryRight="1"/>
+    <pageSetUpPr/>
+  </sheetPr>
+  <dimension ref="A1:G17"/>
+  <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
+  <cols>
+    <col width="18" customWidth="1" min="1" max="1"/>
+    <col width="14" customWidth="1" min="2" max="2"/>
+    <col width="12" customWidth="1" min="3" max="3"/>
+    <col width="15" customWidth="1" min="4" max="4"/>
+    <col width="16" customWidth="1" min="5" max="5"/>
+    <col width="18" customWidth="1" min="6" max="6"/>
+    <col width="15" customWidth="1" min="7" max="7"/>
+  </cols>
+  <sheetData>
+    <row r="1" ht="24" customHeight="1">
+      <c r="A1" s="1" t="inlineStr">
+        <is>
+          <t>إهلاك السنة المالية 2032 — شهر بشهر</t>
+        </is>
+      </c>
+    </row>
+    <row r="2" ht="16" customHeight="1">
+      <c r="A2" s="18" t="inlineStr">
+        <is>
+          <t>القسط الشهري ثابت لكل أصل حتى نهاية عمره؛ يقلّ الإجمالي كلما اكتمل إهلاك أصل.</t>
+        </is>
+      </c>
+    </row>
+    <row r="4">
+      <c r="A4" s="19" t="inlineStr">
+        <is>
+          <t>الشهر
+Month</t>
+        </is>
+      </c>
+      <c r="B4" s="19" t="inlineStr">
+        <is>
+          <t>سيارات
+Vehicles</t>
+        </is>
+      </c>
+      <c r="C4" s="19" t="inlineStr">
+        <is>
+          <t>تقنية
+IT</t>
+        </is>
+      </c>
+      <c r="D4" s="19" t="inlineStr">
+        <is>
+          <t>آلات ومعدات
+Machinery</t>
+        </is>
+      </c>
+      <c r="E4" s="19" t="inlineStr">
+        <is>
+          <t>إجمالي الشهر
+Monthly total</t>
+        </is>
+      </c>
+      <c r="F4" s="19" t="inlineStr">
+        <is>
+          <t>مجمّع تراكمي (كلي)
+Cumulative (all)</t>
+        </is>
+      </c>
+      <c r="G4" s="19" t="inlineStr">
+        <is>
+          <t>صافي متبقّي
+Remaining NBV</t>
+        </is>
+      </c>
+    </row>
+    <row r="5" ht="15" customHeight="1">
+      <c r="A5" s="20" t="inlineStr">
+        <is>
+          <t>يناير 2032</t>
+        </is>
+      </c>
+      <c r="B5" s="21" t="n">
+        <v>0</v>
+      </c>
+      <c r="C5" s="21" t="n">
+        <v>0</v>
+      </c>
+      <c r="D5" s="21" t="n">
         <v>539.58</v>
       </c>
-      <c r="E68" s="14" t="n">
+      <c r="E5" s="22" t="n">
         <v>539.58</v>
       </c>
-      <c r="F68" s="13" t="n">
+      <c r="F5" s="21" t="n">
         <v>381382.54</v>
       </c>
-      <c r="G68" s="13" t="n">
+      <c r="G5" s="21" t="n">
         <v>12150.21</v>
       </c>
     </row>
-    <row r="69" ht="13" customHeight="1">
-      <c r="A69" s="9" t="inlineStr">
-        <is>
-          <t>2032-02</t>
-        </is>
-      </c>
-      <c r="B69" s="10" t="n">
-        <v>0</v>
-      </c>
-      <c r="C69" s="10" t="n">
-        <v>0</v>
-      </c>
-      <c r="D69" s="10" t="n">
+    <row r="6" ht="15" customHeight="1">
+      <c r="A6" s="23" t="inlineStr">
+        <is>
+          <t>فبراير 2032</t>
+        </is>
+      </c>
+      <c r="B6" s="24" t="n">
+        <v>0</v>
+      </c>
+      <c r="C6" s="24" t="n">
+        <v>0</v>
+      </c>
+      <c r="D6" s="24" t="n">
         <v>539.58</v>
       </c>
-      <c r="E69" s="11" t="n">
+      <c r="E6" s="25" t="n">
         <v>539.58</v>
       </c>
-      <c r="F69" s="10" t="n">
+      <c r="F6" s="24" t="n">
         <v>381922.12</v>
       </c>
-      <c r="G69" s="10" t="n">
+      <c r="G6" s="24" t="n">
         <v>11610.63</v>
       </c>
     </row>
-    <row r="70" ht="13" customHeight="1">
-      <c r="A70" s="12" t="inlineStr">
-        <is>
-          <t>2032-03</t>
-        </is>
-      </c>
-      <c r="B70" s="13" t="n">
-        <v>0</v>
-      </c>
-      <c r="C70" s="13" t="n">
-        <v>0</v>
-      </c>
-      <c r="D70" s="13" t="n">
+    <row r="7" ht="15" customHeight="1">
+      <c r="A7" s="20" t="inlineStr">
+        <is>
+          <t>مارس 2032</t>
+        </is>
+      </c>
+      <c r="B7" s="21" t="n">
+        <v>0</v>
+      </c>
+      <c r="C7" s="21" t="n">
+        <v>0</v>
+      </c>
+      <c r="D7" s="21" t="n">
         <v>539.58</v>
       </c>
-      <c r="E70" s="14" t="n">
+      <c r="E7" s="22" t="n">
         <v>539.58</v>
       </c>
-      <c r="F70" s="13" t="n">
+      <c r="F7" s="21" t="n">
         <v>382461.7</v>
       </c>
-      <c r="G70" s="13" t="n">
+      <c r="G7" s="21" t="n">
         <v>11071.05</v>
       </c>
     </row>
-    <row r="71" ht="13" customHeight="1">
-      <c r="A71" s="9" t="inlineStr">
-        <is>
-          <t>2032-04</t>
-        </is>
-      </c>
-      <c r="B71" s="10" t="n">
-        <v>0</v>
-      </c>
-      <c r="C71" s="10" t="n">
-        <v>0</v>
-      </c>
-      <c r="D71" s="10" t="n">
+    <row r="8" ht="15" customHeight="1">
+      <c r="A8" s="23" t="inlineStr">
+        <is>
+          <t>أبريل 2032</t>
+        </is>
+      </c>
+      <c r="B8" s="24" t="n">
+        <v>0</v>
+      </c>
+      <c r="C8" s="24" t="n">
+        <v>0</v>
+      </c>
+      <c r="D8" s="24" t="n">
         <v>539.58</v>
       </c>
-      <c r="E71" s="11" t="n">
+      <c r="E8" s="25" t="n">
         <v>539.58</v>
       </c>
-      <c r="F71" s="10" t="n">
+      <c r="F8" s="24" t="n">
         <v>383001.28</v>
       </c>
-      <c r="G71" s="10" t="n">
+      <c r="G8" s="24" t="n">
         <v>10531.47</v>
       </c>
     </row>
-    <row r="72" ht="13" customHeight="1">
-      <c r="A72" s="12" t="inlineStr">
-        <is>
-          <t>2032-05</t>
-        </is>
-      </c>
-      <c r="B72" s="13" t="n">
-        <v>0</v>
-      </c>
-      <c r="C72" s="13" t="n">
-        <v>0</v>
-      </c>
-      <c r="D72" s="13" t="n">
+    <row r="9" ht="15" customHeight="1">
+      <c r="A9" s="20" t="inlineStr">
+        <is>
+          <t>مايو 2032</t>
+        </is>
+      </c>
+      <c r="B9" s="21" t="n">
+        <v>0</v>
+      </c>
+      <c r="C9" s="21" t="n">
+        <v>0</v>
+      </c>
+      <c r="D9" s="21" t="n">
         <v>539.58</v>
       </c>
-      <c r="E72" s="14" t="n">
+      <c r="E9" s="22" t="n">
         <v>539.58</v>
       </c>
-      <c r="F72" s="13" t="n">
+      <c r="F9" s="21" t="n">
         <v>383540.86</v>
       </c>
-      <c r="G72" s="13" t="n">
+      <c r="G9" s="21" t="n">
         <v>9991.889999999999</v>
       </c>
     </row>
-    <row r="73" ht="13" customHeight="1">
-      <c r="A73" s="9" t="inlineStr">
-        <is>
-          <t>2032-06</t>
-        </is>
-      </c>
-      <c r="B73" s="10" t="n">
-        <v>0</v>
-      </c>
-      <c r="C73" s="10" t="n">
-        <v>0</v>
-      </c>
-      <c r="D73" s="10" t="n">
+    <row r="10" ht="15" customHeight="1">
+      <c r="A10" s="23" t="inlineStr">
+        <is>
+          <t>يونيو 2032</t>
+        </is>
+      </c>
+      <c r="B10" s="24" t="n">
+        <v>0</v>
+      </c>
+      <c r="C10" s="24" t="n">
+        <v>0</v>
+      </c>
+      <c r="D10" s="24" t="n">
         <v>539.58</v>
       </c>
-      <c r="E73" s="11" t="n">
+      <c r="E10" s="25" t="n">
         <v>539.58</v>
       </c>
-      <c r="F73" s="10" t="n">
+      <c r="F10" s="24" t="n">
         <v>384080.44</v>
       </c>
-      <c r="G73" s="10" t="n">
+      <c r="G10" s="24" t="n">
         <v>9452.309999999999</v>
       </c>
     </row>
-    <row r="74" ht="13" customHeight="1">
-      <c r="A74" s="12" t="inlineStr">
-        <is>
-          <t>2032-07</t>
-        </is>
-      </c>
-      <c r="B74" s="13" t="n">
-        <v>0</v>
-      </c>
-      <c r="C74" s="13" t="n">
-        <v>0</v>
-      </c>
-      <c r="D74" s="13" t="n">
+    <row r="11" ht="15" customHeight="1">
+      <c r="A11" s="20" t="inlineStr">
+        <is>
+          <t>يوليو 2032</t>
+        </is>
+      </c>
+      <c r="B11" s="21" t="n">
+        <v>0</v>
+      </c>
+      <c r="C11" s="21" t="n">
+        <v>0</v>
+      </c>
+      <c r="D11" s="21" t="n">
         <v>539.58</v>
       </c>
-      <c r="E74" s="14" t="n">
+      <c r="E11" s="22" t="n">
         <v>539.58</v>
       </c>
-      <c r="F74" s="13" t="n">
+      <c r="F11" s="21" t="n">
         <v>384620.02</v>
       </c>
-      <c r="G74" s="13" t="n">
+      <c r="G11" s="21" t="n">
         <v>8912.73</v>
       </c>
     </row>
-    <row r="75" ht="13" customHeight="1">
-      <c r="A75" s="9" t="inlineStr">
-        <is>
-          <t>2032-08</t>
-        </is>
-      </c>
-      <c r="B75" s="10" t="n">
-        <v>0</v>
-      </c>
-      <c r="C75" s="10" t="n">
-        <v>0</v>
-      </c>
-      <c r="D75" s="10" t="n">
+    <row r="12" ht="15" customHeight="1">
+      <c r="A12" s="23" t="inlineStr">
+        <is>
+          <t>أغسطس 2032</t>
+        </is>
+      </c>
+      <c r="B12" s="24" t="n">
+        <v>0</v>
+      </c>
+      <c r="C12" s="24" t="n">
+        <v>0</v>
+      </c>
+      <c r="D12" s="24" t="n">
         <v>539.58</v>
       </c>
-      <c r="E75" s="11" t="n">
+      <c r="E12" s="25" t="n">
         <v>539.58</v>
       </c>
-      <c r="F75" s="10" t="n">
+      <c r="F12" s="24" t="n">
         <v>385159.6</v>
       </c>
-      <c r="G75" s="10" t="n">
+      <c r="G12" s="24" t="n">
         <v>8373.15</v>
       </c>
     </row>
-    <row r="76" ht="13" customHeight="1">
-      <c r="A76" s="12" t="inlineStr">
-        <is>
-          <t>2032-09</t>
-        </is>
-      </c>
-      <c r="B76" s="13" t="n">
-        <v>0</v>
-      </c>
-      <c r="C76" s="13" t="n">
-        <v>0</v>
-      </c>
-      <c r="D76" s="13" t="n">
+    <row r="13" ht="15" customHeight="1">
+      <c r="A13" s="20" t="inlineStr">
+        <is>
+          <t>سبتمبر 2032</t>
+        </is>
+      </c>
+      <c r="B13" s="21" t="n">
+        <v>0</v>
+      </c>
+      <c r="C13" s="21" t="n">
+        <v>0</v>
+      </c>
+      <c r="D13" s="21" t="n">
         <v>539.58</v>
       </c>
-      <c r="E76" s="14" t="n">
+      <c r="E13" s="22" t="n">
         <v>539.58</v>
       </c>
-      <c r="F76" s="13" t="n">
+      <c r="F13" s="21" t="n">
         <v>385699.18</v>
       </c>
-      <c r="G76" s="13" t="n">
+      <c r="G13" s="21" t="n">
         <v>7833.57</v>
       </c>
     </row>
-    <row r="77" ht="13" customHeight="1">
-      <c r="A77" s="9" t="inlineStr">
-        <is>
-          <t>2032-10</t>
-        </is>
-      </c>
-      <c r="B77" s="10" t="n">
-        <v>0</v>
-      </c>
-      <c r="C77" s="10" t="n">
-        <v>0</v>
-      </c>
-      <c r="D77" s="10" t="n">
+    <row r="14" ht="15" customHeight="1">
+      <c r="A14" s="23" t="inlineStr">
+        <is>
+          <t>أكتوبر 2032</t>
+        </is>
+      </c>
+      <c r="B14" s="24" t="n">
+        <v>0</v>
+      </c>
+      <c r="C14" s="24" t="n">
+        <v>0</v>
+      </c>
+      <c r="D14" s="24" t="n">
         <v>539.58</v>
       </c>
-      <c r="E77" s="11" t="n">
+      <c r="E14" s="25" t="n">
         <v>539.58</v>
       </c>
-      <c r="F77" s="10" t="n">
+      <c r="F14" s="24" t="n">
         <v>386238.76</v>
       </c>
-      <c r="G77" s="10" t="n">
+      <c r="G14" s="24" t="n">
         <v>7293.99</v>
       </c>
     </row>
-    <row r="78" ht="13" customHeight="1">
-      <c r="A78" s="12" t="inlineStr">
-        <is>
-          <t>2032-11</t>
-        </is>
-      </c>
-      <c r="B78" s="13" t="n">
-        <v>0</v>
-      </c>
-      <c r="C78" s="13" t="n">
-        <v>0</v>
-      </c>
-      <c r="D78" s="13" t="n">
+    <row r="15" ht="15" customHeight="1">
+      <c r="A15" s="20" t="inlineStr">
+        <is>
+          <t>نوفمبر 2032</t>
+        </is>
+      </c>
+      <c r="B15" s="21" t="n">
+        <v>0</v>
+      </c>
+      <c r="C15" s="21" t="n">
+        <v>0</v>
+      </c>
+      <c r="D15" s="21" t="n">
         <v>539.58</v>
       </c>
-      <c r="E78" s="14" t="n">
+      <c r="E15" s="22" t="n">
         <v>539.58</v>
       </c>
-      <c r="F78" s="13" t="n">
+      <c r="F15" s="21" t="n">
         <v>386778.34</v>
       </c>
-      <c r="G78" s="13" t="n">
+      <c r="G15" s="21" t="n">
         <v>6754.41</v>
       </c>
     </row>
-    <row r="79" ht="13" customHeight="1">
-      <c r="A79" s="9" t="inlineStr">
-        <is>
-          <t>2032-12</t>
-        </is>
-      </c>
-      <c r="B79" s="10" t="n">
-        <v>0</v>
-      </c>
-      <c r="C79" s="10" t="n">
-        <v>0</v>
-      </c>
-      <c r="D79" s="10" t="n">
+    <row r="16" ht="15" customHeight="1">
+      <c r="A16" s="23" t="inlineStr">
+        <is>
+          <t>ديسمبر 2032</t>
+        </is>
+      </c>
+      <c r="B16" s="24" t="n">
+        <v>0</v>
+      </c>
+      <c r="C16" s="24" t="n">
+        <v>0</v>
+      </c>
+      <c r="D16" s="24" t="n">
         <v>539.58</v>
       </c>
-      <c r="E79" s="11" t="n">
+      <c r="E16" s="25" t="n">
         <v>539.58</v>
       </c>
-      <c r="F79" s="10" t="n">
+      <c r="F16" s="24" t="n">
         <v>387317.92</v>
       </c>
-      <c r="G79" s="10" t="n">
+      <c r="G16" s="24" t="n">
         <v>6214.83</v>
       </c>
     </row>
-    <row r="80" ht="13" customHeight="1">
-      <c r="A80" s="12" t="inlineStr">
-        <is>
-          <t>2033-01</t>
-        </is>
-      </c>
-      <c r="B80" s="13" t="n">
-        <v>0</v>
-      </c>
-      <c r="C80" s="13" t="n">
-        <v>0</v>
-      </c>
-      <c r="D80" s="13" t="n">
-        <v>539.58</v>
-      </c>
-      <c r="E80" s="14" t="n">
-        <v>539.58</v>
-      </c>
-      <c r="F80" s="13" t="n">
-        <v>387857.5</v>
-      </c>
-      <c r="G80" s="13" t="n">
-        <v>5675.25</v>
-      </c>
-    </row>
-    <row r="81" ht="13" customHeight="1">
-      <c r="A81" s="9" t="inlineStr">
-        <is>
-          <t>2033-02</t>
-        </is>
-      </c>
-      <c r="B81" s="10" t="n">
-        <v>0</v>
-      </c>
-      <c r="C81" s="10" t="n">
-        <v>0</v>
-      </c>
-      <c r="D81" s="10" t="n">
-        <v>539.84</v>
-      </c>
-      <c r="E81" s="11" t="n">
-        <v>539.84</v>
-      </c>
-      <c r="F81" s="10" t="n">
-        <v>388397.34</v>
-      </c>
-      <c r="G81" s="10" t="n">
-        <v>5135.41</v>
-      </c>
-    </row>
-    <row r="82" ht="13" customHeight="1">
-      <c r="A82" s="12" t="inlineStr">
-        <is>
-          <t>2033-03</t>
-        </is>
-      </c>
-      <c r="B82" s="13" t="n">
-        <v>0</v>
-      </c>
-      <c r="C82" s="13" t="n">
-        <v>0</v>
-      </c>
-      <c r="D82" s="13" t="n">
-        <v>468.75</v>
-      </c>
-      <c r="E82" s="14" t="n">
-        <v>468.75</v>
-      </c>
-      <c r="F82" s="13" t="n">
-        <v>388866.09</v>
-      </c>
-      <c r="G82" s="13" t="n">
-        <v>4666.66</v>
-      </c>
-    </row>
-    <row r="83" ht="13" customHeight="1">
-      <c r="A83" s="9" t="inlineStr">
-        <is>
-          <t>2033-04</t>
-        </is>
-      </c>
-      <c r="B83" s="10" t="n">
-        <v>0</v>
-      </c>
-      <c r="C83" s="10" t="n">
-        <v>0</v>
-      </c>
-      <c r="D83" s="10" t="n">
-        <v>468.75</v>
-      </c>
-      <c r="E83" s="11" t="n">
-        <v>468.75</v>
-      </c>
-      <c r="F83" s="10" t="n">
-        <v>389334.84</v>
-      </c>
-      <c r="G83" s="10" t="n">
-        <v>4197.91</v>
-      </c>
-    </row>
-    <row r="84" ht="13" customHeight="1">
-      <c r="A84" s="12" t="inlineStr">
-        <is>
-          <t>2033-05</t>
-        </is>
-      </c>
-      <c r="B84" s="13" t="n">
-        <v>0</v>
-      </c>
-      <c r="C84" s="13" t="n">
-        <v>0</v>
-      </c>
-      <c r="D84" s="13" t="n">
-        <v>468.75</v>
-      </c>
-      <c r="E84" s="14" t="n">
-        <v>468.75</v>
-      </c>
-      <c r="F84" s="13" t="n">
-        <v>389803.59</v>
-      </c>
-      <c r="G84" s="13" t="n">
-        <v>3729.16</v>
-      </c>
-    </row>
-    <row r="85" ht="13" customHeight="1">
-      <c r="A85" s="9" t="inlineStr">
-        <is>
-          <t>2033-06</t>
-        </is>
-      </c>
-      <c r="B85" s="10" t="n">
-        <v>0</v>
-      </c>
-      <c r="C85" s="10" t="n">
-        <v>0</v>
-      </c>
-      <c r="D85" s="10" t="n">
-        <v>468.75</v>
-      </c>
-      <c r="E85" s="11" t="n">
-        <v>468.75</v>
-      </c>
-      <c r="F85" s="10" t="n">
-        <v>390272.34</v>
-      </c>
-      <c r="G85" s="10" t="n">
-        <v>3260.41</v>
-      </c>
-    </row>
-    <row r="86" ht="13" customHeight="1">
-      <c r="A86" s="12" t="inlineStr">
-        <is>
-          <t>2033-07</t>
-        </is>
-      </c>
-      <c r="B86" s="13" t="n">
-        <v>0</v>
-      </c>
-      <c r="C86" s="13" t="n">
-        <v>0</v>
-      </c>
-      <c r="D86" s="13" t="n">
-        <v>468.75</v>
-      </c>
-      <c r="E86" s="14" t="n">
-        <v>468.75</v>
-      </c>
-      <c r="F86" s="13" t="n">
-        <v>390741.09</v>
-      </c>
-      <c r="G86" s="13" t="n">
-        <v>2791.66</v>
-      </c>
-    </row>
-    <row r="87" ht="13" customHeight="1">
-      <c r="A87" s="9" t="inlineStr">
-        <is>
-          <t>2033-08</t>
-        </is>
-      </c>
-      <c r="B87" s="10" t="n">
-        <v>0</v>
-      </c>
-      <c r="C87" s="10" t="n">
-        <v>0</v>
-      </c>
-      <c r="D87" s="10" t="n">
-        <v>468.75</v>
-      </c>
-      <c r="E87" s="11" t="n">
-        <v>468.75</v>
-      </c>
-      <c r="F87" s="10" t="n">
-        <v>391209.84</v>
-      </c>
-      <c r="G87" s="10" t="n">
-        <v>2322.91</v>
-      </c>
-    </row>
-    <row r="88" ht="13" customHeight="1">
-      <c r="A88" s="12" t="inlineStr">
-        <is>
-          <t>2033-09</t>
-        </is>
-      </c>
-      <c r="B88" s="13" t="n">
-        <v>0</v>
-      </c>
-      <c r="C88" s="13" t="n">
-        <v>0</v>
-      </c>
-      <c r="D88" s="13" t="n">
-        <v>468.75</v>
-      </c>
-      <c r="E88" s="14" t="n">
-        <v>468.75</v>
-      </c>
-      <c r="F88" s="13" t="n">
-        <v>391678.59</v>
-      </c>
-      <c r="G88" s="13" t="n">
-        <v>1854.16</v>
-      </c>
-    </row>
-    <row r="89" ht="13" customHeight="1">
-      <c r="A89" s="9" t="inlineStr">
-        <is>
-          <t>2033-10</t>
-        </is>
-      </c>
-      <c r="B89" s="10" t="n">
-        <v>0</v>
-      </c>
-      <c r="C89" s="10" t="n">
-        <v>0</v>
-      </c>
-      <c r="D89" s="10" t="n">
-        <v>468.75</v>
-      </c>
-      <c r="E89" s="11" t="n">
-        <v>468.75</v>
-      </c>
-      <c r="F89" s="10" t="n">
-        <v>392147.34</v>
-      </c>
-      <c r="G89" s="10" t="n">
-        <v>1385.41</v>
-      </c>
-    </row>
-    <row r="90" ht="13" customHeight="1">
-      <c r="A90" s="12" t="inlineStr">
-        <is>
-          <t>2033-11</t>
-        </is>
-      </c>
-      <c r="B90" s="13" t="n">
-        <v>0</v>
-      </c>
-      <c r="C90" s="13" t="n">
-        <v>0</v>
-      </c>
-      <c r="D90" s="13" t="n">
-        <v>468.46</v>
-      </c>
-      <c r="E90" s="14" t="n">
-        <v>468.46</v>
-      </c>
-      <c r="F90" s="13" t="n">
-        <v>392615.8</v>
-      </c>
-      <c r="G90" s="13" t="n">
-        <v>916.95</v>
-      </c>
-    </row>
-    <row r="91" ht="13" customHeight="1">
-      <c r="A91" s="9" t="inlineStr">
-        <is>
-          <t>2033-12</t>
-        </is>
-      </c>
-      <c r="B91" s="10" t="n">
-        <v>0</v>
-      </c>
-      <c r="C91" s="10" t="n">
-        <v>0</v>
-      </c>
-      <c r="D91" s="10" t="n">
-        <v>458.33</v>
-      </c>
-      <c r="E91" s="11" t="n">
-        <v>458.33</v>
-      </c>
-      <c r="F91" s="10" t="n">
-        <v>393074.13</v>
-      </c>
-      <c r="G91" s="10" t="n">
-        <v>458.62</v>
-      </c>
-    </row>
-    <row r="92" ht="13" customHeight="1">
-      <c r="A92" s="12" t="inlineStr">
-        <is>
-          <t>2034-01</t>
-        </is>
-      </c>
-      <c r="B92" s="13" t="n">
-        <v>0</v>
-      </c>
-      <c r="C92" s="13" t="n">
-        <v>0</v>
-      </c>
-      <c r="D92" s="13" t="n">
-        <v>458.62</v>
-      </c>
-      <c r="E92" s="14" t="n">
-        <v>458.62</v>
-      </c>
-      <c r="F92" s="13" t="n">
-        <v>393532.75</v>
-      </c>
-      <c r="G92" s="13" t="n">
-        <v>0</v>
-      </c>
+    <row r="17" ht="18" customHeight="1">
+      <c r="A17" s="26" t="inlineStr">
+        <is>
+          <t>إجمالي سنة 2032</t>
+        </is>
+      </c>
+      <c r="B17" s="17" t="n">
+        <v>0</v>
+      </c>
+      <c r="C17" s="17" t="n">
+        <v>0</v>
+      </c>
+      <c r="D17" s="17" t="n">
+        <v>6474.96</v>
+      </c>
+      <c r="E17" s="17" t="n">
+        <v>6474.96</v>
+      </c>
+      <c r="F17" s="16" t="inlineStr"/>
+      <c r="G17" s="16" t="inlineStr"/>
     </row>
   </sheetData>
   <mergeCells count="2">
